--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>69328</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>117.900001525879</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>114.400001525879</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>114.400001525879</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>117.199996948242</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>66489</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>113.400001525879</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>116.099998474121</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>47699</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>116</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>114.400001525879</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>116</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>114.300003051758</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -62943,7 +62943,7 @@
         <v>116</v>
       </c>
       <c r="D2721" t="n">
-        <v>114.400001525879</v>
+        <v>114.300003051758</v>
       </c>
       <c r="E2721" t="n">
         <v>116</v>
@@ -62952,6 +62952,29 @@
         <v>114.300003051758</v>
       </c>
       <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>51815</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>117.900001525879</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>115.099998474121</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>115.400001525879</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>116.199996948242</v>
+      </c>
+      <c r="G2722" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>53602</v>
+        <v>54060</v>
       </c>
       <c r="C2715" t="n">
-        <v>120</v>
+        <v>121.199996948242</v>
       </c>
       <c r="D2715" t="n">
-        <v>116.400001525879</v>
+        <v>118.400001525879</v>
       </c>
       <c r="E2715" t="n">
-        <v>119</v>
+        <v>119.400001525879</v>
       </c>
       <c r="F2715" t="n">
-        <v>118.400001525879</v>
+        <v>119.199996948242</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>112008</v>
+        <v>53602</v>
       </c>
       <c r="C2716" t="n">
-        <v>118.199996948242</v>
+        <v>120</v>
       </c>
       <c r="D2716" t="n">
-        <v>112.400001525879</v>
+        <v>116.400001525879</v>
       </c>
       <c r="E2716" t="n">
-        <v>117.599998474121</v>
+        <v>119</v>
       </c>
       <c r="F2716" t="n">
-        <v>113.099998474121</v>
+        <v>118.400001525879</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>113301</v>
+        <v>112008</v>
       </c>
       <c r="C2717" t="n">
+        <v>118.199996948242</v>
+      </c>
+      <c r="D2717" t="n">
+        <v>112.400001525879</v>
+      </c>
+      <c r="E2717" t="n">
+        <v>117.599998474121</v>
+      </c>
+      <c r="F2717" t="n">
         <v>113.099998474121</v>
-      </c>
-      <c r="D2717" t="n">
-        <v>110.599998474121</v>
-      </c>
-      <c r="E2717" t="n">
-        <v>112.699996948242</v>
-      </c>
-      <c r="F2717" t="n">
-        <v>112.099998474121</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>34850</v>
+        <v>113301</v>
       </c>
       <c r="C2718" t="n">
-        <v>114</v>
+        <v>113.099998474121</v>
       </c>
       <c r="D2718" t="n">
-        <v>110.400001525879</v>
+        <v>110.599998474121</v>
       </c>
       <c r="E2718" t="n">
-        <v>111</v>
+        <v>112.699996948242</v>
       </c>
       <c r="F2718" t="n">
-        <v>114</v>
+        <v>112.099998474121</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>69328</v>
+        <v>34850</v>
       </c>
       <c r="C2719" t="n">
-        <v>117.900001525879</v>
+        <v>114</v>
       </c>
       <c r="D2719" t="n">
-        <v>114.400001525879</v>
+        <v>110.400001525879</v>
       </c>
       <c r="E2719" t="n">
-        <v>114.400001525879</v>
+        <v>111</v>
       </c>
       <c r="F2719" t="n">
-        <v>117.199996948242</v>
+        <v>114</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>66489</v>
+        <v>69328</v>
       </c>
       <c r="C2720" t="n">
-        <v>117.5</v>
+        <v>117.900001525879</v>
       </c>
       <c r="D2720" t="n">
-        <v>113.400001525879</v>
+        <v>114.400001525879</v>
       </c>
       <c r="E2720" t="n">
-        <v>117.5</v>
+        <v>114.400001525879</v>
       </c>
       <c r="F2720" t="n">
-        <v>116.099998474121</v>
+        <v>117.199996948242</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>47699</v>
+        <v>66489</v>
       </c>
       <c r="C2721" t="n">
-        <v>116</v>
+        <v>117.5</v>
       </c>
       <c r="D2721" t="n">
-        <v>114.300003051758</v>
+        <v>113.400001525879</v>
       </c>
       <c r="E2721" t="n">
-        <v>116</v>
+        <v>117.5</v>
       </c>
       <c r="F2721" t="n">
-        <v>114.300003051758</v>
+        <v>116.099998474121</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>51815</v>
+        <v>47699</v>
       </c>
       <c r="C2722" t="n">
-        <v>117.900001525879</v>
+        <v>116</v>
       </c>
       <c r="D2722" t="n">
-        <v>115.099998474121</v>
+        <v>114.300003051758</v>
       </c>
       <c r="E2722" t="n">
+        <v>116</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>114.300003051758</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>397489</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>117.599998474121</v>
+      </c>
+      <c r="D2723" t="n">
         <v>115.400001525879</v>
       </c>
-      <c r="F2722" t="n">
+      <c r="E2723" t="n">
         <v>116.199996948242</v>
       </c>
-      <c r="G2722" t="s">
+      <c r="F2723" t="n">
+        <v>117.099998474121</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>122.599998474121</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>123</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>116264</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>127.599998474121</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>123.099998474121</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>123.099998474121</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>123.099998474121</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>126.5</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>75712</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>126.900001525879</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>123.800003051758</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>126.099998474121</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>126.099998474121</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>125.800003051758</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>80134</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>126.699996948242</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>123.199996948242</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>125.900001525879</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>125.900001525879</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>123.199996948242</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>74558</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>126.099998474121</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>123.599998474121</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>125</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>80104</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>128.899993896484</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>124.699996948242</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>125.300003051758</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>127</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/REY.MI.xlsx
+++ b/data/REY.MI.xlsx
@@ -427,7 +427,7 @@
         <v>31.5</v>
       </c>
       <c r="G2" t="n">
-        <v>28.8517169952393</v>
+        <v>28.8517208099365</v>
       </c>
       <c r="H2" t="n">
         <v>26844</v>
@@ -456,7 +456,7 @@
         <v>31.0499992370605</v>
       </c>
       <c r="G3" t="n">
-        <v>28.4395484924316</v>
+        <v>28.439546585083</v>
       </c>
       <c r="H3" t="n">
         <v>50984</v>
@@ -485,7 +485,7 @@
         <v>31.5</v>
       </c>
       <c r="G4" t="n">
-        <v>28.8517169952393</v>
+        <v>28.8517208099365</v>
       </c>
       <c r="H4" t="n">
         <v>57612</v>
@@ -514,7 +514,7 @@
         <v>30.5</v>
       </c>
       <c r="G5" t="n">
-        <v>27.9357891082764</v>
+        <v>27.935791015625</v>
       </c>
       <c r="H5" t="n">
         <v>66144</v>
@@ -572,7 +572,7 @@
         <v>29.9750003814697</v>
       </c>
       <c r="G7" t="n">
-        <v>27.4549293518066</v>
+        <v>27.454927444458</v>
       </c>
       <c r="H7" t="n">
         <v>49196</v>
@@ -601,7 +601,7 @@
         <v>30.375</v>
       </c>
       <c r="G8" t="n">
-        <v>27.8212985992432</v>
+        <v>27.8213005065918</v>
       </c>
       <c r="H8" t="n">
         <v>24724</v>
@@ -659,7 +659,7 @@
         <v>30.75</v>
       </c>
       <c r="G10" t="n">
-        <v>28.1647720336914</v>
+        <v>28.1647701263428</v>
       </c>
       <c r="H10" t="n">
         <v>73924</v>
@@ -688,7 +688,7 @@
         <v>30.2999992370605</v>
       </c>
       <c r="G11" t="n">
-        <v>27.7526054382324</v>
+        <v>27.7526073455811</v>
       </c>
       <c r="H11" t="n">
         <v>63004</v>
@@ -746,7 +746,7 @@
         <v>30.125</v>
       </c>
       <c r="G13" t="n">
-        <v>27.5923175811768</v>
+        <v>27.5923233032227</v>
       </c>
       <c r="H13" t="n">
         <v>88404</v>
@@ -775,7 +775,7 @@
         <v>28.9249992370605</v>
       </c>
       <c r="G14" t="n">
-        <v>26.4932022094727</v>
+        <v>26.4932060241699</v>
       </c>
       <c r="H14" t="n">
         <v>59996</v>
@@ -804,7 +804,7 @@
         <v>29.5499992370605</v>
       </c>
       <c r="G15" t="n">
-        <v>27.0656585693359</v>
+        <v>27.0656604766846</v>
       </c>
       <c r="H15" t="n">
         <v>75468</v>
@@ -833,7 +833,7 @@
         <v>30.0750007629395</v>
       </c>
       <c r="G16" t="n">
-        <v>27.5465240478516</v>
+        <v>27.5465183258057</v>
       </c>
       <c r="H16" t="n">
         <v>26796</v>
@@ -862,7 +862,7 @@
         <v>30.125</v>
       </c>
       <c r="G17" t="n">
-        <v>27.5923175811768</v>
+        <v>27.5923233032227</v>
       </c>
       <c r="H17" t="n">
         <v>31832</v>
@@ -891,7 +891,7 @@
         <v>29.9500007629395</v>
       </c>
       <c r="G18" t="n">
-        <v>27.4320297241211</v>
+        <v>27.4320335388184</v>
       </c>
       <c r="H18" t="n">
         <v>30768</v>
@@ -920,7 +920,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G19" t="n">
-        <v>27.8899993896484</v>
+        <v>27.8899955749512</v>
       </c>
       <c r="H19" t="n">
         <v>28872</v>
@@ -949,7 +949,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G20" t="n">
-        <v>27.2946376800537</v>
+        <v>27.294641494751</v>
       </c>
       <c r="H20" t="n">
         <v>25340</v>
@@ -978,7 +978,7 @@
         <v>30.25</v>
       </c>
       <c r="G21" t="n">
-        <v>27.7068099975586</v>
+        <v>27.70680809021</v>
       </c>
       <c r="H21" t="n">
         <v>28440</v>
@@ -1007,7 +1007,7 @@
         <v>30</v>
       </c>
       <c r="G22" t="n">
-        <v>27.4778289794922</v>
+        <v>27.4778270721436</v>
       </c>
       <c r="H22" t="n">
         <v>61864</v>
@@ -1036,7 +1036,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G23" t="n">
-        <v>26.8824729919434</v>
+        <v>26.882474899292</v>
       </c>
       <c r="H23" t="n">
         <v>36724</v>
@@ -1094,7 +1094,7 @@
         <v>28.1749992370605</v>
       </c>
       <c r="G25" t="n">
-        <v>25.8062591552734</v>
+        <v>25.8062572479248</v>
       </c>
       <c r="H25" t="n">
         <v>249420</v>
@@ -1123,7 +1123,7 @@
         <v>27.2250003814697</v>
       </c>
       <c r="G26" t="n">
-        <v>24.9361267089844</v>
+        <v>24.936128616333</v>
       </c>
       <c r="H26" t="n">
         <v>54588</v>
@@ -1152,7 +1152,7 @@
         <v>26.25</v>
       </c>
       <c r="G27" t="n">
-        <v>24.0431003570557</v>
+        <v>24.0430965423584</v>
       </c>
       <c r="H27" t="n">
         <v>97852</v>
@@ -1181,7 +1181,7 @@
         <v>26.5</v>
       </c>
       <c r="G28" t="n">
-        <v>24.2720794677734</v>
+        <v>24.2720813751221</v>
       </c>
       <c r="H28" t="n">
         <v>198832</v>
@@ -1210,7 +1210,7 @@
         <v>28</v>
       </c>
       <c r="G29" t="n">
-        <v>25.6459732055664</v>
+        <v>25.6459693908691</v>
       </c>
       <c r="H29" t="n">
         <v>107372</v>
@@ -1268,7 +1268,7 @@
         <v>27.625</v>
       </c>
       <c r="G31" t="n">
-        <v>25.3024978637695</v>
+        <v>25.3024959564209</v>
       </c>
       <c r="H31" t="n">
         <v>73324</v>
@@ -1326,7 +1326,7 @@
         <v>28.3250007629395</v>
       </c>
       <c r="G33" t="n">
-        <v>25.9436492919922</v>
+        <v>25.9436473846436</v>
       </c>
       <c r="H33" t="n">
         <v>74416</v>
@@ -1384,7 +1384,7 @@
         <v>29.1499996185303</v>
       </c>
       <c r="G35" t="n">
-        <v>26.6992874145508</v>
+        <v>26.699291229248</v>
       </c>
       <c r="H35" t="n">
         <v>59688</v>
@@ -1413,7 +1413,7 @@
         <v>28.2250003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>25.8520584106445</v>
+        <v>25.8520565032959</v>
       </c>
       <c r="H36" t="n">
         <v>44228</v>
@@ -1442,7 +1442,7 @@
         <v>28.5</v>
       </c>
       <c r="G37" t="n">
-        <v>26.1039371490479</v>
+        <v>26.1039352416992</v>
       </c>
       <c r="H37" t="n">
         <v>45164</v>
@@ -1471,7 +1471,7 @@
         <v>28.0499992370605</v>
       </c>
       <c r="G38" t="n">
-        <v>25.6917667388916</v>
+        <v>25.6917705535889</v>
       </c>
       <c r="H38" t="n">
         <v>33012</v>
@@ -1500,7 +1500,7 @@
         <v>27.6749992370605</v>
       </c>
       <c r="G39" t="n">
-        <v>25.348295211792</v>
+        <v>25.3482933044434</v>
       </c>
       <c r="H39" t="n">
         <v>34696</v>
@@ -1529,7 +1529,7 @@
         <v>28</v>
       </c>
       <c r="G40" t="n">
-        <v>25.6459732055664</v>
+        <v>25.6459693908691</v>
       </c>
       <c r="H40" t="n">
         <v>34312</v>
@@ -1558,7 +1558,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G41" t="n">
-        <v>25.3711948394775</v>
+        <v>25.3711910247803</v>
       </c>
       <c r="H41" t="n">
         <v>45648</v>
@@ -1587,7 +1587,7 @@
         <v>28</v>
       </c>
       <c r="G42" t="n">
-        <v>25.6459732055664</v>
+        <v>25.6459693908691</v>
       </c>
       <c r="H42" t="n">
         <v>53864</v>
@@ -1674,7 +1674,7 @@
         <v>28.9249992370605</v>
       </c>
       <c r="G45" t="n">
-        <v>26.4932022094727</v>
+        <v>26.4932060241699</v>
       </c>
       <c r="H45" t="n">
         <v>29252</v>
@@ -1732,7 +1732,7 @@
         <v>29.3500003814697</v>
       </c>
       <c r="G47" t="n">
-        <v>26.8824729919434</v>
+        <v>26.882474899292</v>
       </c>
       <c r="H47" t="n">
         <v>48744</v>
@@ -1790,7 +1790,7 @@
         <v>29.3250007629395</v>
       </c>
       <c r="G49" t="n">
-        <v>26.8595809936523</v>
+        <v>26.8595771789551</v>
       </c>
       <c r="H49" t="n">
         <v>20964</v>
@@ -1819,7 +1819,7 @@
         <v>29.25</v>
       </c>
       <c r="G50" t="n">
-        <v>26.7908840179443</v>
+        <v>26.7908802032471</v>
       </c>
       <c r="H50" t="n">
         <v>37112</v>
@@ -1877,7 +1877,7 @@
         <v>30.0499992370605</v>
       </c>
       <c r="G52" t="n">
-        <v>27.5236225128174</v>
+        <v>27.5236206054688</v>
       </c>
       <c r="H52" t="n">
         <v>42040</v>
@@ -1906,7 +1906,7 @@
         <v>31.25</v>
       </c>
       <c r="G53" t="n">
-        <v>28.6227416992188</v>
+        <v>28.6227359771729</v>
       </c>
       <c r="H53" t="n">
         <v>98952</v>
@@ -1964,7 +1964,7 @@
         <v>32.625</v>
       </c>
       <c r="G55" t="n">
-        <v>29.8821392059326</v>
+        <v>29.882137298584</v>
       </c>
       <c r="H55" t="n">
         <v>110356</v>
@@ -2022,7 +2022,7 @@
         <v>32.625</v>
       </c>
       <c r="G57" t="n">
-        <v>29.8821392059326</v>
+        <v>29.882137298584</v>
       </c>
       <c r="H57" t="n">
         <v>29836</v>
@@ -2051,7 +2051,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G58" t="n">
-        <v>29.5844593048096</v>
+        <v>29.5844573974609</v>
       </c>
       <c r="H58" t="n">
         <v>30824</v>
@@ -2080,7 +2080,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G59" t="n">
-        <v>29.5844593048096</v>
+        <v>29.5844573974609</v>
       </c>
       <c r="H59" t="n">
         <v>32312</v>
@@ -2109,7 +2109,7 @@
         <v>32.2750015258789</v>
       </c>
       <c r="G60" t="n">
-        <v>29.5615653991699</v>
+        <v>29.5615634918213</v>
       </c>
       <c r="H60" t="n">
         <v>61764</v>
@@ -2196,7 +2196,7 @@
         <v>32.5499992370605</v>
       </c>
       <c r="G63" t="n">
-        <v>29.8134422302246</v>
+        <v>29.813440322876</v>
       </c>
       <c r="H63" t="n">
         <v>41940</v>
@@ -2254,7 +2254,7 @@
         <v>32</v>
       </c>
       <c r="G65" t="n">
-        <v>29.3096809387207</v>
+        <v>29.3096828460693</v>
       </c>
       <c r="H65" t="n">
         <v>27812</v>
@@ -2312,7 +2312,7 @@
         <v>32.2999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>29.5844593048096</v>
+        <v>29.5844573974609</v>
       </c>
       <c r="H67" t="n">
         <v>14004</v>
@@ -2370,7 +2370,7 @@
         <v>31.8250007629395</v>
       </c>
       <c r="G69" t="n">
-        <v>29.1493968963623</v>
+        <v>29.1493911743164</v>
       </c>
       <c r="H69" t="n">
         <v>41432</v>
@@ -2399,7 +2399,7 @@
         <v>31.5750007629395</v>
       </c>
       <c r="G70" t="n">
-        <v>28.9204120635986</v>
+        <v>28.9204139709473</v>
       </c>
       <c r="H70" t="n">
         <v>23728</v>
@@ -2457,7 +2457,7 @@
         <v>31.5</v>
       </c>
       <c r="G72" t="n">
-        <v>28.8517169952393</v>
+        <v>28.8517208099365</v>
       </c>
       <c r="H72" t="n">
         <v>22784</v>
@@ -2486,7 +2486,7 @@
         <v>32</v>
       </c>
       <c r="G73" t="n">
-        <v>29.3096809387207</v>
+        <v>29.3096828460693</v>
       </c>
       <c r="H73" t="n">
         <v>16564</v>
@@ -2544,7 +2544,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G75" t="n">
-        <v>28.8059215545654</v>
+        <v>28.8059234619141</v>
       </c>
       <c r="H75" t="n">
         <v>24644</v>
@@ -2602,7 +2602,7 @@
         <v>31.625</v>
       </c>
       <c r="G77" t="n">
-        <v>28.9662132263184</v>
+        <v>28.9662075042725</v>
       </c>
       <c r="H77" t="n">
         <v>62764</v>
@@ -2631,7 +2631,7 @@
         <v>31.5</v>
       </c>
       <c r="G78" t="n">
-        <v>28.8517169952393</v>
+        <v>28.8517208099365</v>
       </c>
       <c r="H78" t="n">
         <v>25480</v>
@@ -2660,7 +2660,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G79" t="n">
-        <v>29.1264972686768</v>
+        <v>29.1264953613281</v>
       </c>
       <c r="H79" t="n">
         <v>24120</v>
@@ -2689,7 +2689,7 @@
         <v>31.625</v>
       </c>
       <c r="G80" t="n">
-        <v>28.9662132263184</v>
+        <v>28.9662075042725</v>
       </c>
       <c r="H80" t="n">
         <v>15740</v>
@@ -2718,7 +2718,7 @@
         <v>30.625</v>
       </c>
       <c r="G81" t="n">
-        <v>28.0502796173096</v>
+        <v>28.0502815246582</v>
       </c>
       <c r="H81" t="n">
         <v>72140</v>
@@ -2747,7 +2747,7 @@
         <v>31.25</v>
       </c>
       <c r="G82" t="n">
-        <v>28.6227416992188</v>
+        <v>28.6227359771729</v>
       </c>
       <c r="H82" t="n">
         <v>62968</v>
@@ -2776,7 +2776,7 @@
         <v>30.875</v>
       </c>
       <c r="G83" t="n">
-        <v>28.2792587280273</v>
+        <v>28.2792644500732</v>
       </c>
       <c r="H83" t="n">
         <v>18304</v>
@@ -2805,7 +2805,7 @@
         <v>31.0750007629395</v>
       </c>
       <c r="G84" t="n">
-        <v>28.4624481201172</v>
+        <v>28.4624519348145</v>
       </c>
       <c r="H84" t="n">
         <v>19964</v>
@@ -2834,7 +2834,7 @@
         <v>31.0249996185303</v>
       </c>
       <c r="G85" t="n">
-        <v>28.4166507720947</v>
+        <v>28.416654586792</v>
       </c>
       <c r="H85" t="n">
         <v>14392</v>
@@ -2863,7 +2863,7 @@
         <v>30.5</v>
       </c>
       <c r="G86" t="n">
-        <v>27.9357891082764</v>
+        <v>27.935791015625</v>
       </c>
       <c r="H86" t="n">
         <v>9120</v>
@@ -2892,7 +2892,7 @@
         <v>31.125</v>
       </c>
       <c r="G87" t="n">
-        <v>28.508243560791</v>
+        <v>28.5082454681396</v>
       </c>
       <c r="H87" t="n">
         <v>9824</v>
@@ -2921,7 +2921,7 @@
         <v>30.8250007629395</v>
       </c>
       <c r="G88" t="n">
-        <v>28.2334690093994</v>
+        <v>28.2334671020508</v>
       </c>
       <c r="H88" t="n">
         <v>10936</v>
@@ -2950,7 +2950,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G89" t="n">
-        <v>28.027379989624</v>
+        <v>28.0273857116699</v>
       </c>
       <c r="H89" t="n">
         <v>9492</v>
@@ -3008,7 +3008,7 @@
         <v>30.5</v>
       </c>
       <c r="G91" t="n">
-        <v>28.1659069061279</v>
+        <v>28.1659049987793</v>
       </c>
       <c r="H91" t="n">
         <v>17556</v>
@@ -3037,7 +3037,7 @@
         <v>31</v>
       </c>
       <c r="G92" t="n">
-        <v>28.6276397705078</v>
+        <v>28.6276454925537</v>
       </c>
       <c r="H92" t="n">
         <v>17388</v>
@@ -3066,7 +3066,7 @@
         <v>30.5</v>
       </c>
       <c r="G93" t="n">
-        <v>28.1659069061279</v>
+        <v>28.1659049987793</v>
       </c>
       <c r="H93" t="n">
         <v>65808</v>
@@ -3095,7 +3095,7 @@
         <v>30.25</v>
       </c>
       <c r="G94" t="n">
-        <v>27.9350337982178</v>
+        <v>27.935037612915</v>
       </c>
       <c r="H94" t="n">
         <v>16408</v>
@@ -3124,7 +3124,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G95" t="n">
-        <v>28.1197357177734</v>
+        <v>28.1197319030762</v>
       </c>
       <c r="H95" t="n">
         <v>6448</v>
@@ -3211,7 +3211,7 @@
         <v>31</v>
       </c>
       <c r="G98" t="n">
-        <v>28.6276397705078</v>
+        <v>28.6276454925537</v>
       </c>
       <c r="H98" t="n">
         <v>38732</v>
@@ -3240,7 +3240,7 @@
         <v>31</v>
       </c>
       <c r="G99" t="n">
-        <v>28.6276397705078</v>
+        <v>28.6276454925537</v>
       </c>
       <c r="H99" t="n">
         <v>15560</v>
@@ -3269,7 +3269,7 @@
         <v>31.25</v>
       </c>
       <c r="G100" t="n">
-        <v>28.858512878418</v>
+        <v>28.8585071563721</v>
       </c>
       <c r="H100" t="n">
         <v>23144</v>
@@ -3327,7 +3327,7 @@
         <v>32.5750007629395</v>
       </c>
       <c r="G102" t="n">
-        <v>30.0821094512939</v>
+        <v>30.0821075439453</v>
       </c>
       <c r="H102" t="n">
         <v>19628</v>
@@ -3443,7 +3443,7 @@
         <v>32.75</v>
       </c>
       <c r="G106" t="n">
-        <v>30.2437152862549</v>
+        <v>30.2437133789062</v>
       </c>
       <c r="H106" t="n">
         <v>27380</v>
@@ -3472,7 +3472,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G107" t="n">
-        <v>30.289888381958</v>
+        <v>30.2898921966553</v>
       </c>
       <c r="H107" t="n">
         <v>23804</v>
@@ -3646,7 +3646,7 @@
         <v>32.3250007629395</v>
       </c>
       <c r="G113" t="n">
-        <v>29.8512439727783</v>
+        <v>29.8512401580811</v>
       </c>
       <c r="H113" t="n">
         <v>15280</v>
@@ -3675,7 +3675,7 @@
         <v>31.9249992370605</v>
       </c>
       <c r="G114" t="n">
-        <v>29.4818496704102</v>
+        <v>29.4818515777588</v>
       </c>
       <c r="H114" t="n">
         <v>21436</v>
@@ -3704,7 +3704,7 @@
         <v>30.5</v>
       </c>
       <c r="G115" t="n">
-        <v>28.1659069061279</v>
+        <v>28.1659049987793</v>
       </c>
       <c r="H115" t="n">
         <v>31072</v>
@@ -3733,7 +3733,7 @@
         <v>30.5</v>
       </c>
       <c r="G116" t="n">
-        <v>28.1659069061279</v>
+        <v>28.1659049987793</v>
       </c>
       <c r="H116" t="n">
         <v>43104</v>
@@ -3762,7 +3762,7 @@
         <v>30.25</v>
       </c>
       <c r="G117" t="n">
-        <v>27.9350337982178</v>
+        <v>27.935037612915</v>
       </c>
       <c r="H117" t="n">
         <v>28188</v>
@@ -3791,7 +3791,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G118" t="n">
-        <v>27.796516418457</v>
+        <v>27.7965126037598</v>
       </c>
       <c r="H118" t="n">
         <v>26056</v>
@@ -3820,7 +3820,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G119" t="n">
-        <v>28.1197357177734</v>
+        <v>28.1197319030762</v>
       </c>
       <c r="H119" t="n">
         <v>29824</v>
@@ -3849,7 +3849,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G120" t="n">
-        <v>28.9046821594238</v>
+        <v>28.9046840667725</v>
       </c>
       <c r="H120" t="n">
         <v>17656</v>
@@ -3878,7 +3878,7 @@
         <v>31.5</v>
       </c>
       <c r="G121" t="n">
-        <v>29.0893745422363</v>
+        <v>29.0893802642822</v>
       </c>
       <c r="H121" t="n">
         <v>26836</v>
@@ -3907,7 +3907,7 @@
         <v>31.25</v>
       </c>
       <c r="G122" t="n">
-        <v>28.858512878418</v>
+        <v>28.8585071563721</v>
       </c>
       <c r="H122" t="n">
         <v>33240</v>
@@ -3936,7 +3936,7 @@
         <v>31.25</v>
       </c>
       <c r="G123" t="n">
-        <v>28.858512878418</v>
+        <v>28.8585071563721</v>
       </c>
       <c r="H123" t="n">
         <v>32728</v>
@@ -4023,7 +4023,7 @@
         <v>28.625</v>
       </c>
       <c r="G126" t="n">
-        <v>26.4343967437744</v>
+        <v>26.4343948364258</v>
       </c>
       <c r="H126" t="n">
         <v>56052</v>
@@ -4052,7 +4052,7 @@
         <v>29.1749992370605</v>
       </c>
       <c r="G127" t="n">
-        <v>26.9423065185547</v>
+        <v>26.9423046112061</v>
       </c>
       <c r="H127" t="n">
         <v>57196</v>
@@ -4139,7 +4139,7 @@
         <v>28.7749996185303</v>
       </c>
       <c r="G130" t="n">
-        <v>26.5729160308838</v>
+        <v>26.5729179382324</v>
       </c>
       <c r="H130" t="n">
         <v>21048</v>
@@ -4168,7 +4168,7 @@
         <v>27.5750007629395</v>
       </c>
       <c r="G131" t="n">
-        <v>25.464750289917</v>
+        <v>25.4647464752197</v>
       </c>
       <c r="H131" t="n">
         <v>62316</v>
@@ -4226,7 +4226,7 @@
         <v>28.9500007629395</v>
       </c>
       <c r="G133" t="n">
-        <v>26.7345218658447</v>
+        <v>26.7345237731934</v>
       </c>
       <c r="H133" t="n">
         <v>17596</v>
@@ -4255,7 +4255,7 @@
         <v>29.5</v>
       </c>
       <c r="G134" t="n">
-        <v>27.2424297332764</v>
+        <v>27.2424335479736</v>
       </c>
       <c r="H134" t="n">
         <v>22452</v>
@@ -4284,7 +4284,7 @@
         <v>29.2250003814697</v>
       </c>
       <c r="G135" t="n">
-        <v>26.9884777069092</v>
+        <v>26.9884757995605</v>
       </c>
       <c r="H135" t="n">
         <v>19828</v>
@@ -4313,7 +4313,7 @@
         <v>30.2250003814697</v>
       </c>
       <c r="G136" t="n">
-        <v>27.9119491577148</v>
+        <v>27.9119510650635</v>
       </c>
       <c r="H136" t="n">
         <v>28424</v>
@@ -4371,7 +4371,7 @@
         <v>30.8500003814697</v>
       </c>
       <c r="G138" t="n">
-        <v>28.4891185760498</v>
+        <v>28.4891204833984</v>
       </c>
       <c r="H138" t="n">
         <v>18136</v>
@@ -4400,7 +4400,7 @@
         <v>30.1000003814697</v>
       </c>
       <c r="G139" t="n">
-        <v>27.796516418457</v>
+        <v>27.7965126037598</v>
       </c>
       <c r="H139" t="n">
         <v>22224</v>
@@ -4429,7 +4429,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G140" t="n">
-        <v>28.3506011962891</v>
+        <v>28.3505992889404</v>
       </c>
       <c r="H140" t="n">
         <v>14056</v>
@@ -4458,7 +4458,7 @@
         <v>30.375</v>
       </c>
       <c r="G141" t="n">
-        <v>28.0504722595215</v>
+        <v>28.0504703521729</v>
       </c>
       <c r="H141" t="n">
         <v>16340</v>
@@ -4516,7 +4516,7 @@
         <v>30.875</v>
       </c>
       <c r="G143" t="n">
-        <v>28.51220703125</v>
+        <v>28.5122089385986</v>
       </c>
       <c r="H143" t="n">
         <v>24020</v>
@@ -4603,7 +4603,7 @@
         <v>31.4500007629395</v>
       </c>
       <c r="G146" t="n">
-        <v>29.0432052612305</v>
+        <v>29.0432014465332</v>
       </c>
       <c r="H146" t="n">
         <v>6416</v>
@@ -4632,7 +4632,7 @@
         <v>31.875</v>
       </c>
       <c r="G147" t="n">
-        <v>29.4356784820557</v>
+        <v>29.4356842041016</v>
       </c>
       <c r="H147" t="n">
         <v>27280</v>
@@ -4777,7 +4777,7 @@
         <v>30.6749992370605</v>
       </c>
       <c r="G152" t="n">
-        <v>28.3275127410889</v>
+        <v>28.3275108337402</v>
       </c>
       <c r="H152" t="n">
         <v>25436</v>
@@ -4806,7 +4806,7 @@
         <v>31.125</v>
       </c>
       <c r="G153" t="n">
-        <v>28.7430725097656</v>
+        <v>28.7430744171143</v>
       </c>
       <c r="H153" t="n">
         <v>21304</v>
@@ -4864,7 +4864,7 @@
         <v>30.8999996185303</v>
       </c>
       <c r="G155" t="n">
-        <v>28.5352935791016</v>
+        <v>28.5352954864502</v>
       </c>
       <c r="H155" t="n">
         <v>29428</v>
@@ -4893,7 +4893,7 @@
         <v>30.875</v>
       </c>
       <c r="G156" t="n">
-        <v>28.51220703125</v>
+        <v>28.5122089385986</v>
       </c>
       <c r="H156" t="n">
         <v>35212</v>
@@ -4922,7 +4922,7 @@
         <v>30.4249992370605</v>
       </c>
       <c r="G157" t="n">
-        <v>28.0966453552246</v>
+        <v>28.096643447876</v>
       </c>
       <c r="H157" t="n">
         <v>15536</v>
@@ -4980,7 +4980,7 @@
         <v>30.4500007629395</v>
       </c>
       <c r="G159" t="n">
-        <v>28.1197357177734</v>
+        <v>28.1197319030762</v>
       </c>
       <c r="H159" t="n">
         <v>4772</v>
@@ -5009,7 +5009,7 @@
         <v>29.875</v>
       </c>
       <c r="G160" t="n">
-        <v>27.5887336730957</v>
+        <v>27.588737487793</v>
       </c>
       <c r="H160" t="n">
         <v>34784</v>
@@ -5096,7 +5096,7 @@
         <v>29.125</v>
       </c>
       <c r="G163" t="n">
-        <v>26.8961296081543</v>
+        <v>26.8961315155029</v>
       </c>
       <c r="H163" t="n">
         <v>34800</v>
@@ -5183,7 +5183,7 @@
         <v>28.7250003814697</v>
       </c>
       <c r="G166" t="n">
-        <v>26.5267448425293</v>
+        <v>26.526741027832</v>
       </c>
       <c r="H166" t="n">
         <v>44404</v>
@@ -5270,7 +5270,7 @@
         <v>27.9249992370605</v>
       </c>
       <c r="G169" t="n">
-        <v>25.7879638671875</v>
+        <v>25.7879657745361</v>
       </c>
       <c r="H169" t="n">
         <v>55264</v>
@@ -5328,7 +5328,7 @@
         <v>27.6499996185303</v>
       </c>
       <c r="G171" t="n">
-        <v>25.534008026123</v>
+        <v>25.5340061187744</v>
       </c>
       <c r="H171" t="n">
         <v>54156</v>
@@ -5357,7 +5357,7 @@
         <v>28.5750007629395</v>
       </c>
       <c r="G172" t="n">
-        <v>26.3882217407227</v>
+        <v>26.388219833374</v>
       </c>
       <c r="H172" t="n">
         <v>70020</v>
@@ -5386,7 +5386,7 @@
         <v>28.7749996185303</v>
       </c>
       <c r="G173" t="n">
-        <v>26.5729160308838</v>
+        <v>26.5729179382324</v>
       </c>
       <c r="H173" t="n">
         <v>19176</v>
@@ -5415,7 +5415,7 @@
         <v>29.2250003814697</v>
       </c>
       <c r="G174" t="n">
-        <v>26.9884777069092</v>
+        <v>26.9884757995605</v>
       </c>
       <c r="H174" t="n">
         <v>18588</v>
@@ -5444,7 +5444,7 @@
         <v>29.5</v>
       </c>
       <c r="G175" t="n">
-        <v>27.2424297332764</v>
+        <v>27.2424335479736</v>
       </c>
       <c r="H175" t="n">
         <v>37752</v>
@@ -5473,7 +5473,7 @@
         <v>29.8500003814697</v>
       </c>
       <c r="G176" t="n">
-        <v>27.5656490325928</v>
+        <v>27.5656471252441</v>
       </c>
       <c r="H176" t="n">
         <v>45400</v>
@@ -5531,7 +5531,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>27.427131652832</v>
+        <v>27.4271278381348</v>
       </c>
       <c r="H178" t="n">
         <v>18488</v>
@@ -5647,7 +5647,7 @@
         <v>29.75</v>
       </c>
       <c r="G182" t="n">
-        <v>27.4733028411865</v>
+        <v>27.4733009338379</v>
       </c>
       <c r="H182" t="n">
         <v>12348</v>
@@ -5676,7 +5676,7 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G183" t="n">
-        <v>27.1962585449219</v>
+        <v>27.1962604522705</v>
       </c>
       <c r="H183" t="n">
         <v>23880</v>
@@ -5705,7 +5705,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G184" t="n">
-        <v>27.3347816467285</v>
+        <v>27.3347797393799</v>
       </c>
       <c r="H184" t="n">
         <v>6104</v>
@@ -5734,7 +5734,7 @@
         <v>29.75</v>
       </c>
       <c r="G185" t="n">
-        <v>27.4733028411865</v>
+        <v>27.4733009338379</v>
       </c>
       <c r="H185" t="n">
         <v>17012</v>
@@ -5763,7 +5763,7 @@
         <v>29.625</v>
       </c>
       <c r="G186" t="n">
-        <v>27.3578662872314</v>
+        <v>27.3578624725342</v>
       </c>
       <c r="H186" t="n">
         <v>11696</v>
@@ -5821,7 +5821,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G188" t="n">
-        <v>27.427131652832</v>
+        <v>27.4271278381348</v>
       </c>
       <c r="H188" t="n">
         <v>4828</v>
@@ -5850,7 +5850,7 @@
         <v>29.625</v>
       </c>
       <c r="G189" t="n">
-        <v>27.3578662872314</v>
+        <v>27.3578624725342</v>
       </c>
       <c r="H189" t="n">
         <v>6180</v>
@@ -5879,7 +5879,7 @@
         <v>29.75</v>
       </c>
       <c r="G190" t="n">
-        <v>27.4733028411865</v>
+        <v>27.4733009338379</v>
       </c>
       <c r="H190" t="n">
         <v>5060</v>
@@ -5937,7 +5937,7 @@
         <v>29.6749992370605</v>
       </c>
       <c r="G192" t="n">
-        <v>27.4040374755859</v>
+        <v>27.4040393829346</v>
       </c>
       <c r="H192" t="n">
         <v>39328</v>
@@ -6024,7 +6024,7 @@
         <v>30.375</v>
       </c>
       <c r="G195" t="n">
-        <v>28.0504722595215</v>
+        <v>28.0504703521729</v>
       </c>
       <c r="H195" t="n">
         <v>210380</v>
@@ -6053,7 +6053,7 @@
         <v>30.5</v>
       </c>
       <c r="G196" t="n">
-        <v>28.1659069061279</v>
+        <v>28.1659049987793</v>
       </c>
       <c r="H196" t="n">
         <v>26132</v>
@@ -6082,7 +6082,7 @@
         <v>30.875</v>
       </c>
       <c r="G197" t="n">
-        <v>28.51220703125</v>
+        <v>28.5122089385986</v>
       </c>
       <c r="H197" t="n">
         <v>32136</v>
@@ -6111,7 +6111,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G198" t="n">
-        <v>28.7199878692627</v>
+        <v>28.7199897766113</v>
       </c>
       <c r="H198" t="n">
         <v>36816</v>
@@ -6169,7 +6169,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G200" t="n">
-        <v>28.2582492828369</v>
+        <v>28.2582511901855</v>
       </c>
       <c r="H200" t="n">
         <v>7168</v>
@@ -6256,7 +6256,7 @@
         <v>28.9249992370605</v>
       </c>
       <c r="G203" t="n">
-        <v>26.7114315032959</v>
+        <v>26.7114353179932</v>
       </c>
       <c r="H203" t="n">
         <v>49608</v>
@@ -6314,7 +6314,7 @@
         <v>28.7749996185303</v>
       </c>
       <c r="G205" t="n">
-        <v>26.5729160308838</v>
+        <v>26.5729179382324</v>
       </c>
       <c r="H205" t="n">
         <v>27756</v>
@@ -6372,7 +6372,7 @@
         <v>29.5</v>
       </c>
       <c r="G207" t="n">
-        <v>27.2424297332764</v>
+        <v>27.2424335479736</v>
       </c>
       <c r="H207" t="n">
         <v>38608</v>
@@ -6401,7 +6401,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G208" t="n">
-        <v>27.3347816467285</v>
+        <v>27.3347797393799</v>
       </c>
       <c r="H208" t="n">
         <v>18384</v>
@@ -6430,7 +6430,7 @@
         <v>28.7749996185303</v>
       </c>
       <c r="G209" t="n">
-        <v>26.5729160308838</v>
+        <v>26.5729179382324</v>
       </c>
       <c r="H209" t="n">
         <v>37716</v>
@@ -6488,7 +6488,7 @@
         <v>29.0750007629395</v>
       </c>
       <c r="G211" t="n">
-        <v>26.8499565124512</v>
+        <v>26.8499584197998</v>
       </c>
       <c r="H211" t="n">
         <v>23236</v>
@@ -6546,7 +6546,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G213" t="n">
-        <v>26.457483291626</v>
+        <v>26.4574794769287</v>
       </c>
       <c r="H213" t="n">
         <v>23092</v>
@@ -6575,7 +6575,7 @@
         <v>28.625</v>
       </c>
       <c r="G214" t="n">
-        <v>26.4343967437744</v>
+        <v>26.4343948364258</v>
       </c>
       <c r="H214" t="n">
         <v>3472</v>
@@ -6604,7 +6604,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G215" t="n">
-        <v>26.2727890014648</v>
+        <v>26.2727870941162</v>
       </c>
       <c r="H215" t="n">
         <v>7840</v>
@@ -6691,7 +6691,7 @@
         <v>28.3250007629395</v>
       </c>
       <c r="G218" t="n">
-        <v>26.1573524475098</v>
+        <v>26.1573505401611</v>
       </c>
       <c r="H218" t="n">
         <v>24992</v>
@@ -6749,7 +6749,7 @@
         <v>28.5750007629395</v>
       </c>
       <c r="G220" t="n">
-        <v>26.3882217407227</v>
+        <v>26.388219833374</v>
       </c>
       <c r="H220" t="n">
         <v>12940</v>
@@ -6836,7 +6836,7 @@
         <v>28.125</v>
       </c>
       <c r="G223" t="n">
-        <v>25.97265625</v>
+        <v>25.9726581573486</v>
       </c>
       <c r="H223" t="n">
         <v>16636</v>
@@ -6865,7 +6865,7 @@
         <v>27.5</v>
       </c>
       <c r="G224" t="n">
-        <v>25.3954906463623</v>
+        <v>25.3954887390137</v>
       </c>
       <c r="H224" t="n">
         <v>37892</v>
@@ -6952,7 +6952,7 @@
         <v>26.4500007629395</v>
       </c>
       <c r="G227" t="n">
-        <v>24.4258422851562</v>
+        <v>24.4258460998535</v>
       </c>
       <c r="H227" t="n">
         <v>22812</v>
@@ -6981,7 +6981,7 @@
         <v>26.5750007629395</v>
       </c>
       <c r="G228" t="n">
-        <v>24.5412788391113</v>
+        <v>24.5412769317627</v>
       </c>
       <c r="H228" t="n">
         <v>21212</v>
@@ -7039,7 +7039,7 @@
         <v>26.75</v>
       </c>
       <c r="G230" t="n">
-        <v>24.7028846740723</v>
+        <v>24.7028827667236</v>
       </c>
       <c r="H230" t="n">
         <v>37924</v>
@@ -7155,7 +7155,7 @@
         <v>26.875</v>
       </c>
       <c r="G234" t="n">
-        <v>24.8183174133301</v>
+        <v>24.8183193206787</v>
       </c>
       <c r="H234" t="n">
         <v>18892</v>
@@ -7242,7 +7242,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>24.7490577697754</v>
+        <v>24.7490558624268</v>
       </c>
       <c r="H237" t="n">
         <v>30104</v>
@@ -7271,7 +7271,7 @@
         <v>26.625</v>
       </c>
       <c r="G238" t="n">
-        <v>24.5874500274658</v>
+        <v>24.5874481201172</v>
       </c>
       <c r="H238" t="n">
         <v>22712</v>
@@ -7300,7 +7300,7 @@
         <v>26.7749996185303</v>
       </c>
       <c r="G239" t="n">
-        <v>24.7259693145752</v>
+        <v>24.7259731292725</v>
       </c>
       <c r="H239" t="n">
         <v>37876</v>
@@ -7358,7 +7358,7 @@
         <v>27.9750003814697</v>
       </c>
       <c r="G241" t="n">
-        <v>25.8341369628906</v>
+        <v>25.834135055542</v>
       </c>
       <c r="H241" t="n">
         <v>20604</v>
@@ -7387,7 +7387,7 @@
         <v>27.9500007629395</v>
       </c>
       <c r="G242" t="n">
-        <v>25.8110504150391</v>
+        <v>25.8110523223877</v>
       </c>
       <c r="H242" t="n">
         <v>29700</v>
@@ -7416,7 +7416,7 @@
         <v>28.7250003814697</v>
       </c>
       <c r="G243" t="n">
-        <v>26.5267448425293</v>
+        <v>26.526741027832</v>
       </c>
       <c r="H243" t="n">
         <v>19252</v>
@@ -7445,7 +7445,7 @@
         <v>28.4500007629395</v>
       </c>
       <c r="G244" t="n">
-        <v>26.2727890014648</v>
+        <v>26.2727870941162</v>
       </c>
       <c r="H244" t="n">
         <v>32828</v>
@@ -7474,7 +7474,7 @@
         <v>28.6499996185303</v>
       </c>
       <c r="G245" t="n">
-        <v>26.457483291626</v>
+        <v>26.4574794769287</v>
       </c>
       <c r="H245" t="n">
         <v>14712</v>
@@ -7532,7 +7532,7 @@
         <v>29.5</v>
       </c>
       <c r="G247" t="n">
-        <v>27.2424297332764</v>
+        <v>27.2424335479736</v>
       </c>
       <c r="H247" t="n">
         <v>30260</v>
@@ -7561,7 +7561,7 @@
         <v>29.7250003814697</v>
       </c>
       <c r="G248" t="n">
-        <v>27.4502143859863</v>
+        <v>27.4502105712891</v>
       </c>
       <c r="H248" t="n">
         <v>12224</v>
@@ -7590,7 +7590,7 @@
         <v>29.75</v>
       </c>
       <c r="G249" t="n">
-        <v>27.4733028411865</v>
+        <v>27.4733009338379</v>
       </c>
       <c r="H249" t="n">
         <v>33392</v>
@@ -7619,7 +7619,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>27.427131652832</v>
+        <v>27.4271278381348</v>
       </c>
       <c r="H250" t="n">
         <v>26396</v>
@@ -7648,7 +7648,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G251" t="n">
-        <v>27.427131652832</v>
+        <v>27.4271278381348</v>
       </c>
       <c r="H251" t="n">
         <v>24440</v>
@@ -7677,7 +7677,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G252" t="n">
-        <v>27.3347816467285</v>
+        <v>27.3347797393799</v>
       </c>
       <c r="H252" t="n">
         <v>17184</v>
@@ -7764,7 +7764,7 @@
         <v>29.8250007629395</v>
       </c>
       <c r="G255" t="n">
-        <v>27.5425605773926</v>
+        <v>27.5425624847412</v>
       </c>
       <c r="H255" t="n">
         <v>16232</v>
@@ -7793,7 +7793,7 @@
         <v>29.3250007629395</v>
       </c>
       <c r="G256" t="n">
-        <v>27.0808277130127</v>
+        <v>27.0808258056641</v>
       </c>
       <c r="H256" t="n">
         <v>32096</v>
@@ -7822,7 +7822,7 @@
         <v>29.5</v>
       </c>
       <c r="G257" t="n">
-        <v>27.2424297332764</v>
+        <v>27.2424335479736</v>
       </c>
       <c r="H257" t="n">
         <v>12068</v>
@@ -7851,7 +7851,7 @@
         <v>29.6749992370605</v>
       </c>
       <c r="G258" t="n">
-        <v>27.4040374755859</v>
+        <v>27.4040393829346</v>
       </c>
       <c r="H258" t="n">
         <v>10948</v>
@@ -7880,7 +7880,7 @@
         <v>29.75</v>
       </c>
       <c r="G259" t="n">
-        <v>27.4733028411865</v>
+        <v>27.4733009338379</v>
       </c>
       <c r="H259" t="n">
         <v>28512</v>
@@ -7909,7 +7909,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G260" t="n">
-        <v>27.6118202209473</v>
+        <v>27.6118221282959</v>
       </c>
       <c r="H260" t="n">
         <v>19236</v>
@@ -7938,7 +7938,7 @@
         <v>29.625</v>
       </c>
       <c r="G261" t="n">
-        <v>27.3578662872314</v>
+        <v>27.3578624725342</v>
       </c>
       <c r="H261" t="n">
         <v>6240</v>
@@ -7967,7 +7967,7 @@
         <v>29.7250003814697</v>
       </c>
       <c r="G262" t="n">
-        <v>27.4502143859863</v>
+        <v>27.4502105712891</v>
       </c>
       <c r="H262" t="n">
         <v>18008</v>
@@ -8054,7 +8054,7 @@
         <v>29.125</v>
       </c>
       <c r="G265" t="n">
-        <v>26.8961296081543</v>
+        <v>26.8961315155029</v>
       </c>
       <c r="H265" t="n">
         <v>9128</v>
@@ -8141,7 +8141,7 @@
         <v>29.75</v>
       </c>
       <c r="G268" t="n">
-        <v>27.4733028411865</v>
+        <v>27.4733009338379</v>
       </c>
       <c r="H268" t="n">
         <v>9340</v>
@@ -8199,7 +8199,7 @@
         <v>29.8999996185303</v>
       </c>
       <c r="G270" t="n">
-        <v>27.6118202209473</v>
+        <v>27.6118221282959</v>
       </c>
       <c r="H270" t="n">
         <v>17912</v>
@@ -8257,7 +8257,7 @@
         <v>30.5</v>
       </c>
       <c r="G272" t="n">
-        <v>28.1659069061279</v>
+        <v>28.1659049987793</v>
       </c>
       <c r="H272" t="n">
         <v>40464</v>
@@ -8344,7 +8344,7 @@
         <v>29.6749992370605</v>
       </c>
       <c r="G275" t="n">
-        <v>27.4040374755859</v>
+        <v>27.4040393829346</v>
       </c>
       <c r="H275" t="n">
         <v>36204</v>
@@ -8373,7 +8373,7 @@
         <v>29.75</v>
       </c>
       <c r="G276" t="n">
-        <v>27.4733028411865</v>
+        <v>27.4733009338379</v>
       </c>
       <c r="H276" t="n">
         <v>67380</v>
@@ -8431,7 +8431,7 @@
         <v>29.75</v>
       </c>
       <c r="G278" t="n">
-        <v>27.4733028411865</v>
+        <v>27.4733009338379</v>
       </c>
       <c r="H278" t="n">
         <v>9428</v>
@@ -8460,7 +8460,7 @@
         <v>29.75</v>
       </c>
       <c r="G279" t="n">
-        <v>27.4733028411865</v>
+        <v>27.4733009338379</v>
       </c>
       <c r="H279" t="n">
         <v>39264</v>
@@ -8489,7 +8489,7 @@
         <v>30.4249992370605</v>
       </c>
       <c r="G280" t="n">
-        <v>28.0966453552246</v>
+        <v>28.096643447876</v>
       </c>
       <c r="H280" t="n">
         <v>38688</v>
@@ -8547,7 +8547,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>28.8123378753662</v>
+        <v>28.8123340606689</v>
       </c>
       <c r="H282" t="n">
         <v>44304</v>
@@ -8576,7 +8576,7 @@
         <v>31.3250007629395</v>
       </c>
       <c r="G283" t="n">
-        <v>28.9277687072754</v>
+        <v>28.927770614624</v>
       </c>
       <c r="H283" t="n">
         <v>72412</v>
@@ -8605,7 +8605,7 @@
         <v>30.25</v>
       </c>
       <c r="G284" t="n">
-        <v>27.9350337982178</v>
+        <v>27.935037612915</v>
       </c>
       <c r="H284" t="n">
         <v>110904</v>
@@ -8634,7 +8634,7 @@
         <v>30.8250007629395</v>
       </c>
       <c r="G285" t="n">
-        <v>28.4660339355469</v>
+        <v>28.4660358428955</v>
       </c>
       <c r="H285" t="n">
         <v>24384</v>
@@ -8663,7 +8663,7 @@
         <v>30.2749996185303</v>
       </c>
       <c r="G286" t="n">
-        <v>27.958122253418</v>
+        <v>27.9581203460693</v>
       </c>
       <c r="H286" t="n">
         <v>27908</v>
@@ -8692,7 +8692,7 @@
         <v>29.875</v>
       </c>
       <c r="G287" t="n">
-        <v>27.5887336730957</v>
+        <v>27.588737487793</v>
       </c>
       <c r="H287" t="n">
         <v>17416</v>
@@ -8721,7 +8721,7 @@
         <v>30.25</v>
       </c>
       <c r="G288" t="n">
-        <v>27.9350337982178</v>
+        <v>27.935037612915</v>
       </c>
       <c r="H288" t="n">
         <v>49420</v>
@@ -8750,7 +8750,7 @@
         <v>30.5499992370605</v>
       </c>
       <c r="G289" t="n">
-        <v>28.2120780944824</v>
+        <v>28.2120800018311</v>
       </c>
       <c r="H289" t="n">
         <v>18152</v>
@@ -8779,7 +8779,7 @@
         <v>30.7000007629395</v>
       </c>
       <c r="G290" t="n">
-        <v>28.3506011962891</v>
+        <v>28.3505992889404</v>
       </c>
       <c r="H290" t="n">
         <v>26440</v>
@@ -8808,7 +8808,7 @@
         <v>31.25</v>
       </c>
       <c r="G291" t="n">
-        <v>28.858512878418</v>
+        <v>28.8585071563721</v>
       </c>
       <c r="H291" t="n">
         <v>30000</v>
@@ -8837,7 +8837,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>28.9046821594238</v>
+        <v>28.9046840667725</v>
       </c>
       <c r="H292" t="n">
         <v>19208</v>
@@ -8866,7 +8866,7 @@
         <v>31.4750003814697</v>
       </c>
       <c r="G293" t="n">
-        <v>29.0662899017334</v>
+        <v>29.066291809082</v>
       </c>
       <c r="H293" t="n">
         <v>16636</v>
@@ -8953,7 +8953,7 @@
         <v>31.2999992370605</v>
       </c>
       <c r="G296" t="n">
-        <v>28.9046821594238</v>
+        <v>28.9046840667725</v>
       </c>
       <c r="H296" t="n">
         <v>20128</v>
@@ -8982,7 +8982,7 @@
         <v>31.4750003814697</v>
       </c>
       <c r="G297" t="n">
-        <v>29.0662899017334</v>
+        <v>29.066291809082</v>
       </c>
       <c r="H297" t="n">
         <v>16848</v>
@@ -9011,7 +9011,7 @@
         <v>31.25</v>
       </c>
       <c r="G298" t="n">
-        <v>28.858512878418</v>
+        <v>28.8585071563721</v>
       </c>
       <c r="H298" t="n">
         <v>14548</v>
@@ -9040,7 +9040,7 @@
         <v>31.4249992370605</v>
       </c>
       <c r="G299" t="n">
-        <v>29.0201187133789</v>
+        <v>29.0201168060303</v>
       </c>
       <c r="H299" t="n">
         <v>7580</v>
@@ -9098,7 +9098,7 @@
         <v>31.875</v>
       </c>
       <c r="G301" t="n">
-        <v>29.4356784820557</v>
+        <v>29.4356842041016</v>
       </c>
       <c r="H301" t="n">
         <v>21576</v>
@@ -9185,7 +9185,7 @@
         <v>32.3250007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>29.8512439727783</v>
+        <v>29.8512401580811</v>
       </c>
       <c r="H304" t="n">
         <v>48500</v>
@@ -9214,7 +9214,7 @@
         <v>32.9249992370605</v>
       </c>
       <c r="G305" t="n">
-        <v>30.4053268432617</v>
+        <v>30.4053230285645</v>
       </c>
       <c r="H305" t="n">
         <v>37416</v>
@@ -9243,7 +9243,7 @@
         <v>33.0999984741211</v>
       </c>
       <c r="G306" t="n">
-        <v>30.5669326782227</v>
+        <v>30.5669288635254</v>
       </c>
       <c r="H306" t="n">
         <v>27072</v>
@@ -9272,7 +9272,7 @@
         <v>33.625</v>
       </c>
       <c r="G307" t="n">
-        <v>31.0517597198486</v>
+        <v>31.0517520904541</v>
       </c>
       <c r="H307" t="n">
         <v>61192</v>
@@ -9301,7 +9301,7 @@
         <v>33.375</v>
       </c>
       <c r="G308" t="n">
-        <v>30.8208866119385</v>
+        <v>30.8208904266357</v>
       </c>
       <c r="H308" t="n">
         <v>30908</v>
@@ -9330,7 +9330,7 @@
         <v>33.375</v>
       </c>
       <c r="G309" t="n">
-        <v>30.8208866119385</v>
+        <v>30.8208904266357</v>
       </c>
       <c r="H309" t="n">
         <v>37956</v>
@@ -9359,7 +9359,7 @@
         <v>33.5</v>
       </c>
       <c r="G310" t="n">
-        <v>30.9363250732422</v>
+        <v>30.9363231658936</v>
       </c>
       <c r="H310" t="n">
         <v>53256</v>
@@ -9388,7 +9388,7 @@
         <v>33.5</v>
       </c>
       <c r="G311" t="n">
-        <v>30.9363250732422</v>
+        <v>30.9363231658936</v>
       </c>
       <c r="H311" t="n">
         <v>43320</v>
@@ -9417,7 +9417,7 @@
         <v>33.25</v>
       </c>
       <c r="G312" t="n">
-        <v>30.7054538726807</v>
+        <v>30.7054500579834</v>
       </c>
       <c r="H312" t="n">
         <v>65200</v>
@@ -9446,7 +9446,7 @@
         <v>33.5</v>
       </c>
       <c r="G313" t="n">
-        <v>30.9363250732422</v>
+        <v>30.9363231658936</v>
       </c>
       <c r="H313" t="n">
         <v>57636</v>
@@ -9475,7 +9475,7 @@
         <v>34.375</v>
       </c>
       <c r="G314" t="n">
-        <v>31.7443580627441</v>
+        <v>31.7443695068359</v>
       </c>
       <c r="H314" t="n">
         <v>88688</v>
@@ -9533,7 +9533,7 @@
         <v>35.5250015258789</v>
       </c>
       <c r="G316" t="n">
-        <v>32.8063507080078</v>
+        <v>32.8063545227051</v>
       </c>
       <c r="H316" t="n">
         <v>102988</v>
@@ -9591,7 +9591,7 @@
         <v>37</v>
       </c>
       <c r="G318" t="n">
-        <v>34.1684799194336</v>
+        <v>34.1684761047363</v>
       </c>
       <c r="H318" t="n">
         <v>134332</v>
@@ -9620,7 +9620,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G319" t="n">
-        <v>33.9837799072266</v>
+        <v>33.9837875366211</v>
       </c>
       <c r="H319" t="n">
         <v>52540</v>
@@ -9649,7 +9649,7 @@
         <v>37</v>
       </c>
       <c r="G320" t="n">
-        <v>34.1684799194336</v>
+        <v>34.1684761047363</v>
       </c>
       <c r="H320" t="n">
         <v>74136</v>
@@ -9678,7 +9678,7 @@
         <v>37.0999984741211</v>
       </c>
       <c r="G321" t="n">
-        <v>34.2608261108398</v>
+        <v>34.2608184814453</v>
       </c>
       <c r="H321" t="n">
         <v>50024</v>
@@ -9707,7 +9707,7 @@
         <v>37.0250015258789</v>
       </c>
       <c r="G322" t="n">
-        <v>34.1915626525879</v>
+        <v>34.1915664672852</v>
       </c>
       <c r="H322" t="n">
         <v>39704</v>
@@ -9794,7 +9794,7 @@
         <v>36.5</v>
       </c>
       <c r="G325" t="n">
-        <v>33.7067375183105</v>
+        <v>33.7067413330078</v>
       </c>
       <c r="H325" t="n">
         <v>83652</v>
@@ -9823,7 +9823,7 @@
         <v>37.125</v>
       </c>
       <c r="G326" t="n">
-        <v>34.2839126586914</v>
+        <v>34.2839088439941</v>
       </c>
       <c r="H326" t="n">
         <v>52208</v>
@@ -9852,7 +9852,7 @@
         <v>37.25</v>
       </c>
       <c r="G327" t="n">
-        <v>34.399341583252</v>
+        <v>34.3993492126465</v>
       </c>
       <c r="H327" t="n">
         <v>35132</v>
@@ -9910,7 +9910,7 @@
         <v>36.75</v>
       </c>
       <c r="G329" t="n">
-        <v>33.9376068115234</v>
+        <v>33.9376029968262</v>
       </c>
       <c r="H329" t="n">
         <v>52148</v>
@@ -9939,7 +9939,7 @@
         <v>36.75</v>
       </c>
       <c r="G330" t="n">
-        <v>33.9376068115234</v>
+        <v>33.9376029968262</v>
       </c>
       <c r="H330" t="n">
         <v>70924</v>
@@ -9968,7 +9968,7 @@
         <v>36.75</v>
       </c>
       <c r="G331" t="n">
-        <v>33.9376068115234</v>
+        <v>33.9376029968262</v>
       </c>
       <c r="H331" t="n">
         <v>44596</v>
@@ -9997,7 +9997,7 @@
         <v>36.5</v>
       </c>
       <c r="G332" t="n">
-        <v>33.7067375183105</v>
+        <v>33.7067413330078</v>
       </c>
       <c r="H332" t="n">
         <v>43064</v>
@@ -10026,7 +10026,7 @@
         <v>37</v>
       </c>
       <c r="G333" t="n">
-        <v>34.1684799194336</v>
+        <v>34.1684761047363</v>
       </c>
       <c r="H333" t="n">
         <v>70420</v>
@@ -10142,7 +10142,7 @@
         <v>37.875</v>
       </c>
       <c r="G337" t="n">
-        <v>34.9765167236328</v>
+        <v>34.9765205383301</v>
       </c>
       <c r="H337" t="n">
         <v>30416</v>
@@ -10171,7 +10171,7 @@
         <v>38.2249984741211</v>
       </c>
       <c r="G338" t="n">
-        <v>35.2997245788574</v>
+        <v>35.299732208252</v>
       </c>
       <c r="H338" t="n">
         <v>40252</v>
@@ -10229,7 +10229,7 @@
         <v>40.2249984741211</v>
       </c>
       <c r="G340" t="n">
-        <v>37.146671295166</v>
+        <v>37.1466751098633</v>
       </c>
       <c r="H340" t="n">
         <v>73716</v>
@@ -10258,7 +10258,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G341" t="n">
-        <v>37.3544578552246</v>
+        <v>37.3544616699219</v>
       </c>
       <c r="H341" t="n">
         <v>83280</v>
@@ -10374,7 +10374,7 @@
         <v>39.875</v>
       </c>
       <c r="G345" t="n">
-        <v>37.0888786315918</v>
+        <v>37.0888710021973</v>
       </c>
       <c r="H345" t="n">
         <v>38932</v>
@@ -10461,7 +10461,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G348" t="n">
-        <v>37.3911628723145</v>
+        <v>37.3911666870117</v>
       </c>
       <c r="H348" t="n">
         <v>31408</v>
@@ -10490,7 +10490,7 @@
         <v>40.5</v>
       </c>
       <c r="G349" t="n">
-        <v>37.6702003479004</v>
+        <v>37.6702041625977</v>
       </c>
       <c r="H349" t="n">
         <v>82148</v>
@@ -10548,7 +10548,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G351" t="n">
-        <v>37.6236991882324</v>
+        <v>37.6237030029297</v>
       </c>
       <c r="H351" t="n">
         <v>50056</v>
@@ -10577,7 +10577,7 @@
         <v>39.75</v>
       </c>
       <c r="G352" t="n">
-        <v>36.9726028442383</v>
+        <v>36.9726104736328</v>
       </c>
       <c r="H352" t="n">
         <v>78224</v>
@@ -10635,7 +10635,7 @@
         <v>41.375</v>
       </c>
       <c r="G354" t="n">
-        <v>38.4840660095215</v>
+        <v>38.4840621948242</v>
       </c>
       <c r="H354" t="n">
         <v>83808</v>
@@ -10664,7 +10664,7 @@
         <v>42.5</v>
       </c>
       <c r="G355" t="n">
-        <v>39.5304565429688</v>
+        <v>39.530460357666</v>
       </c>
       <c r="H355" t="n">
         <v>110732</v>
@@ -10693,7 +10693,7 @@
         <v>42.4749984741211</v>
       </c>
       <c r="G356" t="n">
-        <v>39.5072021484375</v>
+        <v>39.5071983337402</v>
       </c>
       <c r="H356" t="n">
         <v>46588</v>
@@ -10722,7 +10722,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G357" t="n">
-        <v>39.2514228820801</v>
+        <v>39.2514266967773</v>
       </c>
       <c r="H357" t="n">
         <v>53972</v>
@@ -10751,7 +10751,7 @@
         <v>43.7249984741211</v>
       </c>
       <c r="G358" t="n">
-        <v>40.669864654541</v>
+        <v>40.6698684692383</v>
       </c>
       <c r="H358" t="n">
         <v>80208</v>
@@ -10780,7 +10780,7 @@
         <v>43.5</v>
       </c>
       <c r="G359" t="n">
-        <v>40.4605941772461</v>
+        <v>40.4605865478516</v>
       </c>
       <c r="H359" t="n">
         <v>63732</v>
@@ -10838,7 +10838,7 @@
         <v>44.2249984741211</v>
       </c>
       <c r="G361" t="n">
-        <v>41.1349334716797</v>
+        <v>41.1349258422852</v>
       </c>
       <c r="H361" t="n">
         <v>67756</v>
@@ -10896,7 +10896,7 @@
         <v>44.3250007629395</v>
       </c>
       <c r="G363" t="n">
-        <v>41.2279434204102</v>
+        <v>41.2279472351074</v>
       </c>
       <c r="H363" t="n">
         <v>52256</v>
@@ -10954,7 +10954,7 @@
         <v>44.7249984741211</v>
       </c>
       <c r="G365" t="n">
-        <v>41.5999946594238</v>
+        <v>41.5999908447266</v>
       </c>
       <c r="H365" t="n">
         <v>26520</v>
@@ -11012,7 +11012,7 @@
         <v>44.3250007629395</v>
       </c>
       <c r="G367" t="n">
-        <v>41.2279434204102</v>
+        <v>41.2279472351074</v>
       </c>
       <c r="H367" t="n">
         <v>43756</v>
@@ -11041,7 +11041,7 @@
         <v>44.8250007629395</v>
       </c>
       <c r="G368" t="n">
-        <v>41.6930122375488</v>
+        <v>41.6930084228516</v>
       </c>
       <c r="H368" t="n">
         <v>75316</v>
@@ -11070,7 +11070,7 @@
         <v>44.3499984741211</v>
       </c>
       <c r="G369" t="n">
-        <v>41.2511978149414</v>
+        <v>41.2511940002441</v>
       </c>
       <c r="H369" t="n">
         <v>44952</v>
@@ -11128,7 +11128,7 @@
         <v>42.2000007629395</v>
       </c>
       <c r="G371" t="n">
-        <v>39.2514228820801</v>
+        <v>39.2514266967773</v>
       </c>
       <c r="H371" t="n">
         <v>110688</v>
@@ -11157,7 +11157,7 @@
         <v>41.9749984741211</v>
       </c>
       <c r="G372" t="n">
-        <v>39.0421371459961</v>
+        <v>39.0421409606934</v>
       </c>
       <c r="H372" t="n">
         <v>61776</v>
@@ -11215,7 +11215,7 @@
         <v>41.3499984741211</v>
       </c>
       <c r="G374" t="n">
-        <v>38.4608154296875</v>
+        <v>38.4608116149902</v>
       </c>
       <c r="H374" t="n">
         <v>75864</v>
@@ -11331,7 +11331,7 @@
         <v>41.9749984741211</v>
       </c>
       <c r="G378" t="n">
-        <v>39.0421371459961</v>
+        <v>39.0421409606934</v>
       </c>
       <c r="H378" t="n">
         <v>23836</v>
@@ -11360,7 +11360,7 @@
         <v>42.5</v>
       </c>
       <c r="G379" t="n">
-        <v>39.5304565429688</v>
+        <v>39.530460357666</v>
       </c>
       <c r="H379" t="n">
         <v>28900</v>
@@ -11389,7 +11389,7 @@
         <v>42.875</v>
       </c>
       <c r="G380" t="n">
-        <v>39.8792572021484</v>
+        <v>39.8792610168457</v>
       </c>
       <c r="H380" t="n">
         <v>60344</v>
@@ -11476,7 +11476,7 @@
         <v>40.5</v>
       </c>
       <c r="G383" t="n">
-        <v>37.6702003479004</v>
+        <v>37.6702041625977</v>
       </c>
       <c r="H383" t="n">
         <v>45852</v>
@@ -11505,7 +11505,7 @@
         <v>40.4500007629395</v>
       </c>
       <c r="G384" t="n">
-        <v>37.6236991882324</v>
+        <v>37.6237030029297</v>
       </c>
       <c r="H384" t="n">
         <v>54188</v>
@@ -11534,7 +11534,7 @@
         <v>40.3499984741211</v>
       </c>
       <c r="G385" t="n">
-        <v>37.5306777954102</v>
+        <v>37.5306854248047</v>
       </c>
       <c r="H385" t="n">
         <v>69112</v>
@@ -11563,7 +11563,7 @@
         <v>41.5</v>
       </c>
       <c r="G386" t="n">
-        <v>38.6003303527832</v>
+        <v>38.6003341674805</v>
       </c>
       <c r="H386" t="n">
         <v>85616</v>
@@ -11592,7 +11592,7 @@
         <v>41.7000007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>38.7863616943359</v>
+        <v>38.7863578796387</v>
       </c>
       <c r="H387" t="n">
         <v>37404</v>
@@ -11650,7 +11650,7 @@
         <v>41.5250015258789</v>
       </c>
       <c r="G389" t="n">
-        <v>38.623592376709</v>
+        <v>38.6235847473145</v>
       </c>
       <c r="H389" t="n">
         <v>22168</v>
@@ -11679,7 +11679,7 @@
         <v>41.9749984741211</v>
       </c>
       <c r="G390" t="n">
-        <v>39.0421371459961</v>
+        <v>39.0421409606934</v>
       </c>
       <c r="H390" t="n">
         <v>33704</v>
@@ -11708,7 +11708,7 @@
         <v>41</v>
       </c>
       <c r="G391" t="n">
-        <v>38.1352691650391</v>
+        <v>38.1352653503418</v>
       </c>
       <c r="H391" t="n">
         <v>23844</v>
@@ -11882,7 +11882,7 @@
         <v>41.1500015258789</v>
       </c>
       <c r="G397" t="n">
-        <v>38.2747917175293</v>
+        <v>38.274787902832</v>
       </c>
       <c r="H397" t="n">
         <v>36504</v>
@@ -11940,7 +11940,7 @@
         <v>41.0750007629395</v>
       </c>
       <c r="G399" t="n">
-        <v>38.2050247192383</v>
+        <v>38.2050285339355</v>
       </c>
       <c r="H399" t="n">
         <v>21604</v>
@@ -11969,7 +11969,7 @@
         <v>41.0250015258789</v>
       </c>
       <c r="G400" t="n">
-        <v>38.158519744873</v>
+        <v>38.1585159301758</v>
       </c>
       <c r="H400" t="n">
         <v>12104</v>
@@ -11998,7 +11998,7 @@
         <v>41.375</v>
       </c>
       <c r="G401" t="n">
-        <v>38.4840660095215</v>
+        <v>38.4840621948242</v>
       </c>
       <c r="H401" t="n">
         <v>18196</v>
@@ -12027,7 +12027,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G402" t="n">
-        <v>38.6933403015137</v>
+        <v>38.6933364868164</v>
       </c>
       <c r="H402" t="n">
         <v>19848</v>
@@ -12056,7 +12056,7 @@
         <v>41.625</v>
       </c>
       <c r="G403" t="n">
-        <v>38.7165946960449</v>
+        <v>38.7165985107422</v>
       </c>
       <c r="H403" t="n">
         <v>13908</v>
@@ -12172,7 +12172,7 @@
         <v>47.4749984741211</v>
       </c>
       <c r="G407" t="n">
-        <v>44.1578407287598</v>
+        <v>44.157844543457</v>
       </c>
       <c r="H407" t="n">
         <v>93892</v>
@@ -12201,7 +12201,7 @@
         <v>47.5</v>
       </c>
       <c r="G408" t="n">
-        <v>44.1811065673828</v>
+        <v>44.1810989379883</v>
       </c>
       <c r="H408" t="n">
         <v>61600</v>
@@ -12230,7 +12230,7 @@
         <v>48.25</v>
       </c>
       <c r="G409" t="n">
-        <v>44.8787002563477</v>
+        <v>44.8787040710449</v>
       </c>
       <c r="H409" t="n">
         <v>60392</v>
@@ -12259,7 +12259,7 @@
         <v>48.0499992370605</v>
       </c>
       <c r="G410" t="n">
-        <v>44.6926727294922</v>
+        <v>44.6926765441895</v>
       </c>
       <c r="H410" t="n">
         <v>33956</v>
@@ -12317,7 +12317,7 @@
         <v>47.375</v>
       </c>
       <c r="G412" t="n">
-        <v>44.0648384094238</v>
+        <v>44.0648422241211</v>
       </c>
       <c r="H412" t="n">
         <v>42588</v>
@@ -12346,7 +12346,7 @@
         <v>47.5</v>
       </c>
       <c r="G413" t="n">
-        <v>44.1811065673828</v>
+        <v>44.1810989379883</v>
       </c>
       <c r="H413" t="n">
         <v>51208</v>
@@ -12375,7 +12375,7 @@
         <v>46.4249992370605</v>
       </c>
       <c r="G414" t="n">
-        <v>43.181209564209</v>
+        <v>43.1812133789062</v>
       </c>
       <c r="H414" t="n">
         <v>52128</v>
@@ -12404,7 +12404,7 @@
         <v>47.4500007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>44.134593963623</v>
+        <v>44.1345977783203</v>
       </c>
       <c r="H415" t="n">
         <v>46816</v>
@@ -12462,7 +12462,7 @@
         <v>47.125</v>
       </c>
       <c r="G417" t="n">
-        <v>43.8323097229004</v>
+        <v>43.8323020935059</v>
       </c>
       <c r="H417" t="n">
         <v>24788</v>
@@ -12491,7 +12491,7 @@
         <v>47.2750015258789</v>
       </c>
       <c r="G418" t="n">
-        <v>43.9718208312988</v>
+        <v>43.9718246459961</v>
       </c>
       <c r="H418" t="n">
         <v>44976</v>
@@ -12520,7 +12520,7 @@
         <v>47</v>
       </c>
       <c r="G419" t="n">
-        <v>43.7160415649414</v>
+        <v>43.7160377502441</v>
       </c>
       <c r="H419" t="n">
         <v>17860</v>
@@ -12549,7 +12549,7 @@
         <v>46.9749984741211</v>
       </c>
       <c r="G420" t="n">
-        <v>43.6927833557129</v>
+        <v>43.6927795410156</v>
       </c>
       <c r="H420" t="n">
         <v>42232</v>
@@ -12636,7 +12636,7 @@
         <v>45.6749992370605</v>
       </c>
       <c r="G423" t="n">
-        <v>42.4836196899414</v>
+        <v>42.4836158752441</v>
       </c>
       <c r="H423" t="n">
         <v>18092</v>
@@ -12665,7 +12665,7 @@
         <v>45.1500015258789</v>
       </c>
       <c r="G424" t="n">
-        <v>41.995304107666</v>
+        <v>41.9953079223633</v>
       </c>
       <c r="H424" t="n">
         <v>19212</v>
@@ -12694,7 +12694,7 @@
         <v>45.875</v>
       </c>
       <c r="G425" t="n">
-        <v>42.6696434020996</v>
+        <v>42.6696472167969</v>
       </c>
       <c r="H425" t="n">
         <v>62744</v>
@@ -12723,7 +12723,7 @@
         <v>47</v>
       </c>
       <c r="G426" t="n">
-        <v>43.7160415649414</v>
+        <v>43.7160377502441</v>
       </c>
       <c r="H426" t="n">
         <v>26240</v>
@@ -12752,7 +12752,7 @@
         <v>48.0999984741211</v>
       </c>
       <c r="G427" t="n">
-        <v>44.7391777038574</v>
+        <v>44.7391815185547</v>
       </c>
       <c r="H427" t="n">
         <v>42340</v>
@@ -12781,7 +12781,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G428" t="n">
-        <v>44.367130279541</v>
+        <v>44.3671264648438</v>
       </c>
       <c r="H428" t="n">
         <v>39088</v>
@@ -12810,7 +12810,7 @@
         <v>47.2750015258789</v>
       </c>
       <c r="G429" t="n">
-        <v>43.9718208312988</v>
+        <v>43.9718246459961</v>
       </c>
       <c r="H429" t="n">
         <v>31320</v>
@@ -12839,7 +12839,7 @@
         <v>47.1749992370605</v>
       </c>
       <c r="G430" t="n">
-        <v>43.8788108825684</v>
+        <v>43.8788146972656</v>
       </c>
       <c r="H430" t="n">
         <v>20896</v>
@@ -12897,7 +12897,7 @@
         <v>48.375</v>
       </c>
       <c r="G432" t="n">
-        <v>44.9949607849121</v>
+        <v>44.9949569702148</v>
       </c>
       <c r="H432" t="n">
         <v>77304</v>
@@ -12926,7 +12926,7 @@
         <v>48.625</v>
       </c>
       <c r="G433" t="n">
-        <v>45.2275009155273</v>
+        <v>45.2274932861328</v>
       </c>
       <c r="H433" t="n">
         <v>44268</v>
@@ -13100,7 +13100,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G439" t="n">
-        <v>47.2505226135254</v>
+        <v>47.2505264282227</v>
       </c>
       <c r="H439" t="n">
         <v>70492</v>
@@ -13129,7 +13129,7 @@
         <v>52.3250007629395</v>
       </c>
       <c r="G440" t="n">
-        <v>48.6689682006836</v>
+        <v>48.6689720153809</v>
       </c>
       <c r="H440" t="n">
         <v>192080</v>
@@ -13274,7 +13274,7 @@
         <v>50.5</v>
       </c>
       <c r="G445" t="n">
-        <v>46.9714851379395</v>
+        <v>46.9714889526367</v>
       </c>
       <c r="H445" t="n">
         <v>81068</v>
@@ -13332,7 +13332,7 @@
         <v>50.75</v>
       </c>
       <c r="G447" t="n">
-        <v>47.2040176391602</v>
+        <v>47.2040214538574</v>
       </c>
       <c r="H447" t="n">
         <v>33332</v>
@@ -13361,7 +13361,7 @@
         <v>50.8499984741211</v>
       </c>
       <c r="G448" t="n">
-        <v>47.2970314025879</v>
+        <v>47.2970275878906</v>
       </c>
       <c r="H448" t="n">
         <v>23664</v>
@@ -13419,7 +13419,7 @@
         <v>47.5</v>
       </c>
       <c r="G450" t="n">
-        <v>44.1811065673828</v>
+        <v>44.1810989379883</v>
       </c>
       <c r="H450" t="n">
         <v>874456</v>
@@ -13477,7 +13477,7 @@
         <v>47.75</v>
       </c>
       <c r="G452" t="n">
-        <v>44.4136390686035</v>
+        <v>44.4136352539062</v>
       </c>
       <c r="H452" t="n">
         <v>78752</v>
@@ -13506,7 +13506,7 @@
         <v>47.25</v>
       </c>
       <c r="G453" t="n">
-        <v>43.9485664367676</v>
+        <v>43.9485740661621</v>
       </c>
       <c r="H453" t="n">
         <v>123228</v>
@@ -13564,7 +13564,7 @@
         <v>45.125</v>
       </c>
       <c r="G455" t="n">
-        <v>41.972053527832</v>
+        <v>41.9720497131348</v>
       </c>
       <c r="H455" t="n">
         <v>244096</v>
@@ -13593,7 +13593,7 @@
         <v>45.5</v>
       </c>
       <c r="G456" t="n">
-        <v>42.3208465576172</v>
+        <v>42.3208503723145</v>
       </c>
       <c r="H456" t="n">
         <v>147280</v>
@@ -13680,7 +13680,7 @@
         <v>44.9900016784668</v>
       </c>
       <c r="G459" t="n">
-        <v>41.8464775085449</v>
+        <v>41.8464813232422</v>
       </c>
       <c r="H459" t="n">
         <v>125282</v>
@@ -13767,7 +13767,7 @@
         <v>44.5099983215332</v>
       </c>
       <c r="G462" t="n">
-        <v>41.4000129699707</v>
+        <v>41.4000205993652</v>
       </c>
       <c r="H462" t="n">
         <v>110936</v>
@@ -13825,7 +13825,7 @@
         <v>44.6199989318848</v>
       </c>
       <c r="G464" t="n">
-        <v>41.5023345947266</v>
+        <v>41.5023307800293</v>
       </c>
       <c r="H464" t="n">
         <v>43101</v>
@@ -13854,7 +13854,7 @@
         <v>45.3300018310547</v>
       </c>
       <c r="G465" t="n">
-        <v>42.1627311706543</v>
+        <v>42.162727355957</v>
       </c>
       <c r="H465" t="n">
         <v>60040</v>
@@ -13883,7 +13883,7 @@
         <v>45.1599998474121</v>
       </c>
       <c r="G466" t="n">
-        <v>42.0046081542969</v>
+        <v>42.0046005249023</v>
       </c>
       <c r="H466" t="n">
         <v>65535</v>
@@ -13912,7 +13912,7 @@
         <v>44.9900016784668</v>
       </c>
       <c r="G467" t="n">
-        <v>41.8464775085449</v>
+        <v>41.8464813232422</v>
       </c>
       <c r="H467" t="n">
         <v>72476</v>
@@ -13999,7 +13999,7 @@
         <v>45.6399993896484</v>
       </c>
       <c r="G470" t="n">
-        <v>42.4510650634766</v>
+        <v>42.4510612487793</v>
       </c>
       <c r="H470" t="n">
         <v>86121</v>
@@ -14086,7 +14086,7 @@
         <v>46.1100006103516</v>
       </c>
       <c r="G473" t="n">
-        <v>42.8882217407227</v>
+        <v>42.8882179260254</v>
       </c>
       <c r="H473" t="n">
         <v>280098</v>
@@ -14115,7 +14115,7 @@
         <v>46.9000015258789</v>
       </c>
       <c r="G474" t="n">
-        <v>43.6230278015137</v>
+        <v>43.6230316162109</v>
       </c>
       <c r="H474" t="n">
         <v>95733</v>
@@ -14173,7 +14173,7 @@
         <v>45.8499984741211</v>
       </c>
       <c r="G476" t="n">
-        <v>42.6463928222656</v>
+        <v>42.6463890075684</v>
       </c>
       <c r="H476" t="n">
         <v>77103</v>
@@ -14289,7 +14289,7 @@
         <v>44.9599990844727</v>
       </c>
       <c r="G480" t="n">
-        <v>41.8185768127441</v>
+        <v>41.8185729980469</v>
       </c>
       <c r="H480" t="n">
         <v>113306</v>
@@ -14347,7 +14347,7 @@
         <v>46.9199981689453</v>
       </c>
       <c r="G482" t="n">
-        <v>43.6416244506836</v>
+        <v>43.6416282653809</v>
       </c>
       <c r="H482" t="n">
         <v>217798</v>
@@ -14376,7 +14376,7 @@
         <v>47.7700004577637</v>
       </c>
       <c r="G483" t="n">
-        <v>44.4322319030762</v>
+        <v>44.4322395324707</v>
       </c>
       <c r="H483" t="n">
         <v>94266</v>
@@ -14405,7 +14405,7 @@
         <v>47.6599998474121</v>
       </c>
       <c r="G484" t="n">
-        <v>44.3299255371094</v>
+        <v>44.3299217224121</v>
       </c>
       <c r="H484" t="n">
         <v>88858</v>
@@ -14434,7 +14434,7 @@
         <v>49.0699996948242</v>
       </c>
       <c r="G485" t="n">
-        <v>45.6414070129395</v>
+        <v>45.6414031982422</v>
       </c>
       <c r="H485" t="n">
         <v>87277</v>
@@ -14463,7 +14463,7 @@
         <v>48.9300003051758</v>
       </c>
       <c r="G486" t="n">
-        <v>45.5111846923828</v>
+        <v>45.5111923217773</v>
       </c>
       <c r="H486" t="n">
         <v>67237</v>
@@ -14550,7 +14550,7 @@
         <v>47.7099990844727</v>
       </c>
       <c r="G489" t="n">
-        <v>44.3764305114746</v>
+        <v>44.3764266967773</v>
       </c>
       <c r="H489" t="n">
         <v>35434</v>
@@ -14579,7 +14579,7 @@
         <v>48.2799987792969</v>
       </c>
       <c r="G490" t="n">
-        <v>44.9066009521484</v>
+        <v>44.9066047668457</v>
       </c>
       <c r="H490" t="n">
         <v>53960</v>
@@ -14608,7 +14608,7 @@
         <v>47.8899993896484</v>
       </c>
       <c r="G491" t="n">
-        <v>44.5438537597656</v>
+        <v>44.5438499450684</v>
       </c>
       <c r="H491" t="n">
         <v>44801</v>
@@ -14724,7 +14724,7 @@
         <v>45.8600006103516</v>
       </c>
       <c r="G495" t="n">
-        <v>42.6556930541992</v>
+        <v>42.6556968688965</v>
       </c>
       <c r="H495" t="n">
         <v>92802</v>
@@ -14753,7 +14753,7 @@
         <v>46.2999992370605</v>
       </c>
       <c r="G496" t="n">
-        <v>43.0649490356445</v>
+        <v>43.0649452209473</v>
       </c>
       <c r="H496" t="n">
         <v>50866</v>
@@ -14782,7 +14782,7 @@
         <v>46.8899993896484</v>
       </c>
       <c r="G497" t="n">
-        <v>43.6137199401855</v>
+        <v>43.6137313842773</v>
       </c>
       <c r="H497" t="n">
         <v>28331</v>
@@ -14811,7 +14811,7 @@
         <v>47.5</v>
       </c>
       <c r="G498" t="n">
-        <v>44.1811065673828</v>
+        <v>44.1810989379883</v>
       </c>
       <c r="H498" t="n">
         <v>63726</v>
@@ -14840,7 +14840,7 @@
         <v>47.7999992370605</v>
       </c>
       <c r="G499" t="n">
-        <v>44.4601402282715</v>
+        <v>44.4601364135742</v>
       </c>
       <c r="H499" t="n">
         <v>28596</v>
@@ -14927,7 +14927,7 @@
         <v>47.9300003051758</v>
       </c>
       <c r="G502" t="n">
-        <v>44.5810546875</v>
+        <v>44.5810623168945</v>
       </c>
       <c r="H502" t="n">
         <v>52475</v>
@@ -14956,7 +14956,7 @@
         <v>48.9300003051758</v>
       </c>
       <c r="G503" t="n">
-        <v>45.5111846923828</v>
+        <v>45.5111923217773</v>
       </c>
       <c r="H503" t="n">
         <v>144242</v>
@@ -14985,7 +14985,7 @@
         <v>49.1199989318848</v>
       </c>
       <c r="G504" t="n">
-        <v>45.6879081726074</v>
+        <v>45.6879119873047</v>
       </c>
       <c r="H504" t="n">
         <v>52521</v>
@@ -15043,7 +15043,7 @@
         <v>48.4099998474121</v>
       </c>
       <c r="G506" t="n">
-        <v>45.0275192260742</v>
+        <v>45.027515411377</v>
       </c>
       <c r="H506" t="n">
         <v>29540</v>
@@ -15072,7 +15072,7 @@
         <v>48.2599983215332</v>
       </c>
       <c r="G507" t="n">
-        <v>44.887996673584</v>
+        <v>44.8880043029785</v>
       </c>
       <c r="H507" t="n">
         <v>35152</v>
@@ -15101,7 +15101,7 @@
         <v>47.25</v>
       </c>
       <c r="G508" t="n">
-        <v>43.9485664367676</v>
+        <v>43.9485740661621</v>
       </c>
       <c r="H508" t="n">
         <v>29701</v>
@@ -15130,7 +15130,7 @@
         <v>46.8300018310547</v>
       </c>
       <c r="G509" t="n">
-        <v>43.5579261779785</v>
+        <v>43.5579147338867</v>
       </c>
       <c r="H509" t="n">
         <v>53910</v>
@@ -15159,7 +15159,7 @@
         <v>46.5099983215332</v>
       </c>
       <c r="G510" t="n">
-        <v>43.2602729797363</v>
+        <v>43.2602767944336</v>
       </c>
       <c r="H510" t="n">
         <v>32260</v>
@@ -15188,7 +15188,7 @@
         <v>46.1699981689453</v>
       </c>
       <c r="G511" t="n">
-        <v>42.9440269470215</v>
+        <v>42.9440307617188</v>
       </c>
       <c r="H511" t="n">
         <v>14035</v>
@@ -15275,7 +15275,7 @@
         <v>47.7999992370605</v>
       </c>
       <c r="G514" t="n">
-        <v>44.4601402282715</v>
+        <v>44.4601364135742</v>
       </c>
       <c r="H514" t="n">
         <v>21825</v>
@@ -15304,7 +15304,7 @@
         <v>48.3600006103516</v>
       </c>
       <c r="G515" t="n">
-        <v>44.9810104370117</v>
+        <v>44.981014251709</v>
       </c>
       <c r="H515" t="n">
         <v>29349</v>
@@ -15333,7 +15333,7 @@
         <v>48.3800010681152</v>
       </c>
       <c r="G516" t="n">
-        <v>44.9996147155762</v>
+        <v>44.9996109008789</v>
       </c>
       <c r="H516" t="n">
         <v>42204</v>
@@ -15362,7 +15362,7 @@
         <v>48.4799995422363</v>
       </c>
       <c r="G517" t="n">
-        <v>45.0926246643066</v>
+        <v>45.0926284790039</v>
       </c>
       <c r="H517" t="n">
         <v>39741</v>
@@ -15391,7 +15391,7 @@
         <v>49.0800018310547</v>
       </c>
       <c r="G518" t="n">
-        <v>45.650707244873</v>
+        <v>45.6507034301758</v>
       </c>
       <c r="H518" t="n">
         <v>41162</v>
@@ -15449,7 +15449,7 @@
         <v>49</v>
       </c>
       <c r="G520" t="n">
-        <v>45.5762939453125</v>
+        <v>45.5762977600098</v>
       </c>
       <c r="H520" t="n">
         <v>23144</v>
@@ -15478,7 +15478,7 @@
         <v>49.4599990844727</v>
       </c>
       <c r="G521" t="n">
-        <v>46.004150390625</v>
+        <v>46.0041580200195</v>
       </c>
       <c r="H521" t="n">
         <v>51297</v>
@@ -15507,7 +15507,7 @@
         <v>49.5200004577637</v>
       </c>
       <c r="G522" t="n">
-        <v>46.0599632263184</v>
+        <v>46.0599594116211</v>
       </c>
       <c r="H522" t="n">
         <v>38009</v>
@@ -15536,7 +15536,7 @@
         <v>49.4000015258789</v>
       </c>
       <c r="G523" t="n">
-        <v>45.9483451843262</v>
+        <v>45.9483489990234</v>
       </c>
       <c r="H523" t="n">
         <v>35542</v>
@@ -15565,7 +15565,7 @@
         <v>49.7200012207031</v>
       </c>
       <c r="G524" t="n">
-        <v>46.2459869384766</v>
+        <v>46.2459831237793</v>
       </c>
       <c r="H524" t="n">
         <v>31890</v>
@@ -15652,7 +15652,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G527" t="n">
-        <v>47.1575202941895</v>
+        <v>47.1575126647949</v>
       </c>
       <c r="H527" t="n">
         <v>79567</v>
@@ -15681,7 +15681,7 @@
         <v>50.7000007629395</v>
       </c>
       <c r="G528" t="n">
-        <v>47.1575202941895</v>
+        <v>47.1575126647949</v>
       </c>
       <c r="H528" t="n">
         <v>52853</v>
@@ -15710,7 +15710,7 @@
         <v>49.4000015258789</v>
       </c>
       <c r="G529" t="n">
-        <v>45.9483451843262</v>
+        <v>45.9483489990234</v>
       </c>
       <c r="H529" t="n">
         <v>64046</v>
@@ -15739,7 +15739,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G530" t="n">
-        <v>47.5295562744141</v>
+        <v>47.5295600891113</v>
       </c>
       <c r="H530" t="n">
         <v>56884</v>
@@ -15797,7 +15797,7 @@
         <v>51.5</v>
       </c>
       <c r="G532" t="n">
-        <v>47.9016151428223</v>
+        <v>47.901611328125</v>
       </c>
       <c r="H532" t="n">
         <v>100856</v>
@@ -15826,7 +15826,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G533" t="n">
-        <v>48.6457214355469</v>
+        <v>48.6457176208496</v>
       </c>
       <c r="H533" t="n">
         <v>72228</v>
@@ -15855,7 +15855,7 @@
         <v>53.3499984741211</v>
       </c>
       <c r="G534" t="n">
-        <v>49.6223526000977</v>
+        <v>49.6223487854004</v>
       </c>
       <c r="H534" t="n">
         <v>88861</v>
@@ -15884,7 +15884,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G535" t="n">
-        <v>49.7153663635254</v>
+        <v>49.7153739929199</v>
       </c>
       <c r="H535" t="n">
         <v>68979</v>
@@ -15942,7 +15942,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G537" t="n">
-        <v>48.6922225952148</v>
+        <v>48.6922264099121</v>
       </c>
       <c r="H537" t="n">
         <v>107201</v>
@@ -15971,7 +15971,7 @@
         <v>53.25</v>
       </c>
       <c r="G538" t="n">
-        <v>49.5293388366699</v>
+        <v>49.5293426513672</v>
       </c>
       <c r="H538" t="n">
         <v>63629</v>
@@ -16000,7 +16000,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>49.389820098877</v>
+        <v>49.3898239135742</v>
       </c>
       <c r="H539" t="n">
         <v>92773</v>
@@ -16029,7 +16029,7 @@
         <v>50.4000015258789</v>
       </c>
       <c r="G540" t="n">
-        <v>46.8784713745117</v>
+        <v>46.878475189209</v>
       </c>
       <c r="H540" t="n">
         <v>125931</v>
@@ -16087,7 +16087,7 @@
         <v>49</v>
       </c>
       <c r="G542" t="n">
-        <v>45.5762939453125</v>
+        <v>45.5762977600098</v>
       </c>
       <c r="H542" t="n">
         <v>80239</v>
@@ -16319,7 +16319,7 @@
         <v>49</v>
       </c>
       <c r="G550" t="n">
-        <v>45.5762939453125</v>
+        <v>45.5762977600098</v>
       </c>
       <c r="H550" t="n">
         <v>83168</v>
@@ -16377,7 +16377,7 @@
         <v>49.4000015258789</v>
       </c>
       <c r="G552" t="n">
-        <v>45.9483451843262</v>
+        <v>45.9483489990234</v>
       </c>
       <c r="H552" t="n">
         <v>105062</v>
@@ -16435,7 +16435,7 @@
         <v>48.5999984741211</v>
       </c>
       <c r="G554" t="n">
-        <v>45.2042388916016</v>
+        <v>45.2042465209961</v>
       </c>
       <c r="H554" t="n">
         <v>64307</v>
@@ -16493,7 +16493,7 @@
         <v>48.4000015258789</v>
       </c>
       <c r="G556" t="n">
-        <v>45.0182151794434</v>
+        <v>45.0182228088379</v>
       </c>
       <c r="H556" t="n">
         <v>45768</v>
@@ -16522,7 +16522,7 @@
         <v>48.6399993896484</v>
       </c>
       <c r="G557" t="n">
-        <v>45.2414474487305</v>
+        <v>45.2414512634277</v>
       </c>
       <c r="H557" t="n">
         <v>48109</v>
@@ -16667,7 +16667,7 @@
         <v>51.75</v>
       </c>
       <c r="G562" t="n">
-        <v>48.1341514587402</v>
+        <v>48.134147644043</v>
       </c>
       <c r="H562" t="n">
         <v>109580</v>
@@ -16754,7 +16754,7 @@
         <v>50.25</v>
       </c>
       <c r="G565" t="n">
-        <v>46.738956451416</v>
+        <v>46.7389488220215</v>
       </c>
       <c r="H565" t="n">
         <v>72206</v>
@@ -16783,7 +16783,7 @@
         <v>51.0999984741211</v>
       </c>
       <c r="G566" t="n">
-        <v>47.5295562744141</v>
+        <v>47.5295600891113</v>
       </c>
       <c r="H566" t="n">
         <v>75270</v>
@@ -16812,7 +16812,7 @@
         <v>49.3199996948242</v>
       </c>
       <c r="G567" t="n">
-        <v>45.8739395141602</v>
+        <v>45.8739433288574</v>
       </c>
       <c r="H567" t="n">
         <v>86829</v>
@@ -16841,7 +16841,7 @@
         <v>47.9000015258789</v>
       </c>
       <c r="G568" t="n">
-        <v>44.553165435791</v>
+        <v>44.5531578063965</v>
       </c>
       <c r="H568" t="n">
         <v>75514</v>
@@ -16899,7 +16899,7 @@
         <v>47.5400009155273</v>
       </c>
       <c r="G570" t="n">
-        <v>44.2183113098145</v>
+        <v>44.2183074951172</v>
       </c>
       <c r="H570" t="n">
         <v>35143</v>
@@ -16957,7 +16957,7 @@
         <v>46.8400001525879</v>
       </c>
       <c r="G572" t="n">
-        <v>43.5672187805176</v>
+        <v>43.5672149658203</v>
       </c>
       <c r="H572" t="n">
         <v>64511</v>
@@ -17073,7 +17073,7 @@
         <v>43.5400009155273</v>
       </c>
       <c r="G576" t="n">
-        <v>40.4977912902832</v>
+        <v>40.4977951049805</v>
       </c>
       <c r="H576" t="n">
         <v>61738</v>
@@ -17160,7 +17160,7 @@
         <v>45.1599998474121</v>
       </c>
       <c r="G579" t="n">
-        <v>42.0046081542969</v>
+        <v>42.0046005249023</v>
       </c>
       <c r="H579" t="n">
         <v>48891</v>
@@ -17189,7 +17189,7 @@
         <v>48.060001373291</v>
       </c>
       <c r="G580" t="n">
-        <v>44.7019805908203</v>
+        <v>44.701976776123</v>
       </c>
       <c r="H580" t="n">
         <v>131794</v>
@@ -17276,7 +17276,7 @@
         <v>48.2000007629395</v>
       </c>
       <c r="G583" t="n">
-        <v>44.8321914672852</v>
+        <v>44.8321876525879</v>
       </c>
       <c r="H583" t="n">
         <v>39665</v>
@@ -17305,7 +17305,7 @@
         <v>48.1399993896484</v>
       </c>
       <c r="G584" t="n">
-        <v>44.7763824462891</v>
+        <v>44.7763786315918</v>
       </c>
       <c r="H584" t="n">
         <v>52904</v>
@@ -17334,7 +17334,7 @@
         <v>48.8800010681152</v>
       </c>
       <c r="G585" t="n">
-        <v>45.4646759033203</v>
+        <v>45.4646797180176</v>
       </c>
       <c r="H585" t="n">
         <v>53861</v>
@@ -17363,7 +17363,7 @@
         <v>48.7599983215332</v>
       </c>
       <c r="G586" t="n">
-        <v>45.3530616760254</v>
+        <v>45.3530693054199</v>
       </c>
       <c r="H586" t="n">
         <v>42644</v>
@@ -17392,7 +17392,7 @@
         <v>49.1800003051758</v>
       </c>
       <c r="G587" t="n">
-        <v>45.7437171936035</v>
+        <v>45.7437210083008</v>
       </c>
       <c r="H587" t="n">
         <v>26752</v>
@@ -17479,7 +17479,7 @@
         <v>52</v>
       </c>
       <c r="G590" t="n">
-        <v>48.3666839599609</v>
+        <v>48.3666725158691</v>
       </c>
       <c r="H590" t="n">
         <v>115205</v>
@@ -17595,7 +17595,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G594" t="n">
-        <v>48.6922225952148</v>
+        <v>48.6922264099121</v>
       </c>
       <c r="H594" t="n">
         <v>70106</v>
@@ -17653,7 +17653,7 @@
         <v>53.75</v>
       </c>
       <c r="G596" t="n">
-        <v>49.9944038391113</v>
+        <v>49.9944076538086</v>
       </c>
       <c r="H596" t="n">
         <v>95286</v>
@@ -17682,7 +17682,7 @@
         <v>53.6500015258789</v>
       </c>
       <c r="G597" t="n">
-        <v>49.9013977050781</v>
+        <v>49.9013938903809</v>
       </c>
       <c r="H597" t="n">
         <v>56659</v>
@@ -17740,7 +17740,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G599" t="n">
-        <v>49.7141418457031</v>
+        <v>49.7141456604004</v>
       </c>
       <c r="H599" t="n">
         <v>85715</v>
@@ -17769,7 +17769,7 @@
         <v>53.75</v>
       </c>
       <c r="G600" t="n">
-        <v>50.3227005004883</v>
+        <v>50.3227081298828</v>
       </c>
       <c r="H600" t="n">
         <v>74547</v>
@@ -17798,7 +17798,7 @@
         <v>55</v>
       </c>
       <c r="G601" t="n">
-        <v>51.4929962158203</v>
+        <v>51.492992401123</v>
       </c>
       <c r="H601" t="n">
         <v>62003</v>
@@ -17827,7 +17827,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G602" t="n">
-        <v>51.3993682861328</v>
+        <v>51.3993721008301</v>
       </c>
       <c r="H602" t="n">
         <v>39811</v>
@@ -17856,7 +17856,7 @@
         <v>54.5</v>
       </c>
       <c r="G603" t="n">
-        <v>51.0248794555664</v>
+        <v>51.0248756408691</v>
       </c>
       <c r="H603" t="n">
         <v>58185</v>
@@ -17914,7 +17914,7 @@
         <v>52.5</v>
       </c>
       <c r="G605" t="n">
-        <v>49.152400970459</v>
+        <v>49.1524047851562</v>
       </c>
       <c r="H605" t="n">
         <v>67416</v>
@@ -17943,7 +17943,7 @@
         <v>54.25</v>
       </c>
       <c r="G606" t="n">
-        <v>50.7908172607422</v>
+        <v>50.7908210754395</v>
       </c>
       <c r="H606" t="n">
         <v>78589</v>
@@ -17972,7 +17972,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G607" t="n">
-        <v>48.5906639099121</v>
+        <v>48.5906677246094</v>
       </c>
       <c r="H607" t="n">
         <v>104479</v>
@@ -18001,7 +18001,7 @@
         <v>52.5</v>
       </c>
       <c r="G608" t="n">
-        <v>49.152400970459</v>
+        <v>49.1524047851562</v>
       </c>
       <c r="H608" t="n">
         <v>45065</v>
@@ -18059,7 +18059,7 @@
         <v>51.9000015258789</v>
       </c>
       <c r="G610" t="n">
-        <v>48.5906639099121</v>
+        <v>48.5906677246094</v>
       </c>
       <c r="H610" t="n">
         <v>57133</v>
@@ -18088,7 +18088,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G611" t="n">
-        <v>48.4034194946289</v>
+        <v>48.4034156799316</v>
       </c>
       <c r="H611" t="n">
         <v>48570</v>
@@ -18117,7 +18117,7 @@
         <v>52.4500007629395</v>
       </c>
       <c r="G612" t="n">
-        <v>49.105598449707</v>
+        <v>49.1055908203125</v>
       </c>
       <c r="H612" t="n">
         <v>64460</v>
@@ -18146,7 +18146,7 @@
         <v>50.8499984741211</v>
       </c>
       <c r="G613" t="n">
-        <v>47.6076126098633</v>
+        <v>47.6076164245605</v>
       </c>
       <c r="H613" t="n">
         <v>39882</v>
@@ -18204,7 +18204,7 @@
         <v>50.6500015258789</v>
       </c>
       <c r="G615" t="n">
-        <v>47.4203643798828</v>
+        <v>47.4203681945801</v>
       </c>
       <c r="H615" t="n">
         <v>89802</v>
@@ -18262,7 +18262,7 @@
         <v>51.9500007629395</v>
       </c>
       <c r="G617" t="n">
-        <v>48.6374778747559</v>
+        <v>48.6374740600586</v>
       </c>
       <c r="H617" t="n">
         <v>56665</v>
@@ -18291,7 +18291,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G618" t="n">
-        <v>48.965160369873</v>
+        <v>48.9651565551758</v>
       </c>
       <c r="H618" t="n">
         <v>42847</v>
@@ -18320,7 +18320,7 @@
         <v>52.6500015258789</v>
       </c>
       <c r="G619" t="n">
-        <v>49.292839050293</v>
+        <v>49.2928428649902</v>
       </c>
       <c r="H619" t="n">
         <v>52322</v>
@@ -18378,7 +18378,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G621" t="n">
-        <v>50.5099487304688</v>
+        <v>50.5099411010742</v>
       </c>
       <c r="H621" t="n">
         <v>98843</v>
@@ -18407,7 +18407,7 @@
         <v>52.8499984741211</v>
       </c>
       <c r="G622" t="n">
-        <v>49.4800872802734</v>
+        <v>49.4800834655762</v>
       </c>
       <c r="H622" t="n">
         <v>54826</v>
@@ -18436,7 +18436,7 @@
         <v>54.2000007629395</v>
       </c>
       <c r="G623" t="n">
-        <v>50.744010925293</v>
+        <v>50.7440071105957</v>
       </c>
       <c r="H623" t="n">
         <v>29152</v>
@@ -18465,7 +18465,7 @@
         <v>54.7999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>51.3057479858398</v>
+        <v>51.3057518005371</v>
       </c>
       <c r="H624" t="n">
         <v>47061</v>
@@ -18494,7 +18494,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G625" t="n">
-        <v>51.3993682861328</v>
+        <v>51.3993721008301</v>
       </c>
       <c r="H625" t="n">
         <v>30726</v>
@@ -18610,7 +18610,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G629" t="n">
-        <v>53.9272155761719</v>
+        <v>53.9272117614746</v>
       </c>
       <c r="H629" t="n">
         <v>75666</v>
@@ -18755,7 +18755,7 @@
         <v>58</v>
       </c>
       <c r="G634" t="n">
-        <v>54.3017082214355</v>
+        <v>54.3017044067383</v>
       </c>
       <c r="H634" t="n">
         <v>34709</v>
@@ -18784,7 +18784,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G635" t="n">
-        <v>54.7230072021484</v>
+        <v>54.7230110168457</v>
       </c>
       <c r="H635" t="n">
         <v>87809</v>
@@ -18842,7 +18842,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>54.488956451416</v>
+        <v>54.4889488220215</v>
       </c>
       <c r="H637" t="n">
         <v>38449</v>
@@ -18871,7 +18871,7 @@
         <v>58</v>
       </c>
       <c r="G638" t="n">
-        <v>54.3017082214355</v>
+        <v>54.3017044067383</v>
       </c>
       <c r="H638" t="n">
         <v>31911</v>
@@ -18900,7 +18900,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G639" t="n">
-        <v>54.488956451416</v>
+        <v>54.4889488220215</v>
       </c>
       <c r="H639" t="n">
         <v>39212</v>
@@ -18929,7 +18929,7 @@
         <v>56</v>
       </c>
       <c r="G640" t="n">
-        <v>52.4292335510254</v>
+        <v>52.4292297363281</v>
       </c>
       <c r="H640" t="n">
         <v>51824</v>
@@ -18958,7 +18958,7 @@
         <v>56.5</v>
       </c>
       <c r="G641" t="n">
-        <v>52.8973503112793</v>
+        <v>52.897346496582</v>
       </c>
       <c r="H641" t="n">
         <v>40607</v>
@@ -19016,7 +19016,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G643" t="n">
-        <v>53.5527114868164</v>
+        <v>53.5527191162109</v>
       </c>
       <c r="H643" t="n">
         <v>25355</v>
@@ -19074,7 +19074,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G645" t="n">
-        <v>53.084602355957</v>
+        <v>53.0845985412598</v>
       </c>
       <c r="H645" t="n">
         <v>35483</v>
@@ -19161,7 +19161,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G648" t="n">
-        <v>53.9272155761719</v>
+        <v>53.9272117614746</v>
       </c>
       <c r="H648" t="n">
         <v>19632</v>
@@ -19190,7 +19190,7 @@
         <v>57.7000007629395</v>
       </c>
       <c r="G649" t="n">
-        <v>54.0208282470703</v>
+        <v>54.0208358764648</v>
       </c>
       <c r="H649" t="n">
         <v>13785</v>
@@ -19219,7 +19219,7 @@
         <v>59.4500007629395</v>
       </c>
       <c r="G650" t="n">
-        <v>55.659252166748</v>
+        <v>55.6592483520508</v>
       </c>
       <c r="H650" t="n">
         <v>41437</v>
@@ -19277,7 +19277,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G652" t="n">
-        <v>55.5188064575195</v>
+        <v>55.5188102722168</v>
       </c>
       <c r="H652" t="n">
         <v>35219</v>
@@ -19364,7 +19364,7 @@
         <v>59.2000007629395</v>
       </c>
       <c r="G655" t="n">
-        <v>55.4251899719238</v>
+        <v>55.4251937866211</v>
       </c>
       <c r="H655" t="n">
         <v>28420</v>
@@ -19393,7 +19393,7 @@
         <v>59.5499992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>55.7528686523438</v>
+        <v>55.7528648376465</v>
       </c>
       <c r="H656" t="n">
         <v>22799</v>
@@ -19422,7 +19422,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>55.8933067321777</v>
+        <v>55.893310546875</v>
       </c>
       <c r="H657" t="n">
         <v>27208</v>
@@ -19451,7 +19451,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G658" t="n">
-        <v>54.488956451416</v>
+        <v>54.4889488220215</v>
       </c>
       <c r="H658" t="n">
         <v>29666</v>
@@ -19480,7 +19480,7 @@
         <v>57.9000015258789</v>
       </c>
       <c r="G659" t="n">
-        <v>54.208080291748</v>
+        <v>54.2080764770508</v>
       </c>
       <c r="H659" t="n">
         <v>35489</v>
@@ -19509,7 +19509,7 @@
         <v>58</v>
       </c>
       <c r="G660" t="n">
-        <v>54.3017082214355</v>
+        <v>54.3017044067383</v>
       </c>
       <c r="H660" t="n">
         <v>24597</v>
@@ -19538,7 +19538,7 @@
         <v>55.4000015258789</v>
       </c>
       <c r="G661" t="n">
-        <v>51.8674926757812</v>
+        <v>51.8674964904785</v>
       </c>
       <c r="H661" t="n">
         <v>65917</v>
@@ -19770,7 +19770,7 @@
         <v>56.5</v>
       </c>
       <c r="G669" t="n">
-        <v>52.8973503112793</v>
+        <v>52.897346496582</v>
       </c>
       <c r="H669" t="n">
         <v>14311</v>
@@ -19828,7 +19828,7 @@
         <v>56</v>
       </c>
       <c r="G671" t="n">
-        <v>52.4292335510254</v>
+        <v>52.4292297363281</v>
       </c>
       <c r="H671" t="n">
         <v>21951</v>
@@ -19886,7 +19886,7 @@
         <v>56.7000007629395</v>
       </c>
       <c r="G673" t="n">
-        <v>53.084602355957</v>
+        <v>53.0845985412598</v>
       </c>
       <c r="H673" t="n">
         <v>20484</v>
@@ -19915,7 +19915,7 @@
         <v>56.9500007629395</v>
       </c>
       <c r="G674" t="n">
-        <v>53.318660736084</v>
+        <v>53.3186569213867</v>
       </c>
       <c r="H674" t="n">
         <v>18731</v>
@@ -19973,7 +19973,7 @@
         <v>57.5999984741211</v>
       </c>
       <c r="G676" t="n">
-        <v>53.9272155761719</v>
+        <v>53.9272117614746</v>
       </c>
       <c r="H676" t="n">
         <v>8317</v>
@@ -20002,7 +20002,7 @@
         <v>57.5</v>
       </c>
       <c r="G677" t="n">
-        <v>53.8335838317871</v>
+        <v>53.8335876464844</v>
       </c>
       <c r="H677" t="n">
         <v>16886</v>
@@ -20060,7 +20060,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G679" t="n">
-        <v>52.7100944519043</v>
+        <v>52.7100982666016</v>
       </c>
       <c r="H679" t="n">
         <v>21855</v>
@@ -20147,7 +20147,7 @@
         <v>56.1500015258789</v>
       </c>
       <c r="G682" t="n">
-        <v>52.5696678161621</v>
+        <v>52.5696716308594</v>
       </c>
       <c r="H682" t="n">
         <v>24937</v>
@@ -20176,7 +20176,7 @@
         <v>55.2000007629395</v>
       </c>
       <c r="G683" t="n">
-        <v>51.680248260498</v>
+        <v>51.6802444458008</v>
       </c>
       <c r="H683" t="n">
         <v>41022</v>
@@ -20205,7 +20205,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>50.3695106506348</v>
+        <v>50.369514465332</v>
       </c>
       <c r="H684" t="n">
         <v>41156</v>
@@ -20234,7 +20234,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G685" t="n">
-        <v>49.7609558105469</v>
+        <v>49.7609596252441</v>
       </c>
       <c r="H685" t="n">
         <v>40633</v>
@@ -20263,7 +20263,7 @@
         <v>53.9500007629395</v>
       </c>
       <c r="G686" t="n">
-        <v>50.5099487304688</v>
+        <v>50.5099411010742</v>
       </c>
       <c r="H686" t="n">
         <v>39685</v>
@@ -20292,7 +20292,7 @@
         <v>55.0499992370605</v>
       </c>
       <c r="G687" t="n">
-        <v>51.5398025512695</v>
+        <v>51.5398063659668</v>
       </c>
       <c r="H687" t="n">
         <v>25522</v>
@@ -20321,7 +20321,7 @@
         <v>54.6500015258789</v>
       </c>
       <c r="G688" t="n">
-        <v>51.1653175354004</v>
+        <v>51.1653137207031</v>
       </c>
       <c r="H688" t="n">
         <v>21210</v>
@@ -20350,7 +20350,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G689" t="n">
-        <v>53.412281036377</v>
+        <v>53.4122772216797</v>
       </c>
       <c r="H689" t="n">
         <v>52349</v>
@@ -20408,7 +20408,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G691" t="n">
-        <v>54.488956451416</v>
+        <v>54.4889488220215</v>
       </c>
       <c r="H691" t="n">
         <v>36268</v>
@@ -20437,7 +20437,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G692" t="n">
-        <v>53.4590950012207</v>
+        <v>53.4590911865234</v>
       </c>
       <c r="H692" t="n">
         <v>37782</v>
@@ -20466,7 +20466,7 @@
         <v>56.4000015258789</v>
       </c>
       <c r="G693" t="n">
-        <v>52.8037300109863</v>
+        <v>52.8037261962891</v>
       </c>
       <c r="H693" t="n">
         <v>21927</v>
@@ -20495,7 +20495,7 @@
         <v>57.4500007629395</v>
       </c>
       <c r="G694" t="n">
-        <v>53.7867774963379</v>
+        <v>53.7867698669434</v>
       </c>
       <c r="H694" t="n">
         <v>24827</v>
@@ -20524,7 +20524,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G695" t="n">
-        <v>53.4590950012207</v>
+        <v>53.4590911865234</v>
       </c>
       <c r="H695" t="n">
         <v>10994</v>
@@ -20553,7 +20553,7 @@
         <v>58.1500015258789</v>
       </c>
       <c r="G696" t="n">
-        <v>54.442138671875</v>
+        <v>54.4421424865723</v>
       </c>
       <c r="H696" t="n">
         <v>44187</v>
@@ -20582,7 +20582,7 @@
         <v>58.2000007629395</v>
       </c>
       <c r="G697" t="n">
-        <v>54.488956451416</v>
+        <v>54.4889488220215</v>
       </c>
       <c r="H697" t="n">
         <v>17973</v>
@@ -20611,7 +20611,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G698" t="n">
-        <v>54.7230072021484</v>
+        <v>54.7230110168457</v>
       </c>
       <c r="H698" t="n">
         <v>45019</v>
@@ -20640,7 +20640,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G699" t="n">
-        <v>54.7230072021484</v>
+        <v>54.7230110168457</v>
       </c>
       <c r="H699" t="n">
         <v>47159</v>
@@ -20669,7 +20669,7 @@
         <v>59.7000007629395</v>
       </c>
       <c r="G700" t="n">
-        <v>55.8933067321777</v>
+        <v>55.893310546875</v>
       </c>
       <c r="H700" t="n">
         <v>52231</v>
@@ -20698,7 +20698,7 @@
         <v>59.25</v>
       </c>
       <c r="G701" t="n">
-        <v>55.4720001220703</v>
+        <v>55.4719924926758</v>
       </c>
       <c r="H701" t="n">
         <v>65714</v>
@@ -20756,7 +20756,7 @@
         <v>60.2999992370605</v>
       </c>
       <c r="G703" t="n">
-        <v>56.4550476074219</v>
+        <v>56.4550399780273</v>
       </c>
       <c r="H703" t="n">
         <v>35409</v>
@@ -20785,7 +20785,7 @@
         <v>61</v>
       </c>
       <c r="G704" t="n">
-        <v>57.110408782959</v>
+        <v>57.1104125976562</v>
       </c>
       <c r="H704" t="n">
         <v>35814</v>
@@ -20814,7 +20814,7 @@
         <v>60</v>
       </c>
       <c r="G705" t="n">
-        <v>56.1741790771484</v>
+        <v>56.1741828918457</v>
       </c>
       <c r="H705" t="n">
         <v>43029</v>
@@ -20843,7 +20843,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G706" t="n">
-        <v>53.4590950012207</v>
+        <v>53.4590911865234</v>
       </c>
       <c r="H706" t="n">
         <v>52515</v>
@@ -20872,7 +20872,7 @@
         <v>53.5</v>
       </c>
       <c r="G707" t="n">
-        <v>50.0886421203613</v>
+        <v>50.0886383056641</v>
       </c>
       <c r="H707" t="n">
         <v>61721</v>
@@ -20901,7 +20901,7 @@
         <v>52.0499992370605</v>
       </c>
       <c r="G708" t="n">
-        <v>48.7310905456543</v>
+        <v>48.7310981750488</v>
       </c>
       <c r="H708" t="n">
         <v>80209</v>
@@ -20930,7 +20930,7 @@
         <v>49.5200004577637</v>
       </c>
       <c r="G709" t="n">
-        <v>46.362419128418</v>
+        <v>46.3624153137207</v>
       </c>
       <c r="H709" t="n">
         <v>74542</v>
@@ -20988,7 +20988,7 @@
         <v>50.7999992370605</v>
       </c>
       <c r="G711" t="n">
-        <v>47.5607986450195</v>
+        <v>47.5608024597168</v>
       </c>
       <c r="H711" t="n">
         <v>76042</v>
@@ -21017,7 +21017,7 @@
         <v>50</v>
       </c>
       <c r="G712" t="n">
-        <v>46.8118171691895</v>
+        <v>46.8118095397949</v>
       </c>
       <c r="H712" t="n">
         <v>49038</v>
@@ -21046,7 +21046,7 @@
         <v>52.8499984741211</v>
       </c>
       <c r="G713" t="n">
-        <v>49.4800872802734</v>
+        <v>49.4800834655762</v>
       </c>
       <c r="H713" t="n">
         <v>60028</v>
@@ -21133,7 +21133,7 @@
         <v>52.4500007629395</v>
       </c>
       <c r="G716" t="n">
-        <v>49.105598449707</v>
+        <v>49.1055908203125</v>
       </c>
       <c r="H716" t="n">
         <v>61353</v>
@@ -21162,7 +21162,7 @@
         <v>52.4500007629395</v>
       </c>
       <c r="G717" t="n">
-        <v>49.105598449707</v>
+        <v>49.1055908203125</v>
       </c>
       <c r="H717" t="n">
         <v>39464</v>
@@ -21191,7 +21191,7 @@
         <v>48.8199996948242</v>
       </c>
       <c r="G718" t="n">
-        <v>45.7070617675781</v>
+        <v>45.7070579528809</v>
       </c>
       <c r="H718" t="n">
         <v>96025</v>
@@ -21249,7 +21249,7 @@
         <v>47.060001373291</v>
       </c>
       <c r="G720" t="n">
-        <v>44.0592803955078</v>
+        <v>44.0592765808105</v>
       </c>
       <c r="H720" t="n">
         <v>69318</v>
@@ -21278,7 +21278,7 @@
         <v>47.0800018310547</v>
       </c>
       <c r="G721" t="n">
-        <v>44.0780029296875</v>
+        <v>44.0780067443848</v>
       </c>
       <c r="H721" t="n">
         <v>53676</v>
@@ -21307,7 +21307,7 @@
         <v>48.6599998474121</v>
       </c>
       <c r="G722" t="n">
-        <v>45.557258605957</v>
+        <v>45.5572547912598</v>
       </c>
       <c r="H722" t="n">
         <v>144083</v>
@@ -21336,7 +21336,7 @@
         <v>49.0400009155273</v>
       </c>
       <c r="G723" t="n">
-        <v>45.9130249023438</v>
+        <v>45.913028717041</v>
       </c>
       <c r="H723" t="n">
         <v>66124</v>
@@ -21365,7 +21365,7 @@
         <v>48.9599990844727</v>
       </c>
       <c r="G724" t="n">
-        <v>45.8381309509277</v>
+        <v>45.8381271362305</v>
       </c>
       <c r="H724" t="n">
         <v>66228</v>
@@ -21394,7 +21394,7 @@
         <v>48.4000015258789</v>
       </c>
       <c r="G725" t="n">
-        <v>45.313835144043</v>
+        <v>45.3138389587402</v>
       </c>
       <c r="H725" t="n">
         <v>33142</v>
@@ -21423,7 +21423,7 @@
         <v>49.939998626709</v>
       </c>
       <c r="G726" t="n">
-        <v>46.7556343078613</v>
+        <v>46.7556419372559</v>
       </c>
       <c r="H726" t="n">
         <v>68513</v>
@@ -21568,7 +21568,7 @@
         <v>48.9199981689453</v>
       </c>
       <c r="G731" t="n">
-        <v>45.8006782531738</v>
+        <v>45.8006744384766</v>
       </c>
       <c r="H731" t="n">
         <v>25332</v>
@@ -21626,7 +21626,7 @@
         <v>47.5400009155273</v>
       </c>
       <c r="G733" t="n">
-        <v>44.508674621582</v>
+        <v>44.5086784362793</v>
       </c>
       <c r="H733" t="n">
         <v>25129</v>
@@ -21655,7 +21655,7 @@
         <v>48</v>
       </c>
       <c r="G734" t="n">
-        <v>44.939338684082</v>
+        <v>44.9393424987793</v>
       </c>
       <c r="H734" t="n">
         <v>55592</v>
@@ -21684,7 +21684,7 @@
         <v>47.5400009155273</v>
       </c>
       <c r="G735" t="n">
-        <v>44.508674621582</v>
+        <v>44.5086784362793</v>
       </c>
       <c r="H735" t="n">
         <v>46384</v>
@@ -21713,7 +21713,7 @@
         <v>48.1399993896484</v>
       </c>
       <c r="G736" t="n">
-        <v>45.0704116821289</v>
+        <v>45.0704078674316</v>
       </c>
       <c r="H736" t="n">
         <v>36799</v>
@@ -21742,7 +21742,7 @@
         <v>44.6199989318848</v>
       </c>
       <c r="G737" t="n">
-        <v>41.7748680114746</v>
+        <v>41.7748641967773</v>
       </c>
       <c r="H737" t="n">
         <v>71497</v>
@@ -21771,7 +21771,7 @@
         <v>43.6800003051758</v>
       </c>
       <c r="G738" t="n">
-        <v>40.8947982788086</v>
+        <v>40.8948020935059</v>
       </c>
       <c r="H738" t="n">
         <v>65361</v>
@@ -21800,7 +21800,7 @@
         <v>44.1599998474121</v>
       </c>
       <c r="G739" t="n">
-        <v>41.3441848754883</v>
+        <v>41.3441925048828</v>
       </c>
       <c r="H739" t="n">
         <v>70447</v>
@@ -21829,7 +21829,7 @@
         <v>45.1599998474121</v>
       </c>
       <c r="G740" t="n">
-        <v>42.2804374694824</v>
+        <v>42.2804260253906</v>
       </c>
       <c r="H740" t="n">
         <v>37759</v>
@@ -21858,7 +21858,7 @@
         <v>46.0800018310547</v>
       </c>
       <c r="G741" t="n">
-        <v>43.1417655944824</v>
+        <v>43.1417694091797</v>
       </c>
       <c r="H741" t="n">
         <v>69267</v>
@@ -21887,7 +21887,7 @@
         <v>47.060001373291</v>
       </c>
       <c r="G742" t="n">
-        <v>44.0592803955078</v>
+        <v>44.0592765808105</v>
       </c>
       <c r="H742" t="n">
         <v>20046</v>
@@ -21916,7 +21916,7 @@
         <v>46.6599998474121</v>
       </c>
       <c r="G743" t="n">
-        <v>43.6847877502441</v>
+        <v>43.6847839355469</v>
       </c>
       <c r="H743" t="n">
         <v>38526</v>
@@ -22003,7 +22003,7 @@
         <v>49.2799987792969</v>
       </c>
       <c r="G746" t="n">
-        <v>46.1377258300781</v>
+        <v>46.1377182006836</v>
       </c>
       <c r="H746" t="n">
         <v>100509</v>
@@ -22090,7 +22090,7 @@
         <v>48.7599983215332</v>
       </c>
       <c r="G749" t="n">
-        <v>45.6508750915527</v>
+        <v>45.6508827209473</v>
       </c>
       <c r="H749" t="n">
         <v>40659</v>
@@ -22119,7 +22119,7 @@
         <v>48</v>
       </c>
       <c r="G750" t="n">
-        <v>44.939338684082</v>
+        <v>44.9393424987793</v>
       </c>
       <c r="H750" t="n">
         <v>40788</v>
@@ -22148,7 +22148,7 @@
         <v>47.5999984741211</v>
       </c>
       <c r="G751" t="n">
-        <v>44.5648536682129</v>
+        <v>44.5648422241211</v>
       </c>
       <c r="H751" t="n">
         <v>51081</v>
@@ -22177,7 +22177,7 @@
         <v>47.6199989318848</v>
       </c>
       <c r="G752" t="n">
-        <v>44.5835647583008</v>
+        <v>44.583568572998</v>
       </c>
       <c r="H752" t="n">
         <v>31079</v>
@@ -22206,7 +22206,7 @@
         <v>47.7000007629395</v>
       </c>
       <c r="G753" t="n">
-        <v>44.6584739685059</v>
+        <v>44.6584663391113</v>
       </c>
       <c r="H753" t="n">
         <v>53028</v>
@@ -22322,7 +22322,7 @@
         <v>46.8600006103516</v>
       </c>
       <c r="G757" t="n">
-        <v>43.8720321655273</v>
+        <v>43.8720359802246</v>
       </c>
       <c r="H757" t="n">
         <v>49258</v>
@@ -22351,7 +22351,7 @@
         <v>45.8600006103516</v>
       </c>
       <c r="G758" t="n">
-        <v>42.9357986450195</v>
+        <v>42.9357948303223</v>
       </c>
       <c r="H758" t="n">
         <v>44101</v>
@@ -22380,7 +22380,7 @@
         <v>45.8400001525879</v>
       </c>
       <c r="G759" t="n">
-        <v>42.9170722961426</v>
+        <v>42.9170684814453</v>
       </c>
       <c r="H759" t="n">
         <v>40969</v>
@@ -22438,7 +22438,7 @@
         <v>43.7799987792969</v>
       </c>
       <c r="G761" t="n">
-        <v>40.9884262084961</v>
+        <v>40.9884300231934</v>
       </c>
       <c r="H761" t="n">
         <v>67177</v>
@@ -22496,7 +22496,7 @@
         <v>44.0800018310547</v>
       </c>
       <c r="G763" t="n">
-        <v>41.2692985534668</v>
+        <v>41.2692947387695</v>
       </c>
       <c r="H763" t="n">
         <v>33090</v>
@@ -22525,7 +22525,7 @@
         <v>44.7200012207031</v>
       </c>
       <c r="G764" t="n">
-        <v>41.8684883117676</v>
+        <v>41.8684921264648</v>
       </c>
       <c r="H764" t="n">
         <v>30052</v>
@@ -22554,7 +22554,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G765" t="n">
-        <v>39.6964225769043</v>
+        <v>39.696418762207</v>
       </c>
       <c r="H765" t="n">
         <v>62932</v>
@@ -22612,7 +22612,7 @@
         <v>45.5</v>
       </c>
       <c r="G767" t="n">
-        <v>42.598747253418</v>
+        <v>42.5987510681152</v>
       </c>
       <c r="H767" t="n">
         <v>25295</v>
@@ -22641,7 +22641,7 @@
         <v>46.3800010681152</v>
       </c>
       <c r="G768" t="n">
-        <v>43.4226417541504</v>
+        <v>43.4226379394531</v>
       </c>
       <c r="H768" t="n">
         <v>39235</v>
@@ -22670,7 +22670,7 @@
         <v>46.6800003051758</v>
       </c>
       <c r="G769" t="n">
-        <v>43.7035064697266</v>
+        <v>43.7035102844238</v>
       </c>
       <c r="H769" t="n">
         <v>23501</v>
@@ -22699,7 +22699,7 @@
         <v>46.7000007629395</v>
       </c>
       <c r="G770" t="n">
-        <v>43.722240447998</v>
+        <v>43.7222366333008</v>
       </c>
       <c r="H770" t="n">
         <v>25300</v>
@@ -22757,7 +22757,7 @@
         <v>44.7200012207031</v>
       </c>
       <c r="G772" t="n">
-        <v>41.8684883117676</v>
+        <v>41.8684921264648</v>
       </c>
       <c r="H772" t="n">
         <v>26923</v>
@@ -22786,7 +22786,7 @@
         <v>48.6599998474121</v>
       </c>
       <c r="G773" t="n">
-        <v>45.557258605957</v>
+        <v>45.5572547912598</v>
       </c>
       <c r="H773" t="n">
         <v>79190</v>
@@ -22844,7 +22844,7 @@
         <v>48.2799987792969</v>
       </c>
       <c r="G775" t="n">
-        <v>45.2014846801758</v>
+        <v>45.2014923095703</v>
       </c>
       <c r="H775" t="n">
         <v>14291</v>
@@ -22902,7 +22902,7 @@
         <v>49.5200004577637</v>
       </c>
       <c r="G777" t="n">
-        <v>46.362419128418</v>
+        <v>46.3624153137207</v>
       </c>
       <c r="H777" t="n">
         <v>23470</v>
@@ -22931,7 +22931,7 @@
         <v>48.8600006103516</v>
       </c>
       <c r="G778" t="n">
-        <v>45.7445030212402</v>
+        <v>45.7445068359375</v>
       </c>
       <c r="H778" t="n">
         <v>26792</v>
@@ -22989,7 +22989,7 @@
         <v>49.7000007629395</v>
       </c>
       <c r="G780" t="n">
-        <v>46.5309410095215</v>
+        <v>46.5309448242188</v>
       </c>
       <c r="H780" t="n">
         <v>53729</v>
@@ -23018,7 +23018,7 @@
         <v>51.7999992370605</v>
       </c>
       <c r="G781" t="n">
-        <v>48.4970397949219</v>
+        <v>48.4970359802246</v>
       </c>
       <c r="H781" t="n">
         <v>101691</v>
@@ -23047,7 +23047,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G782" t="n">
-        <v>47.7012329101562</v>
+        <v>47.7012367248535</v>
       </c>
       <c r="H782" t="n">
         <v>61793</v>
@@ -23105,7 +23105,7 @@
         <v>47.8600006103516</v>
       </c>
       <c r="G784" t="n">
-        <v>44.8082695007324</v>
+        <v>44.8082733154297</v>
       </c>
       <c r="H784" t="n">
         <v>40542</v>
@@ -23134,7 +23134,7 @@
         <v>48.4000015258789</v>
       </c>
       <c r="G785" t="n">
-        <v>45.313835144043</v>
+        <v>45.3138389587402</v>
       </c>
       <c r="H785" t="n">
         <v>28817</v>
@@ -23192,7 +23192,7 @@
         <v>48.0800018310547</v>
       </c>
       <c r="G787" t="n">
-        <v>45.0142402648926</v>
+        <v>45.0142440795898</v>
       </c>
       <c r="H787" t="n">
         <v>37371</v>
@@ -23221,7 +23221,7 @@
         <v>49.7799987792969</v>
       </c>
       <c r="G788" t="n">
-        <v>46.605842590332</v>
+        <v>46.6058387756348</v>
       </c>
       <c r="H788" t="n">
         <v>46023</v>
@@ -23279,7 +23279,7 @@
         <v>50</v>
       </c>
       <c r="G790" t="n">
-        <v>46.8118171691895</v>
+        <v>46.8118095397949</v>
       </c>
       <c r="H790" t="n">
         <v>40255</v>
@@ -23308,7 +23308,7 @@
         <v>50</v>
       </c>
       <c r="G791" t="n">
-        <v>46.8118171691895</v>
+        <v>46.8118095397949</v>
       </c>
       <c r="H791" t="n">
         <v>37787</v>
@@ -23337,7 +23337,7 @@
         <v>51.0499992370605</v>
       </c>
       <c r="G792" t="n">
-        <v>47.7948684692383</v>
+        <v>47.794864654541</v>
       </c>
       <c r="H792" t="n">
         <v>25751</v>
@@ -23424,7 +23424,7 @@
         <v>52.5499992370605</v>
       </c>
       <c r="G795" t="n">
-        <v>49.1992149353027</v>
+        <v>49.1992111206055</v>
       </c>
       <c r="H795" t="n">
         <v>36100</v>
@@ -23482,7 +23482,7 @@
         <v>53.4000015258789</v>
       </c>
       <c r="G797" t="n">
-        <v>49.9950218200684</v>
+        <v>49.9950141906738</v>
       </c>
       <c r="H797" t="n">
         <v>43781</v>
@@ -23511,7 +23511,7 @@
         <v>52.9000015258789</v>
       </c>
       <c r="G798" t="n">
-        <v>49.5269088745117</v>
+        <v>49.5268974304199</v>
       </c>
       <c r="H798" t="n">
         <v>28248</v>
@@ -23540,7 +23540,7 @@
         <v>52.5</v>
       </c>
       <c r="G799" t="n">
-        <v>49.152400970459</v>
+        <v>49.1524047851562</v>
       </c>
       <c r="H799" t="n">
         <v>49972</v>
@@ -23598,7 +23598,7 @@
         <v>53.1500015258789</v>
       </c>
       <c r="G801" t="n">
-        <v>49.7609558105469</v>
+        <v>49.7609596252441</v>
       </c>
       <c r="H801" t="n">
         <v>23652</v>
@@ -23627,7 +23627,7 @@
         <v>52.5</v>
       </c>
       <c r="G802" t="n">
-        <v>49.152400970459</v>
+        <v>49.1524047851562</v>
       </c>
       <c r="H802" t="n">
         <v>22263</v>
@@ -23656,7 +23656,7 @@
         <v>52.6500015258789</v>
       </c>
       <c r="G803" t="n">
-        <v>49.292839050293</v>
+        <v>49.2928428649902</v>
       </c>
       <c r="H803" t="n">
         <v>20978</v>
@@ -23830,7 +23830,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G809" t="n">
-        <v>53.5059051513672</v>
+        <v>53.5059013366699</v>
       </c>
       <c r="H809" t="n">
         <v>71103</v>
@@ -23917,7 +23917,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G812" t="n">
-        <v>53.5527114868164</v>
+        <v>53.5527191162109</v>
       </c>
       <c r="H812" t="n">
         <v>30716</v>
@@ -23975,7 +23975,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G814" t="n">
-        <v>52.9909706115723</v>
+        <v>52.9909744262695</v>
       </c>
       <c r="H814" t="n">
         <v>26300</v>
@@ -24004,7 +24004,7 @@
         <v>57.2000007629395</v>
       </c>
       <c r="G815" t="n">
-        <v>53.5527114868164</v>
+        <v>53.5527191162109</v>
       </c>
       <c r="H815" t="n">
         <v>42072</v>
@@ -24033,7 +24033,7 @@
         <v>58.25</v>
       </c>
       <c r="G816" t="n">
-        <v>54.535758972168</v>
+        <v>54.5357627868652</v>
       </c>
       <c r="H816" t="n">
         <v>90390</v>
@@ -24062,7 +24062,7 @@
         <v>57.2999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>53.6463432312012</v>
+        <v>53.6463394165039</v>
       </c>
       <c r="H817" t="n">
         <v>46592</v>
@@ -24120,7 +24120,7 @@
         <v>58.25</v>
       </c>
       <c r="G819" t="n">
-        <v>54.535758972168</v>
+        <v>54.5357627868652</v>
       </c>
       <c r="H819" t="n">
         <v>41257</v>
@@ -24149,7 +24149,7 @@
         <v>57.5</v>
       </c>
       <c r="G820" t="n">
-        <v>53.8335838317871</v>
+        <v>53.8335876464844</v>
       </c>
       <c r="H820" t="n">
         <v>40529</v>
@@ -24178,7 +24178,7 @@
         <v>56.5999984741211</v>
       </c>
       <c r="G821" t="n">
-        <v>52.9909706115723</v>
+        <v>52.9909744262695</v>
       </c>
       <c r="H821" t="n">
         <v>64358</v>
@@ -24207,7 +24207,7 @@
         <v>56.25</v>
       </c>
       <c r="G822" t="n">
-        <v>52.6632843017578</v>
+        <v>52.6632957458496</v>
       </c>
       <c r="H822" t="n">
         <v>66571</v>
@@ -24294,7 +24294,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G825" t="n">
-        <v>52.7100944519043</v>
+        <v>52.7100982666016</v>
       </c>
       <c r="H825" t="n">
         <v>66887</v>
@@ -24381,7 +24381,7 @@
         <v>57.7000007629395</v>
       </c>
       <c r="G828" t="n">
-        <v>54.0208282470703</v>
+        <v>54.0208358764648</v>
       </c>
       <c r="H828" t="n">
         <v>42454</v>
@@ -24439,7 +24439,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G830" t="n">
-        <v>53.4590950012207</v>
+        <v>53.4590911865234</v>
       </c>
       <c r="H830" t="n">
         <v>38509</v>
@@ -24555,7 +24555,7 @@
         <v>56.5</v>
       </c>
       <c r="G834" t="n">
-        <v>52.8973503112793</v>
+        <v>52.897346496582</v>
       </c>
       <c r="H834" t="n">
         <v>45826</v>
@@ -24584,7 +24584,7 @@
         <v>57.0999984741211</v>
       </c>
       <c r="G835" t="n">
-        <v>53.4590950012207</v>
+        <v>53.4590911865234</v>
       </c>
       <c r="H835" t="n">
         <v>40826</v>
@@ -24613,7 +24613,7 @@
         <v>57.5499992370605</v>
       </c>
       <c r="G836" t="n">
-        <v>53.8803939819336</v>
+        <v>53.8803977966309</v>
       </c>
       <c r="H836" t="n">
         <v>18493</v>
@@ -24642,7 +24642,7 @@
         <v>57.1500015258789</v>
       </c>
       <c r="G837" t="n">
-        <v>53.5059051513672</v>
+        <v>53.5059013366699</v>
       </c>
       <c r="H837" t="n">
         <v>40263</v>
@@ -24671,7 +24671,7 @@
         <v>58</v>
       </c>
       <c r="G838" t="n">
-        <v>54.3017082214355</v>
+        <v>54.3017044067383</v>
       </c>
       <c r="H838" t="n">
         <v>18394</v>
@@ -24700,7 +24700,7 @@
         <v>57.5</v>
       </c>
       <c r="G839" t="n">
-        <v>53.8335838317871</v>
+        <v>53.8335876464844</v>
       </c>
       <c r="H839" t="n">
         <v>22806</v>
@@ -24729,7 +24729,7 @@
         <v>58</v>
       </c>
       <c r="G840" t="n">
-        <v>54.3017082214355</v>
+        <v>54.3017044067383</v>
       </c>
       <c r="H840" t="n">
         <v>262996</v>
@@ -24874,7 +24874,7 @@
         <v>58.1500015258789</v>
       </c>
       <c r="G845" t="n">
-        <v>54.442138671875</v>
+        <v>54.4421424865723</v>
       </c>
       <c r="H845" t="n">
         <v>32340</v>
@@ -24903,7 +24903,7 @@
         <v>58</v>
       </c>
       <c r="G846" t="n">
-        <v>54.3017082214355</v>
+        <v>54.3017044067383</v>
       </c>
       <c r="H846" t="n">
         <v>29440</v>
@@ -24990,7 +24990,7 @@
         <v>55.9500007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>52.7843322753906</v>
+        <v>52.7843284606934</v>
       </c>
       <c r="H849" t="n">
         <v>28964</v>
@@ -25019,7 +25019,7 @@
         <v>56</v>
       </c>
       <c r="G850" t="n">
-        <v>52.8315010070801</v>
+        <v>52.8314971923828</v>
       </c>
       <c r="H850" t="n">
         <v>28610</v>
@@ -25048,7 +25048,7 @@
         <v>56</v>
       </c>
       <c r="G851" t="n">
-        <v>52.8315010070801</v>
+        <v>52.8314971923828</v>
       </c>
       <c r="H851" t="n">
         <v>15193</v>
@@ -25077,7 +25077,7 @@
         <v>55</v>
       </c>
       <c r="G852" t="n">
-        <v>51.8880805969238</v>
+        <v>51.8880844116211</v>
       </c>
       <c r="H852" t="n">
         <v>20113</v>
@@ -25106,7 +25106,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G853" t="n">
-        <v>51.7937355041504</v>
+        <v>51.7937431335449</v>
       </c>
       <c r="H853" t="n">
         <v>22219</v>
@@ -25135,7 +25135,7 @@
         <v>53.7999992370605</v>
       </c>
       <c r="G854" t="n">
-        <v>50.7559814453125</v>
+        <v>50.7559776306152</v>
       </c>
       <c r="H854" t="n">
         <v>28949</v>
@@ -25164,7 +25164,7 @@
         <v>56</v>
       </c>
       <c r="G855" t="n">
-        <v>52.8315010070801</v>
+        <v>52.8314971923828</v>
       </c>
       <c r="H855" t="n">
         <v>28556</v>
@@ -25193,7 +25193,7 @@
         <v>57</v>
       </c>
       <c r="G856" t="n">
-        <v>53.7749252319336</v>
+        <v>53.7749214172363</v>
       </c>
       <c r="H856" t="n">
         <v>56731</v>
@@ -25251,7 +25251,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G858" t="n">
-        <v>55.2843856811523</v>
+        <v>55.2843894958496</v>
       </c>
       <c r="H858" t="n">
         <v>50530</v>
@@ -25309,7 +25309,7 @@
         <v>59.3499984741211</v>
       </c>
       <c r="G860" t="n">
-        <v>55.9919509887695</v>
+        <v>55.9919548034668</v>
       </c>
       <c r="H860" t="n">
         <v>37678</v>
@@ -25338,7 +25338,7 @@
         <v>58.5499992370605</v>
       </c>
       <c r="G861" t="n">
-        <v>55.2372169494629</v>
+        <v>55.2372207641602</v>
       </c>
       <c r="H861" t="n">
         <v>35325</v>
@@ -25396,7 +25396,7 @@
         <v>58.75</v>
       </c>
       <c r="G863" t="n">
-        <v>55.4259033203125</v>
+        <v>55.425910949707</v>
       </c>
       <c r="H863" t="n">
         <v>23066</v>
@@ -25425,7 +25425,7 @@
         <v>58.4500007629395</v>
       </c>
       <c r="G864" t="n">
-        <v>55.142879486084</v>
+        <v>55.1428833007812</v>
       </c>
       <c r="H864" t="n">
         <v>20251</v>
@@ -25570,7 +25570,7 @@
         <v>57.0499992370605</v>
       </c>
       <c r="G869" t="n">
-        <v>53.8220901489258</v>
+        <v>53.8220863342285</v>
       </c>
       <c r="H869" t="n">
         <v>25444</v>
@@ -25628,7 +25628,7 @@
         <v>57.3499984741211</v>
       </c>
       <c r="G871" t="n">
-        <v>54.105110168457</v>
+        <v>54.1051139831543</v>
       </c>
       <c r="H871" t="n">
         <v>48132</v>
@@ -25657,7 +25657,7 @@
         <v>58.75</v>
       </c>
       <c r="G872" t="n">
-        <v>55.4259033203125</v>
+        <v>55.425910949707</v>
       </c>
       <c r="H872" t="n">
         <v>43806</v>
@@ -25686,7 +25686,7 @@
         <v>59.5</v>
       </c>
       <c r="G873" t="n">
-        <v>56.133472442627</v>
+        <v>56.1334686279297</v>
       </c>
       <c r="H873" t="n">
         <v>48282</v>
@@ -25715,7 +25715,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G874" t="n">
-        <v>56.039134979248</v>
+        <v>56.0391311645508</v>
       </c>
       <c r="H874" t="n">
         <v>14839</v>
@@ -25744,7 +25744,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G875" t="n">
-        <v>56.4636650085449</v>
+        <v>56.4636611938477</v>
       </c>
       <c r="H875" t="n">
         <v>19357</v>
@@ -25802,7 +25802,7 @@
         <v>59.2999992370605</v>
       </c>
       <c r="G877" t="n">
-        <v>55.9447784423828</v>
+        <v>55.9447860717773</v>
       </c>
       <c r="H877" t="n">
         <v>23509</v>
@@ -25860,7 +25860,7 @@
         <v>59.5</v>
       </c>
       <c r="G879" t="n">
-        <v>56.133472442627</v>
+        <v>56.1334686279297</v>
       </c>
       <c r="H879" t="n">
         <v>21544</v>
@@ -25918,7 +25918,7 @@
         <v>60.25</v>
       </c>
       <c r="G881" t="n">
-        <v>56.8410377502441</v>
+        <v>56.8410339355469</v>
       </c>
       <c r="H881" t="n">
         <v>26788</v>
@@ -25947,7 +25947,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G882" t="n">
-        <v>57.7372817993164</v>
+        <v>57.7372856140137</v>
       </c>
       <c r="H882" t="n">
         <v>45113</v>
@@ -26005,7 +26005,7 @@
         <v>61</v>
       </c>
       <c r="G884" t="n">
-        <v>57.5485992431641</v>
+        <v>57.5485954284668</v>
       </c>
       <c r="H884" t="n">
         <v>13974</v>
@@ -26063,7 +26063,7 @@
         <v>59.5</v>
       </c>
       <c r="G886" t="n">
-        <v>56.133472442627</v>
+        <v>56.1334686279297</v>
       </c>
       <c r="H886" t="n">
         <v>37226</v>
@@ -26150,7 +26150,7 @@
         <v>60.9500007629395</v>
       </c>
       <c r="G889" t="n">
-        <v>57.5014266967773</v>
+        <v>57.5014343261719</v>
       </c>
       <c r="H889" t="n">
         <v>31149</v>
@@ -26208,7 +26208,7 @@
         <v>62.9000015258789</v>
       </c>
       <c r="G891" t="n">
-        <v>59.3410949707031</v>
+        <v>59.3410911560059</v>
       </c>
       <c r="H891" t="n">
         <v>72248</v>
@@ -26295,7 +26295,7 @@
         <v>60.9500007629395</v>
       </c>
       <c r="G894" t="n">
-        <v>57.5014266967773</v>
+        <v>57.5014343261719</v>
       </c>
       <c r="H894" t="n">
         <v>20532</v>
@@ -26324,7 +26324,7 @@
         <v>60.9500007629395</v>
       </c>
       <c r="G895" t="n">
-        <v>57.5014266967773</v>
+        <v>57.5014343261719</v>
       </c>
       <c r="H895" t="n">
         <v>21709</v>
@@ -26353,7 +26353,7 @@
         <v>61.7999992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>58.3033409118652</v>
+        <v>58.303337097168</v>
       </c>
       <c r="H896" t="n">
         <v>23830</v>
@@ -26382,7 +26382,7 @@
         <v>61.2000007629395</v>
       </c>
       <c r="G897" t="n">
-        <v>57.7372817993164</v>
+        <v>57.7372856140137</v>
       </c>
       <c r="H897" t="n">
         <v>25905</v>
@@ -26411,7 +26411,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G898" t="n">
-        <v>56.5108337402344</v>
+        <v>56.5108413696289</v>
       </c>
       <c r="H898" t="n">
         <v>33178</v>
@@ -26440,7 +26440,7 @@
         <v>60.4500007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>57.029712677002</v>
+        <v>57.0297164916992</v>
       </c>
       <c r="H899" t="n">
         <v>20804</v>
@@ -26527,7 +26527,7 @@
         <v>59.8499984741211</v>
       </c>
       <c r="G902" t="n">
-        <v>56.4636650085449</v>
+        <v>56.4636611938477</v>
       </c>
       <c r="H902" t="n">
         <v>17769</v>
@@ -26556,7 +26556,7 @@
         <v>59.9000015258789</v>
       </c>
       <c r="G903" t="n">
-        <v>56.5108337402344</v>
+        <v>56.5108413696289</v>
       </c>
       <c r="H903" t="n">
         <v>24176</v>
@@ -26585,7 +26585,7 @@
         <v>61</v>
       </c>
       <c r="G904" t="n">
-        <v>57.5485992431641</v>
+        <v>57.5485954284668</v>
       </c>
       <c r="H904" t="n">
         <v>27602</v>
@@ -26614,7 +26614,7 @@
         <v>61.7000007629395</v>
       </c>
       <c r="G905" t="n">
-        <v>58.2089881896973</v>
+        <v>58.2089958190918</v>
       </c>
       <c r="H905" t="n">
         <v>40801</v>
@@ -26672,7 +26672,7 @@
         <v>63.0499992370605</v>
       </c>
       <c r="G907" t="n">
-        <v>59.4826126098633</v>
+        <v>59.482608795166</v>
       </c>
       <c r="H907" t="n">
         <v>40818</v>
@@ -26759,7 +26759,7 @@
         <v>60.9000015258789</v>
       </c>
       <c r="G910" t="n">
-        <v>57.4542617797852</v>
+        <v>57.4542579650879</v>
       </c>
       <c r="H910" t="n">
         <v>17983</v>
@@ -26788,7 +26788,7 @@
         <v>60.6500015258789</v>
       </c>
       <c r="G911" t="n">
-        <v>57.2183990478516</v>
+        <v>57.2184028625488</v>
       </c>
       <c r="H911" t="n">
         <v>24000</v>
@@ -26817,7 +26817,7 @@
         <v>59.4000015258789</v>
       </c>
       <c r="G912" t="n">
-        <v>56.039134979248</v>
+        <v>56.0391311645508</v>
       </c>
       <c r="H912" t="n">
         <v>90140</v>
@@ -27020,7 +27020,7 @@
         <v>52.0499992370605</v>
       </c>
       <c r="G919" t="n">
-        <v>49.1049880981445</v>
+        <v>49.1049919128418</v>
       </c>
       <c r="H919" t="n">
         <v>34144</v>
@@ -27107,7 +27107,7 @@
         <v>51.5</v>
       </c>
       <c r="G922" t="n">
-        <v>48.586109161377</v>
+        <v>48.5861129760742</v>
       </c>
       <c r="H922" t="n">
         <v>28487</v>
@@ -27136,7 +27136,7 @@
         <v>52.25</v>
       </c>
       <c r="G923" t="n">
-        <v>49.2936782836914</v>
+        <v>49.2936820983887</v>
       </c>
       <c r="H923" t="n">
         <v>33907</v>
@@ -27165,7 +27165,7 @@
         <v>52.2000007629395</v>
       </c>
       <c r="G924" t="n">
-        <v>49.2465057373047</v>
+        <v>49.246509552002</v>
       </c>
       <c r="H924" t="n">
         <v>33499</v>
@@ -27223,7 +27223,7 @@
         <v>52.0499992370605</v>
       </c>
       <c r="G926" t="n">
-        <v>49.1049880981445</v>
+        <v>49.1049919128418</v>
       </c>
       <c r="H926" t="n">
         <v>39082</v>
@@ -27281,7 +27281,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G928" t="n">
-        <v>49.3880195617676</v>
+        <v>49.3880157470703</v>
       </c>
       <c r="H928" t="n">
         <v>33560</v>
@@ -27310,7 +27310,7 @@
         <v>52.9500007629395</v>
       </c>
       <c r="G929" t="n">
-        <v>49.9540672302246</v>
+        <v>49.9540786743164</v>
       </c>
       <c r="H929" t="n">
         <v>96550</v>
@@ -27397,7 +27397,7 @@
         <v>53.75</v>
       </c>
       <c r="G932" t="n">
-        <v>50.7088088989258</v>
+        <v>50.708812713623</v>
       </c>
       <c r="H932" t="n">
         <v>27415</v>
@@ -27484,7 +27484,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G935" t="n">
-        <v>50.8031463623047</v>
+        <v>50.803150177002</v>
       </c>
       <c r="H935" t="n">
         <v>20319</v>
@@ -27513,7 +27513,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G936" t="n">
-        <v>50.0955848693848</v>
+        <v>50.0955810546875</v>
       </c>
       <c r="H936" t="n">
         <v>27794</v>
@@ -27542,7 +27542,7 @@
         <v>53.4500007629395</v>
       </c>
       <c r="G937" t="n">
-        <v>50.42578125</v>
+        <v>50.4257850646973</v>
       </c>
       <c r="H937" t="n">
         <v>40495</v>
@@ -27571,7 +27571,7 @@
         <v>53.0999984741211</v>
       </c>
       <c r="G938" t="n">
-        <v>50.0955848693848</v>
+        <v>50.0955810546875</v>
       </c>
       <c r="H938" t="n">
         <v>29269</v>
@@ -27629,7 +27629,7 @@
         <v>52.0499992370605</v>
       </c>
       <c r="G940" t="n">
-        <v>49.1049880981445</v>
+        <v>49.1049919128418</v>
       </c>
       <c r="H940" t="n">
         <v>19001</v>
@@ -27658,7 +27658,7 @@
         <v>51.5499992370605</v>
       </c>
       <c r="G941" t="n">
-        <v>48.6332893371582</v>
+        <v>48.6332817077637</v>
       </c>
       <c r="H941" t="n">
         <v>27103</v>
@@ -27687,7 +27687,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G942" t="n">
-        <v>48.7748031616211</v>
+        <v>48.7747993469238</v>
       </c>
       <c r="H942" t="n">
         <v>31490</v>
@@ -27745,7 +27745,7 @@
         <v>52.3499984741211</v>
       </c>
       <c r="G944" t="n">
-        <v>49.3880195617676</v>
+        <v>49.3880157470703</v>
       </c>
       <c r="H944" t="n">
         <v>15665</v>
@@ -27803,7 +27803,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G946" t="n">
-        <v>49.3408508300781</v>
+        <v>49.3408432006836</v>
       </c>
       <c r="H946" t="n">
         <v>22450</v>
@@ -27832,7 +27832,7 @@
         <v>52.2999992370605</v>
       </c>
       <c r="G947" t="n">
-        <v>49.3408508300781</v>
+        <v>49.3408432006836</v>
       </c>
       <c r="H947" t="n">
         <v>18724</v>
@@ -27890,7 +27890,7 @@
         <v>51.5499992370605</v>
       </c>
       <c r="G949" t="n">
-        <v>48.6332893371582</v>
+        <v>48.6332817077637</v>
       </c>
       <c r="H949" t="n">
         <v>14968</v>
@@ -27948,7 +27948,7 @@
         <v>51.5999984741211</v>
       </c>
       <c r="G951" t="n">
-        <v>48.6804542541504</v>
+        <v>48.6804504394531</v>
       </c>
       <c r="H951" t="n">
         <v>21518</v>
@@ -27977,7 +27977,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G952" t="n">
-        <v>50.8031463623047</v>
+        <v>50.803150177002</v>
       </c>
       <c r="H952" t="n">
         <v>40266</v>
@@ -28006,7 +28006,7 @@
         <v>53.8499984741211</v>
       </c>
       <c r="G953" t="n">
-        <v>50.8031463623047</v>
+        <v>50.803150177002</v>
       </c>
       <c r="H953" t="n">
         <v>60997</v>
@@ -28064,7 +28064,7 @@
         <v>55.8499984741211</v>
       </c>
       <c r="G955" t="n">
-        <v>52.6899909973145</v>
+        <v>52.6899871826172</v>
       </c>
       <c r="H955" t="n">
         <v>191296</v>
@@ -28093,7 +28093,7 @@
         <v>55.9500007629395</v>
       </c>
       <c r="G956" t="n">
-        <v>52.7843322753906</v>
+        <v>52.7843284606934</v>
       </c>
       <c r="H956" t="n">
         <v>70748</v>
@@ -28151,7 +28151,7 @@
         <v>56.6500015258789</v>
       </c>
       <c r="G958" t="n">
-        <v>53.4447288513184</v>
+        <v>53.4447212219238</v>
       </c>
       <c r="H958" t="n">
         <v>24110</v>
@@ -28180,7 +28180,7 @@
         <v>56</v>
       </c>
       <c r="G959" t="n">
-        <v>52.8315010070801</v>
+        <v>52.8314971923828</v>
       </c>
       <c r="H959" t="n">
         <v>22899</v>
@@ -28209,7 +28209,7 @@
         <v>55.5</v>
       </c>
       <c r="G960" t="n">
-        <v>52.3597869873047</v>
+        <v>52.359790802002</v>
       </c>
       <c r="H960" t="n">
         <v>40298</v>
@@ -28238,7 +28238,7 @@
         <v>54.8499984741211</v>
       </c>
       <c r="G961" t="n">
-        <v>51.7465705871582</v>
+        <v>51.7465629577637</v>
       </c>
       <c r="H961" t="n">
         <v>31824</v>
@@ -28267,7 +28267,7 @@
         <v>55.5</v>
       </c>
       <c r="G962" t="n">
-        <v>52.3597869873047</v>
+        <v>52.359790802002</v>
       </c>
       <c r="H962" t="n">
         <v>37836</v>
@@ -28296,7 +28296,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>52.5484733581543</v>
+        <v>52.5484771728516</v>
       </c>
       <c r="H963" t="n">
         <v>27666</v>
@@ -28354,7 +28354,7 @@
         <v>57.4000015258789</v>
       </c>
       <c r="G965" t="n">
-        <v>54.1522941589355</v>
+        <v>54.1522903442383</v>
       </c>
       <c r="H965" t="n">
         <v>134439</v>
@@ -28383,7 +28383,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G966" t="n">
-        <v>53.5862350463867</v>
+        <v>53.5862426757812</v>
       </c>
       <c r="H966" t="n">
         <v>62465</v>
@@ -28412,7 +28412,7 @@
         <v>56.2999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>53.1145210266113</v>
+        <v>53.1145248413086</v>
       </c>
       <c r="H967" t="n">
         <v>32364</v>
@@ -28499,7 +28499,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G970" t="n">
-        <v>53.5862350463867</v>
+        <v>53.5862426757812</v>
       </c>
       <c r="H970" t="n">
         <v>27011</v>
@@ -28528,7 +28528,7 @@
         <v>58.5999984741211</v>
       </c>
       <c r="G971" t="n">
-        <v>55.2843856811523</v>
+        <v>55.2843894958496</v>
       </c>
       <c r="H971" t="n">
         <v>138132</v>
@@ -28702,7 +28702,7 @@
         <v>59.0999984741211</v>
       </c>
       <c r="G977" t="n">
-        <v>55.7560997009277</v>
+        <v>55.7560958862305</v>
       </c>
       <c r="H977" t="n">
         <v>18223</v>
@@ -28789,7 +28789,7 @@
         <v>60.9500007629395</v>
       </c>
       <c r="G980" t="n">
-        <v>57.5014266967773</v>
+        <v>57.5014343261719</v>
       </c>
       <c r="H980" t="n">
         <v>63510</v>
@@ -28818,7 +28818,7 @@
         <v>61.0499992370605</v>
       </c>
       <c r="G981" t="n">
-        <v>57.5957717895508</v>
+        <v>57.5957679748535</v>
       </c>
       <c r="H981" t="n">
         <v>82732</v>
@@ -28847,7 +28847,7 @@
         <v>60.7000007629395</v>
       </c>
       <c r="G982" t="n">
-        <v>57.2655715942383</v>
+        <v>57.2655754089355</v>
       </c>
       <c r="H982" t="n">
         <v>29187</v>
@@ -28934,7 +28934,7 @@
         <v>62</v>
       </c>
       <c r="G985" t="n">
-        <v>58.492015838623</v>
+        <v>58.4920196533203</v>
       </c>
       <c r="H985" t="n">
         <v>36334</v>
@@ -28963,7 +28963,7 @@
         <v>65.6999969482422</v>
       </c>
       <c r="G986" t="n">
-        <v>61.9826736450195</v>
+        <v>61.982666015625</v>
       </c>
       <c r="H986" t="n">
         <v>161493</v>
@@ -28992,7 +28992,7 @@
         <v>66.5</v>
       </c>
       <c r="G987" t="n">
-        <v>62.7374076843262</v>
+        <v>62.7374114990234</v>
       </c>
       <c r="H987" t="n">
         <v>135969</v>
@@ -29195,7 +29195,7 @@
         <v>72.4000015258789</v>
       </c>
       <c r="G994" t="n">
-        <v>68.3035888671875</v>
+        <v>68.303581237793</v>
       </c>
       <c r="H994" t="n">
         <v>162485</v>
@@ -29224,7 +29224,7 @@
         <v>72.1999969482422</v>
       </c>
       <c r="G995" t="n">
-        <v>68.1149063110352</v>
+        <v>68.1148986816406</v>
       </c>
       <c r="H995" t="n">
         <v>104122</v>
@@ -29253,7 +29253,7 @@
         <v>70.4499969482422</v>
       </c>
       <c r="G996" t="n">
-        <v>66.4639129638672</v>
+        <v>66.4639053344727</v>
       </c>
       <c r="H996" t="n">
         <v>97242</v>
@@ -29282,7 +29282,7 @@
         <v>71.0999984741211</v>
       </c>
       <c r="G997" t="n">
-        <v>67.0771331787109</v>
+        <v>67.0771408081055</v>
       </c>
       <c r="H997" t="n">
         <v>57537</v>
@@ -29340,7 +29340,7 @@
         <v>70.3499984741211</v>
       </c>
       <c r="G999" t="n">
-        <v>66.3695678710938</v>
+        <v>66.3695755004883</v>
       </c>
       <c r="H999" t="n">
         <v>52442</v>
@@ -29369,7 +29369,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G1000" t="n">
-        <v>66.6054229736328</v>
+        <v>66.6054153442383</v>
       </c>
       <c r="H1000" t="n">
         <v>77699</v>
@@ -29427,7 +29427,7 @@
         <v>72.3499984741211</v>
       </c>
       <c r="G1002" t="n">
-        <v>68.2564086914062</v>
+        <v>68.2564010620117</v>
       </c>
       <c r="H1002" t="n">
         <v>31557</v>
@@ -29456,7 +29456,7 @@
         <v>71.5500030517578</v>
       </c>
       <c r="G1003" t="n">
-        <v>67.5016860961914</v>
+        <v>67.5016784667969</v>
       </c>
       <c r="H1003" t="n">
         <v>27979</v>
@@ -29485,7 +29485,7 @@
         <v>70.9499969482422</v>
       </c>
       <c r="G1004" t="n">
-        <v>66.9356155395508</v>
+        <v>66.9356231689453</v>
       </c>
       <c r="H1004" t="n">
         <v>32158</v>
@@ -29543,7 +29543,7 @@
         <v>70.0999984741211</v>
       </c>
       <c r="G1006" t="n">
-        <v>66.1337203979492</v>
+        <v>66.1337127685547</v>
       </c>
       <c r="H1006" t="n">
         <v>26257</v>
@@ -29659,7 +29659,7 @@
         <v>68.9000015258789</v>
       </c>
       <c r="G1010" t="n">
-        <v>65.0016021728516</v>
+        <v>65.0016174316406</v>
       </c>
       <c r="H1010" t="n">
         <v>43949</v>
@@ -29717,7 +29717,7 @@
         <v>71.0999984741211</v>
       </c>
       <c r="G1012" t="n">
-        <v>67.0771331787109</v>
+        <v>67.0771408081055</v>
       </c>
       <c r="H1012" t="n">
         <v>60937</v>
@@ -29746,7 +29746,7 @@
         <v>70.9000015258789</v>
       </c>
       <c r="G1013" t="n">
-        <v>66.8884582519531</v>
+        <v>66.8884506225586</v>
       </c>
       <c r="H1013" t="n">
         <v>17568</v>
@@ -29775,7 +29775,7 @@
         <v>70.6999969482422</v>
       </c>
       <c r="G1014" t="n">
-        <v>66.6997680664062</v>
+        <v>66.6997604370117</v>
       </c>
       <c r="H1014" t="n">
         <v>18729</v>
@@ -29949,7 +29949,7 @@
         <v>69.0999984741211</v>
       </c>
       <c r="G1020" t="n">
-        <v>65.1903076171875</v>
+        <v>65.190299987793</v>
       </c>
       <c r="H1020" t="n">
         <v>51956</v>
@@ -29978,7 +29978,7 @@
         <v>70.9000015258789</v>
       </c>
       <c r="G1021" t="n">
-        <v>66.8884582519531</v>
+        <v>66.8884506225586</v>
       </c>
       <c r="H1021" t="n">
         <v>39631</v>
@@ -30007,7 +30007,7 @@
         <v>72.5999984741211</v>
       </c>
       <c r="G1022" t="n">
-        <v>68.4922637939453</v>
+        <v>68.4922714233398</v>
       </c>
       <c r="H1022" t="n">
         <v>40800</v>
@@ -30036,7 +30036,7 @@
         <v>72.1999969482422</v>
       </c>
       <c r="G1023" t="n">
-        <v>68.1149063110352</v>
+        <v>68.1148986816406</v>
       </c>
       <c r="H1023" t="n">
         <v>23475</v>
@@ -30065,7 +30065,7 @@
         <v>70.6999969482422</v>
       </c>
       <c r="G1024" t="n">
-        <v>66.6997680664062</v>
+        <v>66.6997604370117</v>
       </c>
       <c r="H1024" t="n">
         <v>23429</v>
@@ -30094,7 +30094,7 @@
         <v>70.9499969482422</v>
       </c>
       <c r="G1025" t="n">
-        <v>66.9356155395508</v>
+        <v>66.9356231689453</v>
       </c>
       <c r="H1025" t="n">
         <v>20158</v>
@@ -30123,7 +30123,7 @@
         <v>71.3000030517578</v>
       </c>
       <c r="G1026" t="n">
-        <v>67.2658309936523</v>
+        <v>67.2658233642578</v>
       </c>
       <c r="H1026" t="n">
         <v>12150</v>
@@ -30268,7 +30268,7 @@
         <v>77</v>
       </c>
       <c r="G1031" t="n">
-        <v>72.6433181762695</v>
+        <v>72.643310546875</v>
       </c>
       <c r="H1031" t="n">
         <v>20061</v>
@@ -30297,7 +30297,7 @@
         <v>76.6999969482422</v>
       </c>
       <c r="G1032" t="n">
-        <v>72.3602905273438</v>
+        <v>72.3602981567383</v>
       </c>
       <c r="H1032" t="n">
         <v>42595</v>
@@ -30326,7 +30326,7 @@
         <v>73.9000015258789</v>
       </c>
       <c r="G1033" t="n">
-        <v>69.7187194824219</v>
+        <v>69.7187118530273</v>
       </c>
       <c r="H1033" t="n">
         <v>33184</v>
@@ -30355,7 +30355,7 @@
         <v>74</v>
       </c>
       <c r="G1034" t="n">
-        <v>69.8130569458008</v>
+        <v>69.8130645751953</v>
       </c>
       <c r="H1034" t="n">
         <v>34952</v>
@@ -30384,7 +30384,7 @@
         <v>75.75</v>
       </c>
       <c r="G1035" t="n">
-        <v>71.4640502929688</v>
+        <v>71.4640350341797</v>
       </c>
       <c r="H1035" t="n">
         <v>31524</v>
@@ -30413,7 +30413,7 @@
         <v>73.4499969482422</v>
       </c>
       <c r="G1036" t="n">
-        <v>69.2941665649414</v>
+        <v>69.2941589355469</v>
       </c>
       <c r="H1036" t="n">
         <v>38947</v>
@@ -30471,7 +30471,7 @@
         <v>71.75</v>
       </c>
       <c r="G1038" t="n">
-        <v>67.6903610229492</v>
+        <v>67.6903533935547</v>
       </c>
       <c r="H1038" t="n">
         <v>80045</v>
@@ -30529,7 +30529,7 @@
         <v>75.1999969482422</v>
       </c>
       <c r="G1040" t="n">
-        <v>70.9451599121094</v>
+        <v>70.9451446533203</v>
       </c>
       <c r="H1040" t="n">
         <v>48601</v>
@@ -30558,7 +30558,7 @@
         <v>76</v>
       </c>
       <c r="G1041" t="n">
-        <v>71.6998977661133</v>
+        <v>71.6998825073242</v>
       </c>
       <c r="H1041" t="n">
         <v>18010</v>
@@ -30587,7 +30587,7 @@
         <v>76.0500030517578</v>
       </c>
       <c r="G1042" t="n">
-        <v>71.7470703125</v>
+        <v>71.7470855712891</v>
       </c>
       <c r="H1042" t="n">
         <v>21473</v>
@@ -30616,7 +30616,7 @@
         <v>75.9000015258789</v>
       </c>
       <c r="G1043" t="n">
-        <v>71.6055450439453</v>
+        <v>71.6055603027344</v>
       </c>
       <c r="H1043" t="n">
         <v>64644</v>
@@ -30703,7 +30703,7 @@
         <v>77.5</v>
       </c>
       <c r="G1046" t="n">
-        <v>73.1150360107422</v>
+        <v>73.1150207519531</v>
       </c>
       <c r="H1046" t="n">
         <v>41515</v>
@@ -30732,7 +30732,7 @@
         <v>76.0500030517578</v>
       </c>
       <c r="G1047" t="n">
-        <v>71.7470703125</v>
+        <v>71.7470855712891</v>
       </c>
       <c r="H1047" t="n">
         <v>32585</v>
@@ -30790,7 +30790,7 @@
         <v>75.25</v>
       </c>
       <c r="G1049" t="n">
-        <v>70.9923324584961</v>
+        <v>70.9923400878906</v>
       </c>
       <c r="H1049" t="n">
         <v>31929</v>
@@ -30848,7 +30848,7 @@
         <v>75.1999969482422</v>
       </c>
       <c r="G1051" t="n">
-        <v>70.9451599121094</v>
+        <v>70.9451446533203</v>
       </c>
       <c r="H1051" t="n">
         <v>28155</v>
@@ -30877,7 +30877,7 @@
         <v>74.6500015258789</v>
       </c>
       <c r="G1052" t="n">
-        <v>70.4262771606445</v>
+        <v>70.4262847900391</v>
       </c>
       <c r="H1052" t="n">
         <v>22880</v>
@@ -30906,7 +30906,7 @@
         <v>69.0999984741211</v>
       </c>
       <c r="G1053" t="n">
-        <v>65.1903076171875</v>
+        <v>65.190299987793</v>
       </c>
       <c r="H1053" t="n">
         <v>134769</v>
@@ -30935,7 +30935,7 @@
         <v>69.8499984741211</v>
       </c>
       <c r="G1054" t="n">
-        <v>65.8978652954102</v>
+        <v>65.8978729248047</v>
       </c>
       <c r="H1054" t="n">
         <v>92573</v>
@@ -30964,7 +30964,7 @@
         <v>70.0999984741211</v>
       </c>
       <c r="G1055" t="n">
-        <v>66.1337203979492</v>
+        <v>66.1337127685547</v>
       </c>
       <c r="H1055" t="n">
         <v>69386</v>
@@ -30993,7 +30993,7 @@
         <v>68.6999969482422</v>
       </c>
       <c r="G1056" t="n">
-        <v>64.8129348754883</v>
+        <v>64.8129272460938</v>
       </c>
       <c r="H1056" t="n">
         <v>83199</v>
@@ -31051,7 +31051,7 @@
         <v>64.9499969482422</v>
       </c>
       <c r="G1058" t="n">
-        <v>61.2751045227051</v>
+        <v>61.2751083374023</v>
       </c>
       <c r="H1058" t="n">
         <v>148576</v>
@@ -31080,7 +31080,7 @@
         <v>66.6999969482422</v>
       </c>
       <c r="G1059" t="n">
-        <v>62.9260940551758</v>
+        <v>62.9260902404785</v>
       </c>
       <c r="H1059" t="n">
         <v>105402</v>
@@ -31109,7 +31109,7 @@
         <v>64.6999969482422</v>
       </c>
       <c r="G1060" t="n">
-        <v>61.0392456054688</v>
+        <v>61.039249420166</v>
       </c>
       <c r="H1060" t="n">
         <v>49995</v>
@@ -31138,7 +31138,7 @@
         <v>63.7000007629395</v>
       </c>
       <c r="G1061" t="n">
-        <v>60.095832824707</v>
+        <v>60.0958290100098</v>
       </c>
       <c r="H1061" t="n">
         <v>32171</v>
@@ -31167,7 +31167,7 @@
         <v>60.5</v>
       </c>
       <c r="G1062" t="n">
-        <v>57.0768890380859</v>
+        <v>57.0768852233887</v>
       </c>
       <c r="H1062" t="n">
         <v>93684</v>
@@ -31196,7 +31196,7 @@
         <v>56.7999992370605</v>
       </c>
       <c r="G1063" t="n">
-        <v>53.5862350463867</v>
+        <v>53.5862426757812</v>
       </c>
       <c r="H1063" t="n">
         <v>111098</v>
@@ -31283,7 +31283,7 @@
         <v>48.4799995422363</v>
       </c>
       <c r="G1066" t="n">
-        <v>45.7369842529297</v>
+        <v>45.7369766235352</v>
       </c>
       <c r="H1066" t="n">
         <v>115849</v>
@@ -31312,7 +31312,7 @@
         <v>50.9500007629395</v>
       </c>
       <c r="G1067" t="n">
-        <v>48.0672264099121</v>
+        <v>48.0672302246094</v>
       </c>
       <c r="H1067" t="n">
         <v>144399</v>
@@ -31486,7 +31486,7 @@
         <v>47.4000015258789</v>
       </c>
       <c r="G1073" t="n">
-        <v>44.7180938720703</v>
+        <v>44.718090057373</v>
       </c>
       <c r="H1073" t="n">
         <v>86279</v>
@@ -31515,7 +31515,7 @@
         <v>49.2400016784668</v>
       </c>
       <c r="G1074" t="n">
-        <v>46.4539833068848</v>
+        <v>46.453987121582</v>
       </c>
       <c r="H1074" t="n">
         <v>66177</v>
@@ -31573,7 +31573,7 @@
         <v>54.9000015258789</v>
       </c>
       <c r="G1076" t="n">
-        <v>51.7937355041504</v>
+        <v>51.7937431335449</v>
       </c>
       <c r="H1076" t="n">
         <v>113512</v>
@@ -31602,7 +31602,7 @@
         <v>51.4500007629395</v>
       </c>
       <c r="G1077" t="n">
-        <v>48.5389366149902</v>
+        <v>48.5389404296875</v>
       </c>
       <c r="H1077" t="n">
         <v>134477</v>
@@ -31631,7 +31631,7 @@
         <v>51.7000007629395</v>
       </c>
       <c r="G1078" t="n">
-        <v>48.7748031616211</v>
+        <v>48.7747993469238</v>
       </c>
       <c r="H1078" t="n">
         <v>64601</v>
@@ -31660,7 +31660,7 @@
         <v>55.7000007629395</v>
       </c>
       <c r="G1079" t="n">
-        <v>52.5484733581543</v>
+        <v>52.5484771728516</v>
       </c>
       <c r="H1079" t="n">
         <v>114435</v>
@@ -31718,7 +31718,7 @@
         <v>60.4500007629395</v>
       </c>
       <c r="G1081" t="n">
-        <v>57.029712677002</v>
+        <v>57.0297164916992</v>
       </c>
       <c r="H1081" t="n">
         <v>103176</v>
@@ -31805,7 +31805,7 @@
         <v>60.2999992370605</v>
       </c>
       <c r="G1084" t="n">
-        <v>56.8882064819336</v>
+        <v>56.8882026672363</v>
       </c>
       <c r="H1084" t="n">
         <v>85056</v>
@@ -31834,7 +31834,7 @@
         <v>60.9500007629395</v>
       </c>
       <c r="G1085" t="n">
-        <v>57.5014266967773</v>
+        <v>57.5014343261719</v>
       </c>
       <c r="H1085" t="n">
         <v>15150</v>
@@ -31863,7 +31863,7 @@
         <v>61.9500007629395</v>
       </c>
       <c r="G1086" t="n">
-        <v>58.4448509216309</v>
+        <v>58.4448471069336</v>
       </c>
       <c r="H1086" t="n">
         <v>21820</v>
@@ -31921,7 +31921,7 @@
         <v>63.0999984741211</v>
       </c>
       <c r="G1088" t="n">
-        <v>59.5297813415527</v>
+        <v>59.5297775268555</v>
       </c>
       <c r="H1088" t="n">
         <v>53453</v>
@@ -31979,7 +31979,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1090" t="n">
-        <v>60.5675392150879</v>
+        <v>60.5675430297852</v>
       </c>
       <c r="H1090" t="n">
         <v>43522</v>
@@ -32037,7 +32037,7 @@
         <v>66.4000015258789</v>
       </c>
       <c r="G1092" t="n">
-        <v>62.6430702209473</v>
+        <v>62.6430740356445</v>
       </c>
       <c r="H1092" t="n">
         <v>27178</v>
@@ -32066,7 +32066,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G1093" t="n">
-        <v>61.699649810791</v>
+        <v>61.6996421813965</v>
       </c>
       <c r="H1093" t="n">
         <v>46772</v>
@@ -32095,7 +32095,7 @@
         <v>65.4000015258789</v>
       </c>
       <c r="G1094" t="n">
-        <v>61.699649810791</v>
+        <v>61.6996421813965</v>
       </c>
       <c r="H1094" t="n">
         <v>31106</v>
@@ -32124,7 +32124,7 @@
         <v>64.1999969482422</v>
       </c>
       <c r="G1095" t="n">
-        <v>60.5675392150879</v>
+        <v>60.5675430297852</v>
       </c>
       <c r="H1095" t="n">
         <v>17419</v>
@@ -32182,7 +32182,7 @@
         <v>65.9000015258789</v>
       </c>
       <c r="G1097" t="n">
-        <v>62.1713600158691</v>
+        <v>62.1713638305664</v>
       </c>
       <c r="H1097" t="n">
         <v>26815</v>
@@ -32211,7 +32211,7 @@
         <v>64.8000030517578</v>
       </c>
       <c r="G1098" t="n">
-        <v>61.1335945129395</v>
+        <v>61.1335983276367</v>
       </c>
       <c r="H1098" t="n">
         <v>37170</v>
@@ -32269,7 +32269,7 @@
         <v>61.4500007629395</v>
       </c>
       <c r="G1100" t="n">
-        <v>58.4495277404785</v>
+        <v>58.4495315551758</v>
       </c>
       <c r="H1100" t="n">
         <v>44442</v>
@@ -32298,7 +32298,7 @@
         <v>63.1500015258789</v>
       </c>
       <c r="G1101" t="n">
-        <v>60.0665245056152</v>
+        <v>60.0665283203125</v>
       </c>
       <c r="H1101" t="n">
         <v>31448</v>
@@ -32327,7 +32327,7 @@
         <v>64</v>
       </c>
       <c r="G1102" t="n">
-        <v>60.8750152587891</v>
+        <v>60.8750190734863</v>
       </c>
       <c r="H1102" t="n">
         <v>64201</v>
@@ -32356,7 +32356,7 @@
         <v>66.0500030517578</v>
       </c>
       <c r="G1103" t="n">
-        <v>62.8249244689941</v>
+        <v>62.8249282836914</v>
       </c>
       <c r="H1103" t="n">
         <v>52511</v>
@@ -32385,7 +32385,7 @@
         <v>67.0999984741211</v>
       </c>
       <c r="G1104" t="n">
-        <v>63.8236427307129</v>
+        <v>63.8236503601074</v>
       </c>
       <c r="H1104" t="n">
         <v>31485</v>
@@ -32414,7 +32414,7 @@
         <v>65.6999969482422</v>
       </c>
       <c r="G1105" t="n">
-        <v>62.4920120239258</v>
+        <v>62.4920082092285</v>
       </c>
       <c r="H1105" t="n">
         <v>38774</v>
@@ -32443,7 +32443,7 @@
         <v>66</v>
       </c>
       <c r="G1106" t="n">
-        <v>62.7773628234863</v>
+        <v>62.7773590087891</v>
       </c>
       <c r="H1106" t="n">
         <v>33891</v>
@@ -32472,7 +32472,7 @@
         <v>66.4499969482422</v>
       </c>
       <c r="G1107" t="n">
-        <v>63.2053871154785</v>
+        <v>63.2053833007812</v>
       </c>
       <c r="H1107" t="n">
         <v>32281</v>
@@ -32501,7 +32501,7 @@
         <v>66.8000030517578</v>
       </c>
       <c r="G1108" t="n">
-        <v>63.5382995605469</v>
+        <v>63.5382957458496</v>
       </c>
       <c r="H1108" t="n">
         <v>46954</v>
@@ -32588,7 +32588,7 @@
         <v>70.5999984741211</v>
       </c>
       <c r="G1111" t="n">
-        <v>67.1527481079102</v>
+        <v>67.1527404785156</v>
       </c>
       <c r="H1111" t="n">
         <v>61474</v>
@@ -32675,7 +32675,7 @@
         <v>72.5500030517578</v>
       </c>
       <c r="G1114" t="n">
-        <v>69.0075378417969</v>
+        <v>69.0075454711914</v>
       </c>
       <c r="H1114" t="n">
         <v>44703</v>
@@ -32762,7 +32762,7 @@
         <v>76.6500015258789</v>
       </c>
       <c r="G1117" t="n">
-        <v>72.907341003418</v>
+        <v>72.9073486328125</v>
       </c>
       <c r="H1117" t="n">
         <v>96724</v>
@@ -32878,7 +32878,7 @@
         <v>74.5</v>
       </c>
       <c r="G1121" t="n">
-        <v>70.8623199462891</v>
+        <v>70.8623275756836</v>
       </c>
       <c r="H1121" t="n">
         <v>403248</v>
@@ -32907,7 +32907,7 @@
         <v>73.1999969482422</v>
       </c>
       <c r="G1122" t="n">
-        <v>69.6257934570312</v>
+        <v>69.6258010864258</v>
       </c>
       <c r="H1122" t="n">
         <v>111896</v>
@@ -32936,7 +32936,7 @@
         <v>73.75</v>
       </c>
       <c r="G1123" t="n">
-        <v>70.1489410400391</v>
+        <v>70.1489486694336</v>
       </c>
       <c r="H1123" t="n">
         <v>86823</v>
@@ -32965,7 +32965,7 @@
         <v>72.8000030517578</v>
       </c>
       <c r="G1124" t="n">
-        <v>69.2453384399414</v>
+        <v>69.2453308105469</v>
       </c>
       <c r="H1124" t="n">
         <v>106182</v>
@@ -33081,7 +33081,7 @@
         <v>67.25</v>
       </c>
       <c r="G1128" t="n">
-        <v>63.9663314819336</v>
+        <v>63.9663276672363</v>
       </c>
       <c r="H1128" t="n">
         <v>127674</v>
@@ -33139,7 +33139,7 @@
         <v>69.8000030517578</v>
       </c>
       <c r="G1130" t="n">
-        <v>66.3918228149414</v>
+        <v>66.3918151855469</v>
       </c>
       <c r="H1130" t="n">
         <v>49444</v>
@@ -33168,7 +33168,7 @@
         <v>72.5</v>
       </c>
       <c r="G1131" t="n">
-        <v>68.9599838256836</v>
+        <v>68.9599761962891</v>
       </c>
       <c r="H1131" t="n">
         <v>111867</v>
@@ -33197,7 +33197,7 @@
         <v>73.8000030517578</v>
       </c>
       <c r="G1132" t="n">
-        <v>70.1965103149414</v>
+        <v>70.1965179443359</v>
       </c>
       <c r="H1132" t="n">
         <v>84684</v>
@@ -33226,7 +33226,7 @@
         <v>73</v>
       </c>
       <c r="G1133" t="n">
-        <v>69.4355621337891</v>
+        <v>69.4355773925781</v>
       </c>
       <c r="H1133" t="n">
         <v>42121</v>
@@ -33255,7 +33255,7 @@
         <v>74</v>
       </c>
       <c r="G1134" t="n">
-        <v>70.3867416381836</v>
+        <v>70.3867492675781</v>
       </c>
       <c r="H1134" t="n">
         <v>72530</v>
@@ -33284,7 +33284,7 @@
         <v>72.0500030517578</v>
       </c>
       <c r="G1135" t="n">
-        <v>68.5319519042969</v>
+        <v>68.5319595336914</v>
       </c>
       <c r="H1135" t="n">
         <v>60116</v>
@@ -33342,7 +33342,7 @@
         <v>71.0500030517578</v>
       </c>
       <c r="G1137" t="n">
-        <v>67.5807723999023</v>
+        <v>67.5807876586914</v>
       </c>
       <c r="H1137" t="n">
         <v>31591</v>
@@ -33400,7 +33400,7 @@
         <v>71.1999969482422</v>
       </c>
       <c r="G1139" t="n">
-        <v>67.7234649658203</v>
+        <v>67.7234497070312</v>
       </c>
       <c r="H1139" t="n">
         <v>62066</v>
@@ -33429,7 +33429,7 @@
         <v>71.5500030517578</v>
       </c>
       <c r="G1140" t="n">
-        <v>68.0563735961914</v>
+        <v>68.0563659667969</v>
       </c>
       <c r="H1140" t="n">
         <v>36902</v>
@@ -33487,7 +33487,7 @@
         <v>72.5500030517578</v>
       </c>
       <c r="G1142" t="n">
-        <v>69.0075378417969</v>
+        <v>69.0075454711914</v>
       </c>
       <c r="H1142" t="n">
         <v>31472</v>
@@ -33545,7 +33545,7 @@
         <v>73.9000015258789</v>
       </c>
       <c r="G1144" t="n">
-        <v>70.2916259765625</v>
+        <v>70.291618347168</v>
       </c>
       <c r="H1144" t="n">
         <v>29054</v>
@@ -33603,7 +33603,7 @@
         <v>74.4499969482422</v>
       </c>
       <c r="G1146" t="n">
-        <v>70.8147583007812</v>
+        <v>70.8147659301758</v>
       </c>
       <c r="H1146" t="n">
         <v>30606</v>
@@ -33632,7 +33632,7 @@
         <v>72.75</v>
       </c>
       <c r="G1147" t="n">
-        <v>69.1977767944336</v>
+        <v>69.1977691650391</v>
       </c>
       <c r="H1147" t="n">
         <v>45969</v>
@@ -33777,7 +33777,7 @@
         <v>75</v>
       </c>
       <c r="G1152" t="n">
-        <v>71.3379135131836</v>
+        <v>71.3379058837891</v>
       </c>
       <c r="H1152" t="n">
         <v>47210</v>
@@ -33806,7 +33806,7 @@
         <v>74</v>
       </c>
       <c r="G1153" t="n">
-        <v>70.3867416381836</v>
+        <v>70.3867492675781</v>
       </c>
       <c r="H1153" t="n">
         <v>20858</v>
@@ -33835,7 +33835,7 @@
         <v>74.4499969482422</v>
       </c>
       <c r="G1154" t="n">
-        <v>70.8147583007812</v>
+        <v>70.8147659301758</v>
       </c>
       <c r="H1154" t="n">
         <v>34725</v>
@@ -33922,7 +33922,7 @@
         <v>76.1500015258789</v>
       </c>
       <c r="G1157" t="n">
-        <v>72.431755065918</v>
+        <v>72.4317474365234</v>
       </c>
       <c r="H1157" t="n">
         <v>26682</v>
@@ -33951,7 +33951,7 @@
         <v>76.25</v>
       </c>
       <c r="G1158" t="n">
-        <v>72.5268630981445</v>
+        <v>72.5268707275391</v>
       </c>
       <c r="H1158" t="n">
         <v>21013</v>
@@ -33980,7 +33980,7 @@
         <v>74.6500015258789</v>
       </c>
       <c r="G1159" t="n">
-        <v>71.004997253418</v>
+        <v>71.0050048828125</v>
       </c>
       <c r="H1159" t="n">
         <v>48521</v>
@@ -34009,7 +34009,7 @@
         <v>75.75</v>
       </c>
       <c r="G1160" t="n">
-        <v>72.0513000488281</v>
+        <v>72.0512847900391</v>
       </c>
       <c r="H1160" t="n">
         <v>31215</v>
@@ -34038,7 +34038,7 @@
         <v>76.4000015258789</v>
       </c>
       <c r="G1161" t="n">
-        <v>72.669563293457</v>
+        <v>72.6695556640625</v>
       </c>
       <c r="H1161" t="n">
         <v>41956</v>
@@ -34125,7 +34125,7 @@
         <v>77.5</v>
       </c>
       <c r="G1164" t="n">
-        <v>73.7158508300781</v>
+        <v>73.7158432006836</v>
       </c>
       <c r="H1164" t="n">
         <v>95607</v>
@@ -34154,7 +34154,7 @@
         <v>84.9499969482422</v>
       </c>
       <c r="G1165" t="n">
-        <v>80.8020629882812</v>
+        <v>80.8020706176758</v>
       </c>
       <c r="H1165" t="n">
         <v>138543</v>
@@ -34183,7 +34183,7 @@
         <v>86</v>
       </c>
       <c r="G1166" t="n">
-        <v>81.8007965087891</v>
+        <v>81.8008041381836</v>
       </c>
       <c r="H1166" t="n">
         <v>119038</v>
@@ -34212,7 +34212,7 @@
         <v>88.25</v>
       </c>
       <c r="G1167" t="n">
-        <v>83.9409484863281</v>
+        <v>83.9409561157227</v>
       </c>
       <c r="H1167" t="n">
         <v>76111</v>
@@ -34299,7 +34299,7 @@
         <v>86.1999969482422</v>
       </c>
       <c r="G1170" t="n">
-        <v>81.9910430908203</v>
+        <v>81.9910354614258</v>
       </c>
       <c r="H1170" t="n">
         <v>38914</v>
@@ -34357,7 +34357,7 @@
         <v>84.0500030517578</v>
       </c>
       <c r="G1172" t="n">
-        <v>79.9460296630859</v>
+        <v>79.9460220336914</v>
       </c>
       <c r="H1172" t="n">
         <v>45123</v>
@@ -34386,7 +34386,7 @@
         <v>85.6500015258789</v>
       </c>
       <c r="G1173" t="n">
-        <v>81.4678955078125</v>
+        <v>81.467903137207</v>
       </c>
       <c r="H1173" t="n">
         <v>40035</v>
@@ -34473,7 +34473,7 @@
         <v>88.4499969482422</v>
       </c>
       <c r="G1176" t="n">
-        <v>84.1311798095703</v>
+        <v>84.1311721801758</v>
       </c>
       <c r="H1176" t="n">
         <v>55416</v>
@@ -34502,7 +34502,7 @@
         <v>87.6999969482422</v>
       </c>
       <c r="G1177" t="n">
-        <v>83.4178009033203</v>
+        <v>83.4177856445312</v>
       </c>
       <c r="H1177" t="n">
         <v>45666</v>
@@ -34560,7 +34560,7 @@
         <v>86.75</v>
       </c>
       <c r="G1179" t="n">
-        <v>82.5141906738281</v>
+        <v>82.5141830444336</v>
       </c>
       <c r="H1179" t="n">
         <v>14817</v>
@@ -34705,7 +34705,7 @@
         <v>90.9499969482422</v>
       </c>
       <c r="G1184" t="n">
-        <v>86.5091094970703</v>
+        <v>86.5091171264648</v>
       </c>
       <c r="H1184" t="n">
         <v>65273</v>
@@ -34734,7 +34734,7 @@
         <v>93</v>
       </c>
       <c r="G1185" t="n">
-        <v>88.4590072631836</v>
+        <v>88.4590148925781</v>
       </c>
       <c r="H1185" t="n">
         <v>46039</v>
@@ -34792,7 +34792,7 @@
         <v>94</v>
       </c>
       <c r="G1187" t="n">
-        <v>89.4101867675781</v>
+        <v>89.4101791381836</v>
       </c>
       <c r="H1187" t="n">
         <v>58953</v>
@@ -34850,7 +34850,7 @@
         <v>91.0999984741211</v>
       </c>
       <c r="G1189" t="n">
-        <v>86.6517715454102</v>
+        <v>86.6517791748047</v>
       </c>
       <c r="H1189" t="n">
         <v>206478</v>
@@ -34879,7 +34879,7 @@
         <v>94.5999984741211</v>
       </c>
       <c r="G1190" t="n">
-        <v>89.9808883666992</v>
+        <v>89.9808807373047</v>
       </c>
       <c r="H1190" t="n">
         <v>43407</v>
@@ -34908,7 +34908,7 @@
         <v>93.5999984741211</v>
       </c>
       <c r="G1191" t="n">
-        <v>89.0297088623047</v>
+        <v>89.0297164916992</v>
       </c>
       <c r="H1191" t="n">
         <v>72905</v>
@@ -34937,7 +34937,7 @@
         <v>93.9000015258789</v>
       </c>
       <c r="G1192" t="n">
-        <v>89.315071105957</v>
+        <v>89.3150634765625</v>
       </c>
       <c r="H1192" t="n">
         <v>29915</v>
@@ -34995,7 +34995,7 @@
         <v>96.4000015258789</v>
       </c>
       <c r="G1194" t="n">
-        <v>91.693000793457</v>
+        <v>91.6929931640625</v>
       </c>
       <c r="H1194" t="n">
         <v>51733</v>
@@ -35140,7 +35140,7 @@
         <v>96.9499969482422</v>
       </c>
       <c r="G1199" t="n">
-        <v>92.2161483764648</v>
+        <v>92.2161331176758</v>
       </c>
       <c r="H1199" t="n">
         <v>123684</v>
@@ -35169,7 +35169,7 @@
         <v>94.8499984741211</v>
       </c>
       <c r="G1200" t="n">
-        <v>90.2186813354492</v>
+        <v>90.2186737060547</v>
       </c>
       <c r="H1200" t="n">
         <v>72844</v>
@@ -35198,7 +35198,7 @@
         <v>93.25</v>
       </c>
       <c r="G1201" t="n">
-        <v>88.6968078613281</v>
+        <v>88.6968154907227</v>
       </c>
       <c r="H1201" t="n">
         <v>74508</v>
@@ -35227,7 +35227,7 @@
         <v>95</v>
       </c>
       <c r="G1202" t="n">
-        <v>90.3613586425781</v>
+        <v>90.3613510131836</v>
       </c>
       <c r="H1202" t="n">
         <v>36415</v>
@@ -35314,7 +35314,7 @@
         <v>99.0500030517578</v>
       </c>
       <c r="G1205" t="n">
-        <v>94.2136077880859</v>
+        <v>94.2135925292969</v>
       </c>
       <c r="H1205" t="n">
         <v>57756</v>
@@ -35430,7 +35430,7 @@
         <v>97.0500030517578</v>
       </c>
       <c r="G1209" t="n">
-        <v>92.3112564086914</v>
+        <v>92.3112640380859</v>
       </c>
       <c r="H1209" t="n">
         <v>53746</v>
@@ -35488,7 +35488,7 @@
         <v>96.0999984741211</v>
       </c>
       <c r="G1211" t="n">
-        <v>91.4076538085938</v>
+        <v>91.4076461791992</v>
       </c>
       <c r="H1211" t="n">
         <v>73386</v>
@@ -35546,7 +35546,7 @@
         <v>96.4499969482422</v>
       </c>
       <c r="G1213" t="n">
-        <v>91.7405471801758</v>
+        <v>91.7405548095703</v>
       </c>
       <c r="H1213" t="n">
         <v>87145</v>
@@ -35575,7 +35575,7 @@
         <v>98.8000030517578</v>
       </c>
       <c r="G1214" t="n">
-        <v>93.9758071899414</v>
+        <v>93.9758148193359</v>
       </c>
       <c r="H1214" t="n">
         <v>70240</v>
@@ -35604,7 +35604,7 @@
         <v>100.800003051758</v>
       </c>
       <c r="G1215" t="n">
-        <v>95.8781433105469</v>
+        <v>95.8781509399414</v>
       </c>
       <c r="H1215" t="n">
         <v>136348</v>
@@ -35662,7 +35662,7 @@
         <v>103.400001525879</v>
       </c>
       <c r="G1217" t="n">
-        <v>98.3512115478516</v>
+        <v>98.351203918457</v>
       </c>
       <c r="H1217" t="n">
         <v>56791</v>
@@ -35720,7 +35720,7 @@
         <v>101.5</v>
       </c>
       <c r="G1219" t="n">
-        <v>96.5439682006836</v>
+        <v>96.5439758300781</v>
       </c>
       <c r="H1219" t="n">
         <v>25345</v>
@@ -35749,7 +35749,7 @@
         <v>102</v>
       </c>
       <c r="G1220" t="n">
-        <v>97.0195617675781</v>
+        <v>97.0195693969727</v>
       </c>
       <c r="H1220" t="n">
         <v>23102</v>
@@ -35778,7 +35778,7 @@
         <v>99.8499984741211</v>
       </c>
       <c r="G1221" t="n">
-        <v>94.9745330810547</v>
+        <v>94.9745254516602</v>
       </c>
       <c r="H1221" t="n">
         <v>28479</v>
@@ -35807,7 +35807,7 @@
         <v>97.1999969482422</v>
       </c>
       <c r="G1222" t="n">
-        <v>92.4539260864258</v>
+        <v>92.4539337158203</v>
       </c>
       <c r="H1222" t="n">
         <v>39108</v>
@@ -35836,7 +35836,7 @@
         <v>96.25</v>
       </c>
       <c r="G1223" t="n">
-        <v>91.5503158569336</v>
+        <v>91.5503311157227</v>
       </c>
       <c r="H1223" t="n">
         <v>44547</v>
@@ -35894,7 +35894,7 @@
         <v>94</v>
       </c>
       <c r="G1225" t="n">
-        <v>89.4101867675781</v>
+        <v>89.4101791381836</v>
       </c>
       <c r="H1225" t="n">
         <v>71967</v>
@@ -35923,7 +35923,7 @@
         <v>93.5999984741211</v>
       </c>
       <c r="G1226" t="n">
-        <v>89.0297088623047</v>
+        <v>89.0297164916992</v>
       </c>
       <c r="H1226" t="n">
         <v>39237</v>
@@ -35981,7 +35981,7 @@
         <v>91.4499969482422</v>
       </c>
       <c r="G1228" t="n">
-        <v>86.9846878051758</v>
+        <v>86.9846801757812</v>
       </c>
       <c r="H1228" t="n">
         <v>51731</v>
@@ -36039,7 +36039,7 @@
         <v>93.4499969482422</v>
       </c>
       <c r="G1230" t="n">
-        <v>88.8870315551758</v>
+        <v>88.8870468139648</v>
       </c>
       <c r="H1230" t="n">
         <v>36869</v>
@@ -36097,7 +36097,7 @@
         <v>100</v>
       </c>
       <c r="G1232" t="n">
-        <v>95.1172180175781</v>
+        <v>95.1172103881836</v>
       </c>
       <c r="H1232" t="n">
         <v>62981</v>
@@ -36126,7 +36126,7 @@
         <v>98.9499969482422</v>
       </c>
       <c r="G1233" t="n">
-        <v>94.1184768676758</v>
+        <v>94.1184921264648</v>
       </c>
       <c r="H1233" t="n">
         <v>58932</v>
@@ -36155,7 +36155,7 @@
         <v>99.3000030517578</v>
       </c>
       <c r="G1234" t="n">
-        <v>94.4513931274414</v>
+        <v>94.4514007568359</v>
       </c>
       <c r="H1234" t="n">
         <v>48780</v>
@@ -36242,7 +36242,7 @@
         <v>96.0999984741211</v>
       </c>
       <c r="G1237" t="n">
-        <v>91.4076538085938</v>
+        <v>91.4076461791992</v>
       </c>
       <c r="H1237" t="n">
         <v>50690</v>
@@ -36271,7 +36271,7 @@
         <v>95.4499969482422</v>
       </c>
       <c r="G1238" t="n">
-        <v>90.7893905639648</v>
+        <v>90.7893753051758</v>
       </c>
       <c r="H1238" t="n">
         <v>58034</v>
@@ -36329,7 +36329,7 @@
         <v>95.1999969482422</v>
       </c>
       <c r="G1240" t="n">
-        <v>90.5515899658203</v>
+        <v>90.5515823364258</v>
       </c>
       <c r="H1240" t="n">
         <v>42883</v>
@@ -36387,7 +36387,7 @@
         <v>94.1999969482422</v>
       </c>
       <c r="G1242" t="n">
-        <v>89.6004028320312</v>
+        <v>89.6004104614258</v>
       </c>
       <c r="H1242" t="n">
         <v>38249</v>
@@ -36445,7 +36445,7 @@
         <v>94.8499984741211</v>
       </c>
       <c r="G1244" t="n">
-        <v>90.2186813354492</v>
+        <v>90.2186737060547</v>
       </c>
       <c r="H1244" t="n">
         <v>28781</v>
@@ -36532,7 +36532,7 @@
         <v>91.5</v>
       </c>
       <c r="G1247" t="n">
-        <v>87.0322494506836</v>
+        <v>87.0322418212891</v>
       </c>
       <c r="H1247" t="n">
         <v>44578</v>
@@ -36561,7 +36561,7 @@
         <v>92.6500015258789</v>
       </c>
       <c r="G1248" t="n">
-        <v>88.1260986328125</v>
+        <v>88.126106262207</v>
       </c>
       <c r="H1248" t="n">
         <v>40262</v>
@@ -36590,7 +36590,7 @@
         <v>93.6999969482422</v>
       </c>
       <c r="G1249" t="n">
-        <v>89.1248321533203</v>
+        <v>89.1248245239258</v>
       </c>
       <c r="H1249" t="n">
         <v>30424</v>
@@ -36619,7 +36619,7 @@
         <v>93.6999969482422</v>
       </c>
       <c r="G1250" t="n">
-        <v>89.1248321533203</v>
+        <v>89.1248245239258</v>
       </c>
       <c r="H1250" t="n">
         <v>63343</v>
@@ -36648,7 +36648,7 @@
         <v>97.75</v>
       </c>
       <c r="G1251" t="n">
-        <v>92.9770660400391</v>
+        <v>92.9770736694336</v>
       </c>
       <c r="H1251" t="n">
         <v>57759</v>
@@ -36677,7 +36677,7 @@
         <v>93.6999969482422</v>
       </c>
       <c r="G1252" t="n">
-        <v>89.1248321533203</v>
+        <v>89.1248245239258</v>
       </c>
       <c r="H1252" t="n">
         <v>45494</v>
@@ -36735,7 +36735,7 @@
         <v>93.4499969482422</v>
       </c>
       <c r="G1254" t="n">
-        <v>88.8870315551758</v>
+        <v>88.8870468139648</v>
       </c>
       <c r="H1254" t="n">
         <v>36762</v>
@@ -36793,7 +36793,7 @@
         <v>95.9000015258789</v>
       </c>
       <c r="G1256" t="n">
-        <v>91.2174072265625</v>
+        <v>91.217414855957</v>
       </c>
       <c r="H1256" t="n">
         <v>28624</v>
@@ -36822,7 +36822,7 @@
         <v>94</v>
       </c>
       <c r="G1257" t="n">
-        <v>89.4101867675781</v>
+        <v>89.4101791381836</v>
       </c>
       <c r="H1257" t="n">
         <v>30381</v>
@@ -36851,7 +36851,7 @@
         <v>92.6500015258789</v>
       </c>
       <c r="G1258" t="n">
-        <v>88.1260986328125</v>
+        <v>88.126106262207</v>
       </c>
       <c r="H1258" t="n">
         <v>40249</v>
@@ -36880,7 +36880,7 @@
         <v>92.75</v>
       </c>
       <c r="G1259" t="n">
-        <v>88.2212219238281</v>
+        <v>88.2212142944336</v>
       </c>
       <c r="H1259" t="n">
         <v>37729</v>
@@ -36909,7 +36909,7 @@
         <v>94.8499984741211</v>
       </c>
       <c r="G1260" t="n">
-        <v>90.2186813354492</v>
+        <v>90.2186737060547</v>
       </c>
       <c r="H1260" t="n">
         <v>72658</v>
@@ -36938,7 +36938,7 @@
         <v>95.9000015258789</v>
       </c>
       <c r="G1261" t="n">
-        <v>91.2174072265625</v>
+        <v>91.217414855957</v>
       </c>
       <c r="H1261" t="n">
         <v>54871</v>
@@ -37054,7 +37054,7 @@
         <v>95.3000030517578</v>
       </c>
       <c r="G1265" t="n">
-        <v>90.6467056274414</v>
+        <v>90.6467132568359</v>
       </c>
       <c r="H1265" t="n">
         <v>26692</v>
@@ -37112,7 +37112,7 @@
         <v>94.4499969482422</v>
       </c>
       <c r="G1267" t="n">
-        <v>89.8382110595703</v>
+        <v>89.8381958007812</v>
       </c>
       <c r="H1267" t="n">
         <v>25415</v>
@@ -37141,7 +37141,7 @@
         <v>94.25</v>
       </c>
       <c r="G1268" t="n">
-        <v>89.6479797363281</v>
+        <v>89.6479721069336</v>
       </c>
       <c r="H1268" t="n">
         <v>21197</v>
@@ -37199,7 +37199,7 @@
         <v>95.3000030517578</v>
       </c>
       <c r="G1270" t="n">
-        <v>90.6467056274414</v>
+        <v>90.6467132568359</v>
       </c>
       <c r="H1270" t="n">
         <v>28340</v>
@@ -37257,7 +37257,7 @@
         <v>95.9499969482422</v>
       </c>
       <c r="G1272" t="n">
-        <v>91.2649612426758</v>
+        <v>91.2649765014648</v>
       </c>
       <c r="H1272" t="n">
         <v>31892</v>
@@ -37286,7 +37286,7 @@
         <v>94</v>
       </c>
       <c r="G1273" t="n">
-        <v>89.4101867675781</v>
+        <v>89.4101791381836</v>
       </c>
       <c r="H1273" t="n">
         <v>49431</v>
@@ -37344,7 +37344,7 @@
         <v>95.9000015258789</v>
       </c>
       <c r="G1275" t="n">
-        <v>91.2174072265625</v>
+        <v>91.217414855957</v>
       </c>
       <c r="H1275" t="n">
         <v>32675</v>
@@ -37373,7 +37373,7 @@
         <v>99.4499969482422</v>
       </c>
       <c r="G1276" t="n">
-        <v>94.5940704345703</v>
+        <v>94.5940551757812</v>
       </c>
       <c r="H1276" t="n">
         <v>97237</v>
@@ -37460,7 +37460,7 @@
         <v>97.75</v>
       </c>
       <c r="G1279" t="n">
-        <v>92.9770660400391</v>
+        <v>92.9770736694336</v>
       </c>
       <c r="H1279" t="n">
         <v>30226</v>
@@ -37489,7 +37489,7 @@
         <v>96.4000015258789</v>
       </c>
       <c r="G1280" t="n">
-        <v>91.693000793457</v>
+        <v>91.6929931640625</v>
       </c>
       <c r="H1280" t="n">
         <v>36393</v>
@@ -37547,7 +37547,7 @@
         <v>98.0500030517578</v>
       </c>
       <c r="G1282" t="n">
-        <v>93.2624282836914</v>
+        <v>93.2624359130859</v>
       </c>
       <c r="H1282" t="n">
         <v>25580</v>
@@ -37576,7 +37576,7 @@
         <v>99.5999984741211</v>
       </c>
       <c r="G1283" t="n">
-        <v>94.7367401123047</v>
+        <v>94.7367477416992</v>
       </c>
       <c r="H1283" t="n">
         <v>47187</v>
@@ -37605,7 +37605,7 @@
         <v>102.099998474121</v>
       </c>
       <c r="G1284" t="n">
-        <v>97.1146850585938</v>
+        <v>97.1146774291992</v>
       </c>
       <c r="H1284" t="n">
         <v>58169</v>
@@ -37634,7 +37634,7 @@
         <v>102</v>
       </c>
       <c r="G1285" t="n">
-        <v>97.0195617675781</v>
+        <v>97.0195693969727</v>
       </c>
       <c r="H1285" t="n">
         <v>42361</v>
@@ -37663,7 +37663,7 @@
         <v>103.400001525879</v>
       </c>
       <c r="G1286" t="n">
-        <v>98.3512115478516</v>
+        <v>98.351203918457</v>
       </c>
       <c r="H1286" t="n">
         <v>59565</v>
@@ -37721,7 +37721,7 @@
         <v>101.800003051758</v>
       </c>
       <c r="G1288" t="n">
-        <v>96.8293304443359</v>
+        <v>96.8293380737305</v>
       </c>
       <c r="H1288" t="n">
         <v>68095</v>
@@ -37808,7 +37808,7 @@
         <v>104.5</v>
       </c>
       <c r="G1291" t="n">
-        <v>99.3974914550781</v>
+        <v>99.3974990844727</v>
       </c>
       <c r="H1291" t="n">
         <v>49043</v>
@@ -37866,7 +37866,7 @@
         <v>105.199996948242</v>
       </c>
       <c r="G1293" t="n">
-        <v>100.06330871582</v>
+        <v>100.063301086426</v>
       </c>
       <c r="H1293" t="n">
         <v>67681</v>
@@ -37895,7 +37895,7 @@
         <v>106.5</v>
       </c>
       <c r="G1294" t="n">
-        <v>101.299827575684</v>
+        <v>101.299835205078</v>
       </c>
       <c r="H1294" t="n">
         <v>39475</v>
@@ -37924,7 +37924,7 @@
         <v>106.5</v>
       </c>
       <c r="G1295" t="n">
-        <v>101.299827575684</v>
+        <v>101.299835205078</v>
       </c>
       <c r="H1295" t="n">
         <v>44033</v>
@@ -37982,7 +37982,7 @@
         <v>105.900001525879</v>
       </c>
       <c r="G1297" t="n">
-        <v>100.729125976562</v>
+        <v>100.729133605957</v>
       </c>
       <c r="H1297" t="n">
         <v>38588</v>
@@ -38040,7 +38040,7 @@
         <v>106.900001525879</v>
       </c>
       <c r="G1299" t="n">
-        <v>101.680305480957</v>
+        <v>101.680313110352</v>
       </c>
       <c r="H1299" t="n">
         <v>28641</v>
@@ -38069,7 +38069,7 @@
         <v>107.400001525879</v>
       </c>
       <c r="G1300" t="n">
-        <v>102.155883789062</v>
+        <v>102.155891418457</v>
       </c>
       <c r="H1300" t="n">
         <v>20497</v>
@@ -38098,7 +38098,7 @@
         <v>106.599998474121</v>
       </c>
       <c r="G1301" t="n">
-        <v>101.394950866699</v>
+        <v>101.394958496094</v>
       </c>
       <c r="H1301" t="n">
         <v>37459</v>
@@ -38156,7 +38156,7 @@
         <v>104.199996948242</v>
       </c>
       <c r="G1303" t="n">
-        <v>99.1121368408203</v>
+        <v>99.1121444702148</v>
       </c>
       <c r="H1303" t="n">
         <v>27557</v>
@@ -38185,7 +38185,7 @@
         <v>103.400001525879</v>
       </c>
       <c r="G1304" t="n">
-        <v>98.3512115478516</v>
+        <v>98.351203918457</v>
       </c>
       <c r="H1304" t="n">
         <v>26925</v>
@@ -38214,7 +38214,7 @@
         <v>104.099998474121</v>
       </c>
       <c r="G1305" t="n">
-        <v>99.0170135498047</v>
+        <v>99.0170211791992</v>
       </c>
       <c r="H1305" t="n">
         <v>30338</v>
@@ -38301,7 +38301,7 @@
         <v>97.5999984741211</v>
       </c>
       <c r="G1308" t="n">
-        <v>92.8344116210938</v>
+        <v>92.8344039916992</v>
       </c>
       <c r="H1308" t="n">
         <v>46582</v>
@@ -38359,7 +38359,7 @@
         <v>96.0999984741211</v>
       </c>
       <c r="G1310" t="n">
-        <v>91.4076538085938</v>
+        <v>91.4076461791992</v>
       </c>
       <c r="H1310" t="n">
         <v>44072</v>
@@ -38388,7 +38388,7 @@
         <v>100</v>
       </c>
       <c r="G1311" t="n">
-        <v>95.1172180175781</v>
+        <v>95.1172103881836</v>
       </c>
       <c r="H1311" t="n">
         <v>35577</v>
@@ -38417,7 +38417,7 @@
         <v>100</v>
       </c>
       <c r="G1312" t="n">
-        <v>95.1172180175781</v>
+        <v>95.1172103881836</v>
       </c>
       <c r="H1312" t="n">
         <v>37909</v>
@@ -38475,7 +38475,7 @@
         <v>94</v>
       </c>
       <c r="G1314" t="n">
-        <v>89.4101867675781</v>
+        <v>89.4101791381836</v>
       </c>
       <c r="H1314" t="n">
         <v>59197</v>
@@ -38504,7 +38504,7 @@
         <v>92.5</v>
       </c>
       <c r="G1315" t="n">
-        <v>87.9834289550781</v>
+        <v>87.9834213256836</v>
       </c>
       <c r="H1315" t="n">
         <v>55193</v>
@@ -38533,7 +38533,7 @@
         <v>93.4499969482422</v>
       </c>
       <c r="G1316" t="n">
-        <v>88.8870315551758</v>
+        <v>88.8870468139648</v>
       </c>
       <c r="H1316" t="n">
         <v>52523</v>
@@ -38562,7 +38562,7 @@
         <v>96.4000015258789</v>
       </c>
       <c r="G1317" t="n">
-        <v>91.693000793457</v>
+        <v>91.6929931640625</v>
       </c>
       <c r="H1317" t="n">
         <v>49546</v>
@@ -38591,7 +38591,7 @@
         <v>95.1999969482422</v>
       </c>
       <c r="G1318" t="n">
-        <v>90.5515899658203</v>
+        <v>90.5515823364258</v>
       </c>
       <c r="H1318" t="n">
         <v>51988</v>
@@ -38823,7 +38823,7 @@
         <v>104.099998474121</v>
       </c>
       <c r="G1326" t="n">
-        <v>99.0170135498047</v>
+        <v>99.0170211791992</v>
       </c>
       <c r="H1326" t="n">
         <v>33265</v>
@@ -38852,7 +38852,7 @@
         <v>107.800003051758</v>
       </c>
       <c r="G1327" t="n">
-        <v>102.536361694336</v>
+        <v>102.536354064941</v>
       </c>
       <c r="H1327" t="n">
         <v>64274</v>
@@ -38910,7 +38910,7 @@
         <v>106.599998474121</v>
       </c>
       <c r="G1329" t="n">
-        <v>101.394950866699</v>
+        <v>101.394958496094</v>
       </c>
       <c r="H1329" t="n">
         <v>47410</v>
@@ -38939,7 +38939,7 @@
         <v>107.599998474121</v>
       </c>
       <c r="G1330" t="n">
-        <v>102.346130371094</v>
+        <v>102.346115112305</v>
       </c>
       <c r="H1330" t="n">
         <v>36683</v>
@@ -38997,7 +38997,7 @@
         <v>107.300003051758</v>
       </c>
       <c r="G1332" t="n">
-        <v>102.060775756836</v>
+        <v>102.06078338623</v>
       </c>
       <c r="H1332" t="n">
         <v>50548</v>
@@ -39026,7 +39026,7 @@
         <v>107.900001525879</v>
       </c>
       <c r="G1333" t="n">
-        <v>102.631477355957</v>
+        <v>102.631469726562</v>
       </c>
       <c r="H1333" t="n">
         <v>35336</v>
@@ -39055,7 +39055,7 @@
         <v>112</v>
       </c>
       <c r="G1334" t="n">
-        <v>106.531280517578</v>
+        <v>106.531272888184</v>
       </c>
       <c r="H1334" t="n">
         <v>66181</v>
@@ -39084,7 +39084,7 @@
         <v>114.199996948242</v>
       </c>
       <c r="G1335" t="n">
-        <v>108.62385559082</v>
+        <v>108.623863220215</v>
       </c>
       <c r="H1335" t="n">
         <v>51043</v>
@@ -39113,7 +39113,7 @@
         <v>112.699996948242</v>
       </c>
       <c r="G1336" t="n">
-        <v>107.197090148926</v>
+        <v>107.197113037109</v>
       </c>
       <c r="H1336" t="n">
         <v>31715</v>
@@ -39171,7 +39171,7 @@
         <v>111.400001525879</v>
       </c>
       <c r="G1338" t="n">
-        <v>105.960571289062</v>
+        <v>105.960578918457</v>
       </c>
       <c r="H1338" t="n">
         <v>34981</v>
@@ -39200,7 +39200,7 @@
         <v>110.300003051758</v>
       </c>
       <c r="G1339" t="n">
-        <v>104.914291381836</v>
+        <v>104.914283752441</v>
       </c>
       <c r="H1339" t="n">
         <v>31560</v>
@@ -39258,7 +39258,7 @@
         <v>111.800003051758</v>
       </c>
       <c r="G1341" t="n">
-        <v>106.34105682373</v>
+        <v>106.341049194336</v>
       </c>
       <c r="H1341" t="n">
         <v>25542</v>
@@ -39287,7 +39287,7 @@
         <v>112.699996948242</v>
       </c>
       <c r="G1342" t="n">
-        <v>107.197090148926</v>
+        <v>107.197113037109</v>
       </c>
       <c r="H1342" t="n">
         <v>22324</v>
@@ -39374,7 +39374,7 @@
         <v>111</v>
       </c>
       <c r="G1345" t="n">
-        <v>105.580101013184</v>
+        <v>105.580108642578</v>
       </c>
       <c r="H1345" t="n">
         <v>39539</v>
@@ -39403,7 +39403,7 @@
         <v>111.300003051758</v>
       </c>
       <c r="G1346" t="n">
-        <v>105.865455627441</v>
+        <v>105.865463256836</v>
       </c>
       <c r="H1346" t="n">
         <v>26545</v>
@@ -39432,7 +39432,7 @@
         <v>111.800003051758</v>
       </c>
       <c r="G1347" t="n">
-        <v>106.34105682373</v>
+        <v>106.341049194336</v>
       </c>
       <c r="H1347" t="n">
         <v>19174</v>
@@ -39461,7 +39461,7 @@
         <v>112</v>
       </c>
       <c r="G1348" t="n">
-        <v>106.531280517578</v>
+        <v>106.531272888184</v>
       </c>
       <c r="H1348" t="n">
         <v>25932</v>
@@ -39548,7 +39548,7 @@
         <v>112.5</v>
       </c>
       <c r="G1351" t="n">
-        <v>107.006858825684</v>
+        <v>107.006874084473</v>
       </c>
       <c r="H1351" t="n">
         <v>18095</v>
@@ -39577,7 +39577,7 @@
         <v>112.5</v>
       </c>
       <c r="G1352" t="n">
-        <v>107.006858825684</v>
+        <v>107.006874084473</v>
       </c>
       <c r="H1352" t="n">
         <v>21119</v>
@@ -39635,7 +39635,7 @@
         <v>113</v>
       </c>
       <c r="G1354" t="n">
-        <v>108.017288208008</v>
+        <v>108.017280578613</v>
       </c>
       <c r="H1354" t="n">
         <v>16846</v>
@@ -39693,7 +39693,7 @@
         <v>112.199996948242</v>
       </c>
       <c r="G1356" t="n">
-        <v>107.252563476562</v>
+        <v>107.252555847168</v>
       </c>
       <c r="H1356" t="n">
         <v>28836</v>
@@ -39722,7 +39722,7 @@
         <v>112.5</v>
       </c>
       <c r="G1357" t="n">
-        <v>107.539329528809</v>
+        <v>107.539337158203</v>
       </c>
       <c r="H1357" t="n">
         <v>31786</v>
@@ -39751,7 +39751,7 @@
         <v>113.400001525879</v>
       </c>
       <c r="G1358" t="n">
-        <v>108.399658203125</v>
+        <v>108.39965057373</v>
       </c>
       <c r="H1358" t="n">
         <v>19147</v>
@@ -39809,7 +39809,7 @@
         <v>113.300003051758</v>
       </c>
       <c r="G1360" t="n">
-        <v>108.304061889648</v>
+        <v>108.304054260254</v>
       </c>
       <c r="H1360" t="n">
         <v>38040</v>
@@ -40099,7 +40099,7 @@
         <v>120.199996948242</v>
       </c>
       <c r="G1370" t="n">
-        <v>114.899795532227</v>
+        <v>114.899803161621</v>
       </c>
       <c r="H1370" t="n">
         <v>35964</v>
@@ -40157,7 +40157,7 @@
         <v>130.600006103516</v>
       </c>
       <c r="G1372" t="n">
-        <v>124.841232299805</v>
+        <v>124.84122467041</v>
       </c>
       <c r="H1372" t="n">
         <v>144632</v>
@@ -40186,7 +40186,7 @@
         <v>132.899993896484</v>
       </c>
       <c r="G1373" t="n">
-        <v>127.03980255127</v>
+        <v>127.03978729248</v>
       </c>
       <c r="H1373" t="n">
         <v>59231</v>
@@ -40215,7 +40215,7 @@
         <v>131.399993896484</v>
       </c>
       <c r="G1374" t="n">
-        <v>125.605949401855</v>
+        <v>125.605934143066</v>
       </c>
       <c r="H1374" t="n">
         <v>33468</v>
@@ -40244,7 +40244,7 @@
         <v>131.399993896484</v>
       </c>
       <c r="G1375" t="n">
-        <v>125.605949401855</v>
+        <v>125.605934143066</v>
       </c>
       <c r="H1375" t="n">
         <v>27445</v>
@@ -40273,7 +40273,7 @@
         <v>131.300003051758</v>
       </c>
       <c r="G1376" t="n">
-        <v>125.510345458984</v>
+        <v>125.510360717773</v>
       </c>
       <c r="H1376" t="n">
         <v>39830</v>
@@ -40302,7 +40302,7 @@
         <v>131.399993896484</v>
       </c>
       <c r="G1377" t="n">
-        <v>125.605949401855</v>
+        <v>125.605934143066</v>
       </c>
       <c r="H1377" t="n">
         <v>28798</v>
@@ -40331,7 +40331,7 @@
         <v>132.5</v>
       </c>
       <c r="G1378" t="n">
-        <v>126.657432556152</v>
+        <v>126.657440185547</v>
       </c>
       <c r="H1378" t="n">
         <v>62887</v>
@@ -40360,7 +40360,7 @@
         <v>137.399993896484</v>
       </c>
       <c r="G1379" t="n">
-        <v>131.341369628906</v>
+        <v>131.341354370117</v>
       </c>
       <c r="H1379" t="n">
         <v>79282</v>
@@ -40389,7 +40389,7 @@
         <v>134.600006103516</v>
       </c>
       <c r="G1380" t="n">
-        <v>128.664855957031</v>
+        <v>128.664840698242</v>
       </c>
       <c r="H1380" t="n">
         <v>60060</v>
@@ -40476,7 +40476,7 @@
         <v>138.899993896484</v>
       </c>
       <c r="G1383" t="n">
-        <v>132.775238037109</v>
+        <v>132.77522277832</v>
       </c>
       <c r="H1383" t="n">
         <v>67629</v>
@@ -40505,7 +40505,7 @@
         <v>140</v>
       </c>
       <c r="G1384" t="n">
-        <v>133.826721191406</v>
+        <v>133.826736450195</v>
       </c>
       <c r="H1384" t="n">
         <v>48147</v>
@@ -40679,7 +40679,7 @@
         <v>138.899993896484</v>
       </c>
       <c r="G1390" t="n">
-        <v>132.775238037109</v>
+        <v>132.77522277832</v>
       </c>
       <c r="H1390" t="n">
         <v>44778</v>
@@ -41027,7 +41027,7 @@
         <v>144.5</v>
       </c>
       <c r="G1402" t="n">
-        <v>138.128295898438</v>
+        <v>138.128311157227</v>
       </c>
       <c r="H1402" t="n">
         <v>112135</v>
@@ -41056,7 +41056,7 @@
         <v>143.199996948242</v>
       </c>
       <c r="G1403" t="n">
-        <v>136.885635375977</v>
+        <v>136.885620117188</v>
       </c>
       <c r="H1403" t="n">
         <v>62167</v>
@@ -41085,7 +41085,7 @@
         <v>145</v>
       </c>
       <c r="G1404" t="n">
-        <v>138.606262207031</v>
+        <v>138.606246948242</v>
       </c>
       <c r="H1404" t="n">
         <v>44508</v>
@@ -41201,7 +41201,7 @@
         <v>143</v>
       </c>
       <c r="G1408" t="n">
-        <v>136.694442749023</v>
+        <v>136.694458007812</v>
       </c>
       <c r="H1408" t="n">
         <v>43072</v>
@@ -41230,7 +41230,7 @@
         <v>140.300003051758</v>
       </c>
       <c r="G1409" t="n">
-        <v>134.113494873047</v>
+        <v>134.113510131836</v>
       </c>
       <c r="H1409" t="n">
         <v>38233</v>
@@ -41259,7 +41259,7 @@
         <v>142</v>
       </c>
       <c r="G1410" t="n">
-        <v>135.738540649414</v>
+        <v>135.738525390625</v>
       </c>
       <c r="H1410" t="n">
         <v>33438</v>
@@ -41317,7 +41317,7 @@
         <v>145.699996948242</v>
       </c>
       <c r="G1412" t="n">
-        <v>139.275375366211</v>
+        <v>139.275390625</v>
       </c>
       <c r="H1412" t="n">
         <v>24565</v>
@@ -41346,7 +41346,7 @@
         <v>147.100006103516</v>
       </c>
       <c r="G1413" t="n">
-        <v>140.613647460938</v>
+        <v>140.613662719727</v>
       </c>
       <c r="H1413" t="n">
         <v>32223</v>
@@ -41375,7 +41375,7 @@
         <v>146.399993896484</v>
       </c>
       <c r="G1414" t="n">
-        <v>139.94450378418</v>
+        <v>139.944519042969</v>
       </c>
       <c r="H1414" t="n">
         <v>20347</v>
@@ -41404,7 +41404,7 @@
         <v>145</v>
       </c>
       <c r="G1415" t="n">
-        <v>138.606262207031</v>
+        <v>138.606246948242</v>
       </c>
       <c r="H1415" t="n">
         <v>20017</v>
@@ -41433,7 +41433,7 @@
         <v>147.800003051758</v>
       </c>
       <c r="G1416" t="n">
-        <v>141.282791137695</v>
+        <v>141.282775878906</v>
       </c>
       <c r="H1416" t="n">
         <v>36663</v>
@@ -41520,7 +41520,7 @@
         <v>153.600006103516</v>
       </c>
       <c r="G1419" t="n">
-        <v>146.827041625977</v>
+        <v>146.827056884766</v>
       </c>
       <c r="H1419" t="n">
         <v>39581</v>
@@ -41549,7 +41549,7 @@
         <v>152.699996948242</v>
       </c>
       <c r="G1420" t="n">
-        <v>145.966735839844</v>
+        <v>145.966720581055</v>
       </c>
       <c r="H1420" t="n">
         <v>73358</v>
@@ -41578,7 +41578,7 @@
         <v>153.899993896484</v>
       </c>
       <c r="G1421" t="n">
-        <v>147.113784790039</v>
+        <v>147.113800048828</v>
       </c>
       <c r="H1421" t="n">
         <v>39004</v>
@@ -41665,7 +41665,7 @@
         <v>151.899993896484</v>
       </c>
       <c r="G1424" t="n">
-        <v>145.201995849609</v>
+        <v>145.20198059082</v>
       </c>
       <c r="H1424" t="n">
         <v>23388</v>
@@ -41694,7 +41694,7 @@
         <v>152.699996948242</v>
       </c>
       <c r="G1425" t="n">
-        <v>145.966735839844</v>
+        <v>145.966720581055</v>
       </c>
       <c r="H1425" t="n">
         <v>35670</v>
@@ -41723,7 +41723,7 @@
         <v>152.899993896484</v>
       </c>
       <c r="G1426" t="n">
-        <v>146.157913208008</v>
+        <v>146.157897949219</v>
       </c>
       <c r="H1426" t="n">
         <v>24907</v>
@@ -41810,7 +41810,7 @@
         <v>153.899993896484</v>
       </c>
       <c r="G1429" t="n">
-        <v>147.113784790039</v>
+        <v>147.113800048828</v>
       </c>
       <c r="H1429" t="n">
         <v>30111</v>
@@ -41868,7 +41868,7 @@
         <v>160</v>
       </c>
       <c r="G1431" t="n">
-        <v>152.94482421875</v>
+        <v>152.944808959961</v>
       </c>
       <c r="H1431" t="n">
         <v>115666</v>
@@ -41955,7 +41955,7 @@
         <v>162.899993896484</v>
       </c>
       <c r="G1434" t="n">
-        <v>155.71696472168</v>
+        <v>155.716949462891</v>
       </c>
       <c r="H1434" t="n">
         <v>92761</v>
@@ -42071,7 +42071,7 @@
         <v>171.100006103516</v>
       </c>
       <c r="G1438" t="n">
-        <v>163.555374145508</v>
+        <v>163.555389404297</v>
       </c>
       <c r="H1438" t="n">
         <v>62716</v>
@@ -42100,7 +42100,7 @@
         <v>170.699996948242</v>
       </c>
       <c r="G1439" t="n">
-        <v>163.173004150391</v>
+        <v>163.17301940918</v>
       </c>
       <c r="H1439" t="n">
         <v>49153</v>
@@ -42129,7 +42129,7 @@
         <v>170.899993896484</v>
       </c>
       <c r="G1440" t="n">
-        <v>163.364196777344</v>
+        <v>163.364181518555</v>
       </c>
       <c r="H1440" t="n">
         <v>98616</v>
@@ -42187,7 +42187,7 @@
         <v>174.199996948242</v>
       </c>
       <c r="G1442" t="n">
-        <v>166.518676757812</v>
+        <v>166.518692016602</v>
       </c>
       <c r="H1442" t="n">
         <v>51312</v>
@@ -42216,7 +42216,7 @@
         <v>174.5</v>
       </c>
       <c r="G1443" t="n">
-        <v>166.805435180664</v>
+        <v>166.805450439453</v>
       </c>
       <c r="H1443" t="n">
         <v>63616</v>
@@ -42245,7 +42245,7 @@
         <v>175</v>
       </c>
       <c r="G1444" t="n">
-        <v>167.283416748047</v>
+        <v>167.283401489258</v>
       </c>
       <c r="H1444" t="n">
         <v>73534</v>
@@ -42303,7 +42303,7 @@
         <v>174.600006103516</v>
       </c>
       <c r="G1446" t="n">
-        <v>166.90104675293</v>
+        <v>166.901031494141</v>
       </c>
       <c r="H1446" t="n">
         <v>36715</v>
@@ -42361,7 +42361,7 @@
         <v>174.300003051758</v>
       </c>
       <c r="G1448" t="n">
-        <v>166.614273071289</v>
+        <v>166.614288330078</v>
       </c>
       <c r="H1448" t="n">
         <v>48289</v>
@@ -42419,7 +42419,7 @@
         <v>170.899993896484</v>
       </c>
       <c r="G1450" t="n">
-        <v>163.364196777344</v>
+        <v>163.364181518555</v>
       </c>
       <c r="H1450" t="n">
         <v>68801</v>
@@ -42477,7 +42477,7 @@
         <v>170.699996948242</v>
       </c>
       <c r="G1452" t="n">
-        <v>163.173004150391</v>
+        <v>163.17301940918</v>
       </c>
       <c r="H1452" t="n">
         <v>54486</v>
@@ -42506,7 +42506,7 @@
         <v>172.5</v>
       </c>
       <c r="G1453" t="n">
-        <v>164.893646240234</v>
+        <v>164.893630981445</v>
       </c>
       <c r="H1453" t="n">
         <v>347532</v>
@@ -42535,7 +42535,7 @@
         <v>170.300003051758</v>
       </c>
       <c r="G1454" t="n">
-        <v>162.790679931641</v>
+        <v>162.790664672852</v>
       </c>
       <c r="H1454" t="n">
         <v>53170</v>
@@ -42680,7 +42680,7 @@
         <v>174.600006103516</v>
       </c>
       <c r="G1459" t="n">
-        <v>166.90104675293</v>
+        <v>166.901031494141</v>
       </c>
       <c r="H1459" t="n">
         <v>52449</v>
@@ -42912,7 +42912,7 @@
         <v>153.899993896484</v>
       </c>
       <c r="G1467" t="n">
-        <v>147.113784790039</v>
+        <v>147.113800048828</v>
       </c>
       <c r="H1467" t="n">
         <v>78518</v>
@@ -43028,7 +43028,7 @@
         <v>162</v>
       </c>
       <c r="G1471" t="n">
-        <v>154.856643676758</v>
+        <v>154.856628417969</v>
       </c>
       <c r="H1471" t="n">
         <v>98031</v>
@@ -43057,7 +43057,7 @@
         <v>164.699996948242</v>
       </c>
       <c r="G1472" t="n">
-        <v>157.437576293945</v>
+        <v>157.437591552734</v>
       </c>
       <c r="H1472" t="n">
         <v>63746</v>
@@ -43173,7 +43173,7 @@
         <v>166.199996948242</v>
       </c>
       <c r="G1476" t="n">
-        <v>158.871429443359</v>
+        <v>158.87141418457</v>
       </c>
       <c r="H1476" t="n">
         <v>52895</v>
@@ -43260,7 +43260,7 @@
         <v>165.699996948242</v>
       </c>
       <c r="G1479" t="n">
-        <v>158.393478393555</v>
+        <v>158.393493652344</v>
       </c>
       <c r="H1479" t="n">
         <v>46070</v>
@@ -43289,7 +43289,7 @@
         <v>170.699996948242</v>
       </c>
       <c r="G1480" t="n">
-        <v>163.173004150391</v>
+        <v>163.17301940918</v>
       </c>
       <c r="H1480" t="n">
         <v>33924</v>
@@ -43318,7 +43318,7 @@
         <v>166.699996948242</v>
       </c>
       <c r="G1481" t="n">
-        <v>159.349411010742</v>
+        <v>159.349395751953</v>
       </c>
       <c r="H1481" t="n">
         <v>38713</v>
@@ -43434,7 +43434,7 @@
         <v>169.600006103516</v>
       </c>
       <c r="G1485" t="n">
-        <v>162.121536254883</v>
+        <v>162.121520996094</v>
       </c>
       <c r="H1485" t="n">
         <v>34085</v>
@@ -43463,7 +43463,7 @@
         <v>176.699996948242</v>
       </c>
       <c r="G1486" t="n">
-        <v>168.908416748047</v>
+        <v>168.908432006836</v>
       </c>
       <c r="H1486" t="n">
         <v>48368</v>
@@ -43579,7 +43579,7 @@
         <v>177.100006103516</v>
       </c>
       <c r="G1490" t="n">
-        <v>169.290832519531</v>
+        <v>169.290817260742</v>
       </c>
       <c r="H1490" t="n">
         <v>26620</v>
@@ -43608,7 +43608,7 @@
         <v>174.199996948242</v>
       </c>
       <c r="G1491" t="n">
-        <v>166.518676757812</v>
+        <v>166.518692016602</v>
       </c>
       <c r="H1491" t="n">
         <v>46029</v>
@@ -43695,7 +43695,7 @@
         <v>185.5</v>
       </c>
       <c r="G1494" t="n">
-        <v>177.320419311523</v>
+        <v>177.320404052734</v>
       </c>
       <c r="H1494" t="n">
         <v>57419</v>
@@ -43753,7 +43753,7 @@
         <v>176.699996948242</v>
       </c>
       <c r="G1496" t="n">
-        <v>168.908416748047</v>
+        <v>168.908432006836</v>
       </c>
       <c r="H1496" t="n">
         <v>42422</v>
@@ -43782,7 +43782,7 @@
         <v>174.100006103516</v>
       </c>
       <c r="G1497" t="n">
-        <v>166.423110961914</v>
+        <v>166.423095703125</v>
       </c>
       <c r="H1497" t="n">
         <v>55736</v>
@@ -43840,7 +43840,7 @@
         <v>172.300003051758</v>
       </c>
       <c r="G1499" t="n">
-        <v>164.702453613281</v>
+        <v>164.70246887207</v>
       </c>
       <c r="H1499" t="n">
         <v>31419</v>
@@ -43898,7 +43898,7 @@
         <v>167.600006103516</v>
       </c>
       <c r="G1501" t="n">
-        <v>160.209701538086</v>
+        <v>160.209716796875</v>
       </c>
       <c r="H1501" t="n">
         <v>38992</v>
@@ -44072,7 +44072,7 @@
         <v>165.800003051758</v>
       </c>
       <c r="G1507" t="n">
-        <v>158.48908996582</v>
+        <v>158.489074707031</v>
       </c>
       <c r="H1507" t="n">
         <v>34461</v>
@@ -44130,7 +44130,7 @@
         <v>164.199996948242</v>
       </c>
       <c r="G1509" t="n">
-        <v>156.959625244141</v>
+        <v>156.959609985352</v>
       </c>
       <c r="H1509" t="n">
         <v>26320</v>
@@ -44159,7 +44159,7 @@
         <v>178</v>
       </c>
       <c r="G1510" t="n">
-        <v>170.151107788086</v>
+        <v>170.151123046875</v>
       </c>
       <c r="H1510" t="n">
         <v>61985</v>
@@ -44217,7 +44217,7 @@
         <v>180.5</v>
       </c>
       <c r="G1512" t="n">
-        <v>172.540893554688</v>
+        <v>172.540878295898</v>
       </c>
       <c r="H1512" t="n">
         <v>51673</v>
@@ -44275,7 +44275,7 @@
         <v>180.100006103516</v>
       </c>
       <c r="G1514" t="n">
-        <v>172.15852355957</v>
+        <v>172.158508300781</v>
       </c>
       <c r="H1514" t="n">
         <v>39525</v>
@@ -44304,7 +44304,7 @@
         <v>174.800003051758</v>
       </c>
       <c r="G1515" t="n">
-        <v>167.092224121094</v>
+        <v>167.092239379883</v>
       </c>
       <c r="H1515" t="n">
         <v>49659</v>
@@ -44333,7 +44333,7 @@
         <v>173.399993896484</v>
       </c>
       <c r="G1516" t="n">
-        <v>165.753967285156</v>
+        <v>165.753952026367</v>
       </c>
       <c r="H1516" t="n">
         <v>43490</v>
@@ -44362,7 +44362,7 @@
         <v>170.300003051758</v>
       </c>
       <c r="G1517" t="n">
-        <v>162.790679931641</v>
+        <v>162.790664672852</v>
       </c>
       <c r="H1517" t="n">
         <v>31949</v>
@@ -44420,7 +44420,7 @@
         <v>170.100006103516</v>
       </c>
       <c r="G1519" t="n">
-        <v>162.599472045898</v>
+        <v>162.599487304688</v>
       </c>
       <c r="H1519" t="n">
         <v>41298</v>
@@ -44478,7 +44478,7 @@
         <v>176</v>
       </c>
       <c r="G1521" t="n">
-        <v>168.239288330078</v>
+        <v>168.239303588867</v>
       </c>
       <c r="H1521" t="n">
         <v>28207</v>
@@ -44507,7 +44507,7 @@
         <v>174.600006103516</v>
       </c>
       <c r="G1522" t="n">
-        <v>166.90104675293</v>
+        <v>166.901031494141</v>
       </c>
       <c r="H1522" t="n">
         <v>17658</v>
@@ -44536,7 +44536,7 @@
         <v>175.199996948242</v>
       </c>
       <c r="G1523" t="n">
-        <v>167.474563598633</v>
+        <v>167.474578857422</v>
       </c>
       <c r="H1523" t="n">
         <v>19137</v>
@@ -44565,7 +44565,7 @@
         <v>180</v>
       </c>
       <c r="G1524" t="n">
-        <v>172.062942504883</v>
+        <v>172.062927246094</v>
       </c>
       <c r="H1524" t="n">
         <v>50857</v>
@@ -44652,7 +44652,7 @@
         <v>174.600006103516</v>
       </c>
       <c r="G1527" t="n">
-        <v>166.90104675293</v>
+        <v>166.901031494141</v>
       </c>
       <c r="H1527" t="n">
         <v>24336</v>
@@ -44681,7 +44681,7 @@
         <v>169.199996948242</v>
       </c>
       <c r="G1528" t="n">
-        <v>161.739151000977</v>
+        <v>161.739135742188</v>
       </c>
       <c r="H1528" t="n">
         <v>52023</v>
@@ -44739,7 +44739,7 @@
         <v>162.300003051758</v>
       </c>
       <c r="G1530" t="n">
-        <v>155.143417358398</v>
+        <v>155.143402099609</v>
       </c>
       <c r="H1530" t="n">
         <v>60175</v>
@@ -44797,7 +44797,7 @@
         <v>152.699996948242</v>
       </c>
       <c r="G1532" t="n">
-        <v>145.966735839844</v>
+        <v>145.966720581055</v>
       </c>
       <c r="H1532" t="n">
         <v>75538</v>
@@ -44826,7 +44826,7 @@
         <v>160.800003051758</v>
       </c>
       <c r="G1533" t="n">
-        <v>153.709548950195</v>
+        <v>153.709533691406</v>
       </c>
       <c r="H1533" t="n">
         <v>81184</v>
@@ -44855,7 +44855,7 @@
         <v>160.600006103516</v>
       </c>
       <c r="G1534" t="n">
-        <v>153.51838684082</v>
+        <v>153.518402099609</v>
       </c>
       <c r="H1534" t="n">
         <v>46550</v>
@@ -44913,7 +44913,7 @@
         <v>155.800003051758</v>
       </c>
       <c r="G1536" t="n">
-        <v>148.930038452148</v>
+        <v>148.930023193359</v>
       </c>
       <c r="H1536" t="n">
         <v>47460</v>
@@ -44942,7 +44942,7 @@
         <v>162.199996948242</v>
       </c>
       <c r="G1537" t="n">
-        <v>155.047805786133</v>
+        <v>155.047821044922</v>
       </c>
       <c r="H1537" t="n">
         <v>32089</v>
@@ -45087,7 +45087,7 @@
         <v>145.699996948242</v>
       </c>
       <c r="G1542" t="n">
-        <v>139.275375366211</v>
+        <v>139.275390625</v>
       </c>
       <c r="H1542" t="n">
         <v>71724</v>
@@ -45174,7 +45174,7 @@
         <v>146.399993896484</v>
       </c>
       <c r="G1545" t="n">
-        <v>139.94450378418</v>
+        <v>139.944519042969</v>
       </c>
       <c r="H1545" t="n">
         <v>59846</v>
@@ -45261,7 +45261,7 @@
         <v>149.100006103516</v>
       </c>
       <c r="G1548" t="n">
-        <v>142.525482177734</v>
+        <v>142.525466918945</v>
       </c>
       <c r="H1548" t="n">
         <v>37523</v>
@@ -45290,7 +45290,7 @@
         <v>149.5</v>
       </c>
       <c r="G1549" t="n">
-        <v>142.907821655273</v>
+        <v>142.907836914062</v>
       </c>
       <c r="H1549" t="n">
         <v>33814</v>
@@ -45464,7 +45464,7 @@
         <v>136.5</v>
       </c>
       <c r="G1555" t="n">
-        <v>130.481063842773</v>
+        <v>130.481048583984</v>
       </c>
       <c r="H1555" t="n">
         <v>57243</v>
@@ -45551,7 +45551,7 @@
         <v>143.399993896484</v>
       </c>
       <c r="G1558" t="n">
-        <v>137.076782226562</v>
+        <v>137.076797485352</v>
       </c>
       <c r="H1558" t="n">
         <v>68151</v>
@@ -45580,7 +45580,7 @@
         <v>142.199996948242</v>
       </c>
       <c r="G1559" t="n">
-        <v>135.929718017578</v>
+        <v>135.929733276367</v>
       </c>
       <c r="H1559" t="n">
         <v>44673</v>
@@ -45609,7 +45609,7 @@
         <v>143.199996948242</v>
       </c>
       <c r="G1560" t="n">
-        <v>136.885635375977</v>
+        <v>136.885620117188</v>
       </c>
       <c r="H1560" t="n">
         <v>46823</v>
@@ -45667,7 +45667,7 @@
         <v>140</v>
       </c>
       <c r="G1562" t="n">
-        <v>133.826721191406</v>
+        <v>133.826736450195</v>
       </c>
       <c r="H1562" t="n">
         <v>35852</v>
@@ -45696,7 +45696,7 @@
         <v>141.899993896484</v>
       </c>
       <c r="G1563" t="n">
-        <v>135.642944335938</v>
+        <v>135.642929077148</v>
       </c>
       <c r="H1563" t="n">
         <v>42985</v>
@@ -45754,7 +45754,7 @@
         <v>142.899993896484</v>
       </c>
       <c r="G1565" t="n">
-        <v>136.598846435547</v>
+        <v>136.598861694336</v>
       </c>
       <c r="H1565" t="n">
         <v>52836</v>
@@ -45783,7 +45783,7 @@
         <v>144.5</v>
       </c>
       <c r="G1566" t="n">
-        <v>138.128295898438</v>
+        <v>138.128311157227</v>
       </c>
       <c r="H1566" t="n">
         <v>76281</v>
@@ -45812,7 +45812,7 @@
         <v>145.699996948242</v>
       </c>
       <c r="G1567" t="n">
-        <v>139.275375366211</v>
+        <v>139.275390625</v>
       </c>
       <c r="H1567" t="n">
         <v>48715</v>
@@ -45841,7 +45841,7 @@
         <v>143</v>
       </c>
       <c r="G1568" t="n">
-        <v>136.694442749023</v>
+        <v>136.694458007812</v>
       </c>
       <c r="H1568" t="n">
         <v>59052</v>
@@ -45899,7 +45899,7 @@
         <v>141.899993896484</v>
       </c>
       <c r="G1570" t="n">
-        <v>135.642944335938</v>
+        <v>135.642929077148</v>
       </c>
       <c r="H1570" t="n">
         <v>46700</v>
@@ -46218,7 +46218,7 @@
         <v>156.800003051758</v>
       </c>
       <c r="G1581" t="n">
-        <v>149.885940551758</v>
+        <v>149.885955810547</v>
       </c>
       <c r="H1581" t="n">
         <v>72286</v>
@@ -46276,7 +46276,7 @@
         <v>154.100006103516</v>
       </c>
       <c r="G1583" t="n">
-        <v>147.30500793457</v>
+        <v>147.304992675781</v>
       </c>
       <c r="H1583" t="n">
         <v>31179</v>
@@ -46392,7 +46392,7 @@
         <v>149.699996948242</v>
       </c>
       <c r="G1587" t="n">
-        <v>143.099014282227</v>
+        <v>143.098999023438</v>
       </c>
       <c r="H1587" t="n">
         <v>33092</v>
@@ -46537,7 +46537,7 @@
         <v>151.399993896484</v>
       </c>
       <c r="G1592" t="n">
-        <v>144.724044799805</v>
+        <v>144.724060058594</v>
       </c>
       <c r="H1592" t="n">
         <v>18047</v>
@@ -46624,7 +46624,7 @@
         <v>146</v>
       </c>
       <c r="G1595" t="n">
-        <v>139.562164306641</v>
+        <v>139.56217956543</v>
       </c>
       <c r="H1595" t="n">
         <v>49591</v>
@@ -46682,7 +46682,7 @@
         <v>143</v>
       </c>
       <c r="G1597" t="n">
-        <v>136.694442749023</v>
+        <v>136.694458007812</v>
       </c>
       <c r="H1597" t="n">
         <v>30165</v>
@@ -46740,7 +46740,7 @@
         <v>142</v>
       </c>
       <c r="G1599" t="n">
-        <v>135.738540649414</v>
+        <v>135.738525390625</v>
       </c>
       <c r="H1599" t="n">
         <v>56362</v>
@@ -46798,7 +46798,7 @@
         <v>138.800003051758</v>
       </c>
       <c r="G1601" t="n">
-        <v>132.679656982422</v>
+        <v>132.679641723633</v>
       </c>
       <c r="H1601" t="n">
         <v>32150</v>
@@ -46914,7 +46914,7 @@
         <v>138.800003051758</v>
       </c>
       <c r="G1605" t="n">
-        <v>132.679656982422</v>
+        <v>132.679641723633</v>
       </c>
       <c r="H1605" t="n">
         <v>31026</v>
@@ -46943,7 +46943,7 @@
         <v>136</v>
       </c>
       <c r="G1606" t="n">
-        <v>130.00309753418</v>
+        <v>130.003112792969</v>
       </c>
       <c r="H1606" t="n">
         <v>31999</v>
@@ -47088,7 +47088,7 @@
         <v>139.5</v>
       </c>
       <c r="G1611" t="n">
-        <v>133.348785400391</v>
+        <v>133.348770141602</v>
       </c>
       <c r="H1611" t="n">
         <v>33848</v>
@@ -47117,7 +47117,7 @@
         <v>135.100006103516</v>
       </c>
       <c r="G1612" t="n">
-        <v>129.142807006836</v>
+        <v>129.142791748047</v>
       </c>
       <c r="H1612" t="n">
         <v>31064</v>
@@ -47146,7 +47146,7 @@
         <v>131.800003051758</v>
       </c>
       <c r="G1613" t="n">
-        <v>125.988311767578</v>
+        <v>125.988319396973</v>
       </c>
       <c r="H1613" t="n">
         <v>23634</v>
@@ -47262,7 +47262,7 @@
         <v>121</v>
       </c>
       <c r="G1617" t="n">
-        <v>115.664527893066</v>
+        <v>115.664520263672</v>
       </c>
       <c r="H1617" t="n">
         <v>24683</v>
@@ -47291,7 +47291,7 @@
         <v>118.599998474121</v>
       </c>
       <c r="G1618" t="n">
-        <v>113.370346069336</v>
+        <v>113.37035369873</v>
       </c>
       <c r="H1618" t="n">
         <v>31396</v>
@@ -47320,7 +47320,7 @@
         <v>121.300003051758</v>
       </c>
       <c r="G1619" t="n">
-        <v>115.951293945312</v>
+        <v>115.951301574707</v>
       </c>
       <c r="H1619" t="n">
         <v>46882</v>
@@ -47349,7 +47349,7 @@
         <v>119.800003051758</v>
       </c>
       <c r="G1620" t="n">
-        <v>114.517440795898</v>
+        <v>114.517448425293</v>
       </c>
       <c r="H1620" t="n">
         <v>34303</v>
@@ -47436,7 +47436,7 @@
         <v>118.5</v>
       </c>
       <c r="G1623" t="n">
-        <v>113.274765014648</v>
+        <v>113.274749755859</v>
       </c>
       <c r="H1623" t="n">
         <v>37428</v>
@@ -80212,6 +80212,35 @@
         <v>44546</v>
       </c>
       <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>132.199996948242</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>133.699996948242</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>131.899993896484</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>133.699996948242</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>133.699996948242</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>55852</v>
+      </c>
+      <c r="I2754" t="s">
         <v>9</v>
       </c>
     </row>
